--- a/output/analysis_result.xlsx
+++ b/output/analysis_result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="2082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="2081">
   <si>
     <t>code</t>
   </si>
@@ -5920,15 +5920,15 @@
     <t>2021-03-13</t>
   </si>
   <si>
+    <t>極少使用</t>
+  </si>
+  <si>
+    <t>低頻</t>
+  </si>
+  <si>
     <t>中頻</t>
   </si>
   <si>
-    <t>低頻</t>
-  </si>
-  <si>
-    <t>極少使用</t>
-  </si>
-  <si>
     <t>從未領用</t>
   </si>
   <si>
@@ -5965,283 +5965,280 @@
     <t>建議提高：Min 1→3、Max 4→5</t>
   </si>
   <si>
+    <t>建議提高：Min 1→3、Max 3→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→2、Max 2→3</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→2、Max 2→4</t>
+  </si>
+  <si>
+    <t>建議提高：Max 2→3</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 4→3</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→3、Max 2→5</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→3、Max 1→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→2、Max 1→3</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 0→3、Max 10→4</t>
+  </si>
+  <si>
+    <t>建議降低：Max 10→5</t>
+  </si>
+  <si>
+    <t>建議降低：Max 10→3</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→8</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 0→3、Max 10→5</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 19 / Max 21</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 1→2、Max 5→3</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 1→2、Max 5→4</t>
+  </si>
+  <si>
+    <t>建議降低：Max 5→3</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→3</t>
+  </si>
+  <si>
+    <t>建議降低：Max 5→2</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 1→3、Max 10→5</t>
+  </si>
+  <si>
+    <t>建議降低：Min 3→1、Max 10→2</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 3→4、Max 10→6</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 2 / Max 4</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 1 / Max 3</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 1 / Max 2</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 12 / Max 14</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→19、Max 10→28</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 4 / Max 5</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→3、Max 2→4</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 5→2</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→3、Max 5→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→4、Max 5→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→2、Max 3→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→2</t>
+  </si>
+  <si>
+    <t>建議降低：Max 3→2</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 0→7、Max 20→9</t>
+  </si>
+  <si>
+    <t>建議降低：Min 10→2、Max 20→5</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 5 / Max 8</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 2 / Max 3</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 6 / Max 8</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→1、Max 1→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→1、Max 2→3</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→4、Max 3→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→1</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→3、Max 2→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→5、Max 8→9</t>
+  </si>
+  <si>
+    <t>建議提高：Max 4→6</t>
+  </si>
+  <si>
+    <t>建議降低：Max 8→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→6、Max 4→8</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 0→1、Max 4→3</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→3、Max 8→5</t>
+  </si>
+  <si>
+    <t>建議提高：Min 4→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→6、Max 4→9</t>
+  </si>
+  <si>
+    <t>建議降低：Max 8→7</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→9、Max 4→13</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→1、Max 8→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→3、Max 4→5</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→6、Max 1→9</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→27、Max 8→30</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→2、Max 10→4</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→3、Max 10→5</t>
+  </si>
+  <si>
+    <t>建議提高：Min 4→8、Max 10→11</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 4→7、Max 10→9</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→1、Max 10→3</t>
+  </si>
+  <si>
+    <t>建議降低：Max 10→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→13、Max 6→16</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 10→4</t>
+  </si>
+  <si>
+    <t>建議降低：Max 10→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→4、Max 5→6</t>
+  </si>
+  <si>
+    <t>建議降低：Max 4→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→21、Max 4→26</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→5、Max 1→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→3、Max 1→5</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→7、Max 10→9</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 10→3</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→4、Max 10→6</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 8→3</t>
+  </si>
+  <si>
+    <t>建議降低：Max 8→5</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→3、Max 10→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→6、Max 8→9</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 10→32、Max 50→35</t>
+  </si>
+  <si>
+    <t>建議降低：Min 5→2、Max 10→3</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→5、Max 10→7</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 3 / Max 4</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 6 / Max 9</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→4、Max 3→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→5、Max 4→7</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→5、Max 2→7</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 12→4</t>
+  </si>
+  <si>
     <t>建議提高：Min 1→4、Max 2→6</t>
   </si>
   <si>
-    <t>建議提高：Min 1→3、Max 3→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→2、Max 2→3</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→2、Max 2→4</t>
-  </si>
-  <si>
-    <t>建議提高：Max 2→3</t>
-  </si>
-  <si>
-    <t>建議降低：Min 2→1、Max 4→3</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→3、Max 2→5</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→3、Max 2→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→3、Max 1→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→2、Max 1→3</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 0→3、Max 10→4</t>
-  </si>
-  <si>
-    <t>建議降低：Max 10→5</t>
-  </si>
-  <si>
-    <t>建議降低：Max 10→3</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→8</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 0→3、Max 10→5</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 19 / Max 21</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 1→2、Max 5→3</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 1→2、Max 5→4</t>
-  </si>
-  <si>
-    <t>建議降低：Max 5→3</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→3</t>
-  </si>
-  <si>
-    <t>建議降低：Max 5→2</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 1→3、Max 10→5</t>
-  </si>
-  <si>
-    <t>建議降低：Min 3→1、Max 10→2</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 3→4、Max 10→6</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 3 / Max 5</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 2 / Max 3</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 14 / Max 16</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→19、Max 10→28</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 4 / Max 5</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 1 / Max 2</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→3、Max 5→4</t>
-  </si>
-  <si>
-    <t>建議降低：Min 2→1、Max 5→2</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→4、Max 5→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→2、Max 3→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→2</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 0→7、Max 20→9</t>
-  </si>
-  <si>
-    <t>建議降低：Min 10→2、Max 20→5</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 5 / Max 8</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 2 / Max 4</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 6 / Max 8</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 13 / Max 15</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 1 / Max 3</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→1、Max 1→2</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→4、Max 3→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→2、Max 2→3</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→3、Max 2→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→5、Max 8→9</t>
-  </si>
-  <si>
-    <t>建議提高：Max 4→6</t>
-  </si>
-  <si>
-    <t>建議降低：Max 8→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→6、Max 4→8</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 0→1、Max 4→3</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→3、Max 8→5</t>
-  </si>
-  <si>
-    <t>建議提高：Min 4→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→6、Max 4→9</t>
-  </si>
-  <si>
-    <t>建議降低：Max 8→7</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→9、Max 4→13</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→3、Max 8→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→3、Max 4→5</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→6、Max 1→9</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→34、Max 8→37</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→2、Max 10→4</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→3、Max 10→5</t>
-  </si>
-  <si>
-    <t>建議提高：Min 4→8、Max 10→11</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 4→7、Max 10→9</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→1、Max 10→3</t>
-  </si>
-  <si>
-    <t>建議降低：Max 10→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→13、Max 6→16</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→5、Max 10→8</t>
-  </si>
-  <si>
-    <t>建議降低：Max 10→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→4、Max 5→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→21、Max 4→26</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→7、Max 1→8</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→5、Max 1→7</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→7、Max 10→9</t>
-  </si>
-  <si>
-    <t>建議降低：Min 2→1、Max 10→3</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→4、Max 10→6</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→4、Max 8→7</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→3、Max 10→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→6、Max 8→9</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 10→32、Max 50→35</t>
-  </si>
-  <si>
-    <t>建議降低：Min 5→2、Max 10→3</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→5、Max 10→7</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 3 / Max 4</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 6 / Max 9</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→39、Max 2→40</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→4、Max 3→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→5、Max 4→7</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→5、Max 2→7</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→12、Max 2→13</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→4、Max 4→6</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→8、Max 12→11</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→17、Max 1→19</t>
+    <t>建議提高：Min 0→1、Max 1→3</t>
   </si>
   <si>
     <t>decrease</t>
@@ -6780,13 +6777,13 @@
         <v>1792</v>
       </c>
       <c r="R2">
-        <v>1.64</v>
+        <v>0.32</v>
       </c>
       <c r="S2">
         <v>0.32</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>0.32</v>
       </c>
       <c r="U2">
         <v>0.32</v>
@@ -6822,7 +6819,7 @@
         <v>1973</v>
       </c>
       <c r="AF2" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -6929,7 +6926,7 @@
         <v>1974</v>
       </c>
       <c r="AF3" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -7015,7 +7012,7 @@
         <v>2.5</v>
       </c>
       <c r="Z4" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA4">
         <v>2</v>
@@ -7033,7 +7030,7 @@
         <v>1975</v>
       </c>
       <c r="AF4" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG4" t="b">
         <v>1</v>
@@ -7116,7 +7113,7 @@
         <v>2.67</v>
       </c>
       <c r="Z5" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA5">
         <v>2</v>
@@ -7134,7 +7131,7 @@
         <v>1976</v>
       </c>
       <c r="AF5" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -7220,7 +7217,7 @@
         <v>2.81</v>
       </c>
       <c r="Z6" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA6">
         <v>2</v>
@@ -7238,7 +7235,7 @@
         <v>1977</v>
       </c>
       <c r="AF6" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -7339,7 +7336,7 @@
         <v>1975</v>
       </c>
       <c r="AF7" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG7" t="b">
         <v>1</v>
@@ -7422,7 +7419,7 @@
         <v>1978</v>
       </c>
       <c r="AF8" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG8" t="b">
         <v>1</v>
@@ -7505,7 +7502,7 @@
         <v>1978</v>
       </c>
       <c r="AF9" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG9" t="b">
         <v>1</v>
@@ -7588,7 +7585,7 @@
         <v>2.75</v>
       </c>
       <c r="Z10" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA10">
         <v>2</v>
@@ -7606,7 +7603,7 @@
         <v>1979</v>
       </c>
       <c r="AF10" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -7695,7 +7692,7 @@
         <v>2.25</v>
       </c>
       <c r="Z11" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA11">
         <v>2</v>
@@ -7713,7 +7710,7 @@
         <v>1974</v>
       </c>
       <c r="AF11" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -7799,13 +7796,13 @@
         <v>15.5</v>
       </c>
       <c r="Z12" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE12" t="s">
         <v>1978</v>
       </c>
       <c r="AF12" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG12" t="b">
         <v>1</v>
@@ -7894,7 +7891,7 @@
         <v>1975</v>
       </c>
       <c r="AF13" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG13" t="b">
         <v>1</v>
@@ -7974,7 +7971,7 @@
         <v>1978</v>
       </c>
       <c r="AF14" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG14" t="b">
         <v>1</v>
@@ -8069,7 +8066,7 @@
         <v>1975</v>
       </c>
       <c r="AF15" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG15" t="b">
         <v>1</v>
@@ -8170,7 +8167,7 @@
         <v>1980</v>
       </c>
       <c r="AF16" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -8256,7 +8253,7 @@
         <v>1978</v>
       </c>
       <c r="AF17" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG17" t="b">
         <v>1</v>
@@ -8339,7 +8336,7 @@
         <v>1978</v>
       </c>
       <c r="AF18" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG18" t="b">
         <v>1</v>
@@ -8422,7 +8419,7 @@
         <v>1.67</v>
       </c>
       <c r="Z19" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA19">
         <v>1</v>
@@ -8440,7 +8437,7 @@
         <v>1981</v>
       </c>
       <c r="AF19" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -8544,7 +8541,7 @@
         <v>1982</v>
       </c>
       <c r="AF20" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -8606,7 +8603,7 @@
         <v>1803</v>
       </c>
       <c r="R21">
-        <v>5.27</v>
+        <v>3.38</v>
       </c>
       <c r="S21">
         <v>1.13</v>
@@ -8639,25 +8636,25 @@
         <v>2</v>
       </c>
       <c r="AC21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="AF21" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21">
+        <v>2</v>
+      </c>
+      <c r="AI21">
         <v>3</v>
-      </c>
-      <c r="AI21">
-        <v>4</v>
       </c>
       <c r="AJ21">
         <v>1</v>
@@ -8725,7 +8722,7 @@
         <v>1978</v>
       </c>
       <c r="AF22" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG22" t="b">
         <v>1</v>
@@ -8805,7 +8802,7 @@
         <v>2.2</v>
       </c>
       <c r="Z23" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA23">
         <v>1</v>
@@ -8820,10 +8817,10 @@
         <v>4</v>
       </c>
       <c r="AE23" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="AF23" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -8924,10 +8921,10 @@
         <v>3</v>
       </c>
       <c r="AE24" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AF24" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -9028,10 +9025,10 @@
         <v>4</v>
       </c>
       <c r="AE25" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="AF25" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -9093,13 +9090,13 @@
         <v>1807</v>
       </c>
       <c r="R26">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="S26">
         <v>0.49</v>
       </c>
       <c r="T26">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="U26">
         <v>0.33</v>
@@ -9117,7 +9114,7 @@
         <v>2</v>
       </c>
       <c r="Z26" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA26">
         <v>1</v>
@@ -9132,10 +9129,10 @@
         <v>3</v>
       </c>
       <c r="AE26" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="AF26" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -9197,13 +9194,13 @@
         <v>1760</v>
       </c>
       <c r="R27">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="S27">
         <v>0.52</v>
       </c>
       <c r="T27">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="U27">
         <v>0.35</v>
@@ -9221,7 +9218,7 @@
         <v>4</v>
       </c>
       <c r="Z27" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA27">
         <v>2</v>
@@ -9236,10 +9233,10 @@
         <v>3</v>
       </c>
       <c r="AE27" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="AF27" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -9325,7 +9322,7 @@
         <v>2.17</v>
       </c>
       <c r="Z28" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA28">
         <v>0</v>
@@ -9340,10 +9337,10 @@
         <v>5</v>
       </c>
       <c r="AE28" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AF28" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -9405,13 +9402,13 @@
         <v>1777</v>
       </c>
       <c r="R29">
-        <v>1.63</v>
+        <v>0.4</v>
       </c>
       <c r="S29">
         <v>0.4</v>
       </c>
       <c r="T29">
-        <v>1.81</v>
+        <v>0.4</v>
       </c>
       <c r="U29">
         <v>0.4</v>
@@ -9438,13 +9435,13 @@
         <v>2</v>
       </c>
       <c r="AC29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="s">
-        <v>1990</v>
+        <v>1977</v>
       </c>
       <c r="AF29" t="s">
         <v>2078</v>
@@ -9453,10 +9450,10 @@
         <v>0</v>
       </c>
       <c r="AH29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
         <v>2</v>
@@ -9533,7 +9530,7 @@
         <v>2.12</v>
       </c>
       <c r="Z30" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA30">
         <v>0</v>
@@ -9548,10 +9545,10 @@
         <v>4</v>
       </c>
       <c r="AE30" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="AF30" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -9646,7 +9643,7 @@
         <v>1975</v>
       </c>
       <c r="AF31" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG31" t="b">
         <v>1</v>
@@ -9735,7 +9732,7 @@
         <v>1975</v>
       </c>
       <c r="AF32" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG32" t="b">
         <v>1</v>
@@ -9791,13 +9788,13 @@
         <v>1809</v>
       </c>
       <c r="R33">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="S33">
         <v>0.82</v>
       </c>
       <c r="T33">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="U33">
         <v>0.82</v>
@@ -9830,10 +9827,10 @@
         <v>3</v>
       </c>
       <c r="AE33" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="AF33" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -9892,13 +9889,13 @@
         <v>1810</v>
       </c>
       <c r="R34">
-        <v>0.47</v>
+        <v>0.64</v>
       </c>
       <c r="S34">
         <v>0.64</v>
       </c>
       <c r="T34">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="U34">
         <v>0.64</v>
@@ -9934,7 +9931,7 @@
         <v>1977</v>
       </c>
       <c r="AF34" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -10014,7 +10011,7 @@
         <v>3</v>
       </c>
       <c r="Z35" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA35">
         <v>1</v>
@@ -10032,7 +10029,7 @@
         <v>1975</v>
       </c>
       <c r="AF35" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG35" t="b">
         <v>1</v>
@@ -10127,7 +10124,7 @@
         <v>1975</v>
       </c>
       <c r="AF36" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG36" t="b">
         <v>1</v>
@@ -10207,7 +10204,7 @@
         <v>1.67</v>
       </c>
       <c r="Z37" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA37">
         <v>1</v>
@@ -10222,10 +10219,10 @@
         <v>3</v>
       </c>
       <c r="AE37" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AF37" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -10323,7 +10320,7 @@
         <v>1975</v>
       </c>
       <c r="AF38" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG38" t="b">
         <v>1</v>
@@ -10403,7 +10400,7 @@
         <v>4</v>
       </c>
       <c r="Z39" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA39">
         <v>0</v>
@@ -10418,10 +10415,10 @@
         <v>4</v>
       </c>
       <c r="AE39" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="AF39" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
@@ -10507,7 +10504,7 @@
         <v>12.83</v>
       </c>
       <c r="Z40" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA40">
         <v>3</v>
@@ -10522,10 +10519,10 @@
         <v>5</v>
       </c>
       <c r="AE40" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="AF40" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -10626,10 +10623,10 @@
         <v>3</v>
       </c>
       <c r="AE41" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="AF41" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -10730,10 +10727,10 @@
         <v>5</v>
       </c>
       <c r="AE42" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="AF42" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -10834,10 +10831,10 @@
         <v>10</v>
       </c>
       <c r="AE43" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="AF43" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -10923,7 +10920,7 @@
         <v>4.2</v>
       </c>
       <c r="Z44" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA44">
         <v>0</v>
@@ -10938,10 +10935,10 @@
         <v>5</v>
       </c>
       <c r="AE44" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="AF44" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -11024,7 +11021,7 @@
         <v>4</v>
       </c>
       <c r="Z45" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA45">
         <v>3</v>
@@ -11042,7 +11039,7 @@
         <v>1975</v>
       </c>
       <c r="AF45" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG45" t="b">
         <v>1</v>
@@ -11137,7 +11134,7 @@
         <v>1975</v>
       </c>
       <c r="AF46" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG46" t="b">
         <v>1</v>
@@ -11211,7 +11208,7 @@
         <v>5</v>
       </c>
       <c r="Z47" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA47">
         <v>3</v>
@@ -11229,7 +11226,7 @@
         <v>1975</v>
       </c>
       <c r="AF47" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG47" t="b">
         <v>1</v>
@@ -11321,7 +11318,7 @@
         <v>1975</v>
       </c>
       <c r="AF48" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG48" t="b">
         <v>1</v>
@@ -11416,7 +11413,7 @@
         <v>1975</v>
       </c>
       <c r="AF49" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG49" t="b">
         <v>1</v>
@@ -11505,10 +11502,10 @@
         <v>21</v>
       </c>
       <c r="AE50" t="s">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="AF50" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -11582,7 +11579,7 @@
         <v>5</v>
       </c>
       <c r="Z51" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA51">
         <v>1</v>
@@ -11600,7 +11597,7 @@
         <v>1975</v>
       </c>
       <c r="AF51" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG51" t="b">
         <v>1</v>
@@ -11677,7 +11674,7 @@
         <v>5</v>
       </c>
       <c r="Z52" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA52">
         <v>1</v>
@@ -11692,10 +11689,10 @@
         <v>3</v>
       </c>
       <c r="AE52" t="s">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="AF52" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
@@ -11778,7 +11775,7 @@
         <v>5</v>
       </c>
       <c r="Z53" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA53">
         <v>1</v>
@@ -11793,10 +11790,10 @@
         <v>4</v>
       </c>
       <c r="AE53" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="AF53" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG53" t="b">
         <v>0</v>
@@ -11897,10 +11894,10 @@
         <v>3</v>
       </c>
       <c r="AE54" t="s">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="AF54" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -11986,7 +11983,7 @@
         <v>3.2</v>
       </c>
       <c r="Z55" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA55">
         <v>1</v>
@@ -12001,10 +11998,10 @@
         <v>5</v>
       </c>
       <c r="AE55" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="AF55" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
@@ -12087,7 +12084,7 @@
         <v>5</v>
       </c>
       <c r="Z56" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA56">
         <v>1</v>
@@ -12102,10 +12099,10 @@
         <v>4</v>
       </c>
       <c r="AE56" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="AF56" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
@@ -12203,7 +12200,7 @@
         <v>1975</v>
       </c>
       <c r="AF57" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG57" t="b">
         <v>1</v>
@@ -12295,7 +12292,7 @@
         <v>1975</v>
       </c>
       <c r="AF58" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG58" t="b">
         <v>1</v>
@@ -12351,13 +12348,13 @@
         <v>1827</v>
       </c>
       <c r="R59">
-        <v>0.84</v>
+        <v>0.48</v>
       </c>
       <c r="S59">
         <v>0.48</v>
       </c>
       <c r="T59">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="U59">
         <v>0.48</v>
@@ -12390,10 +12387,10 @@
         <v>2</v>
       </c>
       <c r="AE59" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="AF59" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG59" t="b">
         <v>0</v>
@@ -12491,7 +12488,7 @@
         <v>1975</v>
       </c>
       <c r="AF60" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG60" t="b">
         <v>1</v>
@@ -12547,7 +12544,7 @@
         <v>1828</v>
       </c>
       <c r="R61">
-        <v>6.42</v>
+        <v>5.79</v>
       </c>
       <c r="S61">
         <v>1.93</v>
@@ -12571,7 +12568,7 @@
         <v>6</v>
       </c>
       <c r="Z61" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA61">
         <v>1</v>
@@ -12586,10 +12583,10 @@
         <v>5</v>
       </c>
       <c r="AE61" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="AF61" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG61" t="b">
         <v>0</v>
@@ -12651,13 +12648,13 @@
         <v>1829</v>
       </c>
       <c r="R62">
-        <v>1.24</v>
+        <v>0.32</v>
       </c>
       <c r="S62">
         <v>0.32</v>
       </c>
       <c r="T62">
-        <v>1.38</v>
+        <v>0.32</v>
       </c>
       <c r="U62">
         <v>0.32</v>
@@ -12675,7 +12672,7 @@
         <v>2</v>
       </c>
       <c r="Z62" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA62">
         <v>3</v>
@@ -12690,10 +12687,10 @@
         <v>2</v>
       </c>
       <c r="AE62" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="AF62" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG62" t="b">
         <v>0</v>
@@ -12779,7 +12776,7 @@
         <v>10</v>
       </c>
       <c r="Z63" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA63">
         <v>3</v>
@@ -12794,10 +12791,10 @@
         <v>6</v>
       </c>
       <c r="AE63" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="AF63" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG63" t="b">
         <v>0</v>
@@ -12895,7 +12892,7 @@
         <v>1975</v>
       </c>
       <c r="AF64" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG64" t="b">
         <v>1</v>
@@ -12987,7 +12984,7 @@
         <v>1975</v>
       </c>
       <c r="AF65" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG65" t="b">
         <v>1</v>
@@ -13043,7 +13040,7 @@
         <v>1831</v>
       </c>
       <c r="R66">
-        <v>11.38</v>
+        <v>6.92</v>
       </c>
       <c r="S66">
         <v>2.31</v>
@@ -13070,16 +13067,16 @@
         <v>1972</v>
       </c>
       <c r="AC66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD66">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE66" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="AF66" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG66" t="b">
         <v>0</v>
@@ -13135,7 +13132,7 @@
         <v>1832</v>
       </c>
       <c r="R67">
-        <v>30.15</v>
+        <v>4.94</v>
       </c>
       <c r="S67">
         <v>1.65</v>
@@ -13159,16 +13156,16 @@
         <v>1972</v>
       </c>
       <c r="AC67">
+        <v>1</v>
+      </c>
+      <c r="AD67">
         <v>3</v>
       </c>
-      <c r="AD67">
-        <v>5</v>
-      </c>
       <c r="AE67" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="AF67" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG67" t="b">
         <v>0</v>
@@ -13239,7 +13236,7 @@
         <v>1978</v>
       </c>
       <c r="AF68" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG68" t="b">
         <v>1</v>
@@ -13295,13 +13292,13 @@
         <v>1794</v>
       </c>
       <c r="R69">
-        <v>2.94</v>
+        <v>0.49</v>
       </c>
       <c r="S69">
         <v>0.49</v>
       </c>
       <c r="T69">
-        <v>3.27</v>
+        <v>0.49</v>
       </c>
       <c r="U69">
         <v>0.49</v>
@@ -13316,19 +13313,19 @@
         <v>10</v>
       </c>
       <c r="Z69" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AC69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE69" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="AF69" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG69" t="b">
         <v>0</v>
@@ -13384,7 +13381,7 @@
         <v>1833</v>
       </c>
       <c r="R70">
-        <v>11.55</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="S70">
         <v>3.21</v>
@@ -13411,16 +13408,16 @@
         <v>1972</v>
       </c>
       <c r="AC70">
+        <v>12</v>
+      </c>
+      <c r="AD70">
         <v>14</v>
       </c>
-      <c r="AD70">
-        <v>16</v>
-      </c>
       <c r="AE70" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="AF70" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG70" t="b">
         <v>0</v>
@@ -13476,13 +13473,13 @@
         <v>1834</v>
       </c>
       <c r="R71">
-        <v>1.8</v>
+        <v>0.34</v>
       </c>
       <c r="S71">
         <v>0.34</v>
       </c>
       <c r="T71">
-        <v>2.01</v>
+        <v>0.34</v>
       </c>
       <c r="U71">
         <v>0.34</v>
@@ -13500,16 +13497,16 @@
         <v>1968</v>
       </c>
       <c r="AC71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE71" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="AF71" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG71" t="b">
         <v>0</v>
@@ -13565,13 +13562,13 @@
         <v>1835</v>
       </c>
       <c r="R72">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="S72">
         <v>0.48</v>
       </c>
       <c r="T72">
-        <v>0.72</v>
+        <v>0.32</v>
       </c>
       <c r="U72">
         <v>0.32</v>
@@ -13586,7 +13583,7 @@
         <v>12</v>
       </c>
       <c r="Z72" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA72">
         <v>2</v>
@@ -13601,10 +13598,10 @@
         <v>3</v>
       </c>
       <c r="AE72" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="AF72" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG72" t="b">
         <v>0</v>
@@ -13702,7 +13699,7 @@
         <v>1975</v>
       </c>
       <c r="AF73" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG73" t="b">
         <v>1</v>
@@ -13794,7 +13791,7 @@
         <v>1975</v>
       </c>
       <c r="AF74" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG74" t="b">
         <v>1</v>
@@ -13886,7 +13883,7 @@
         <v>1975</v>
       </c>
       <c r="AF75" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG75" t="b">
         <v>1</v>
@@ -13978,7 +13975,7 @@
         <v>1975</v>
       </c>
       <c r="AF76" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG76" t="b">
         <v>1</v>
@@ -14034,13 +14031,13 @@
         <v>1836</v>
       </c>
       <c r="R77">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="S77">
         <v>0.32</v>
       </c>
       <c r="T77">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="U77">
         <v>0.32</v>
@@ -14058,7 +14055,7 @@
         <v>2.5</v>
       </c>
       <c r="Z77" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA77">
         <v>1</v>
@@ -14073,10 +14070,10 @@
         <v>2</v>
       </c>
       <c r="AE77" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="AF77" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -14177,10 +14174,10 @@
         <v>28</v>
       </c>
       <c r="AE78" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="AF78" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
@@ -14278,7 +14275,7 @@
         <v>1975</v>
       </c>
       <c r="AF79" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG79" t="b">
         <v>1</v>
@@ -14370,7 +14367,7 @@
         <v>1975</v>
       </c>
       <c r="AF80" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG80" t="b">
         <v>1</v>
@@ -14462,7 +14459,7 @@
         <v>1975</v>
       </c>
       <c r="AF81" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG81" t="b">
         <v>1</v>
@@ -14554,7 +14551,7 @@
         <v>1975</v>
       </c>
       <c r="AF82" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG82" t="b">
         <v>1</v>
@@ -14634,7 +14631,7 @@
         <v>2.14</v>
       </c>
       <c r="Z83" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC83">
         <v>4</v>
@@ -14643,10 +14640,10 @@
         <v>5</v>
       </c>
       <c r="AE83" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="AF83" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -14723,13 +14720,13 @@
         <v>1</v>
       </c>
       <c r="Z84" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE84" t="s">
         <v>1978</v>
       </c>
       <c r="AF84" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG84" t="b">
         <v>1</v>
@@ -14809,13 +14806,13 @@
         <v>1</v>
       </c>
       <c r="Z85" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE85" t="s">
         <v>1978</v>
       </c>
       <c r="AF85" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG85" t="b">
         <v>1</v>
@@ -14895,13 +14892,13 @@
         <v>2</v>
       </c>
       <c r="Z86" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE86" t="s">
         <v>1978</v>
       </c>
       <c r="AF86" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG86" t="b">
         <v>1</v>
@@ -14957,13 +14954,13 @@
         <v>1839</v>
       </c>
       <c r="R87">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="S87">
         <v>0.32</v>
       </c>
       <c r="T87">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="U87">
         <v>0.32</v>
@@ -14981,7 +14978,7 @@
         <v>1.5</v>
       </c>
       <c r="Z87" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AC87">
         <v>1</v>
@@ -14990,10 +14987,10 @@
         <v>2</v>
       </c>
       <c r="AE87" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="AF87" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG87" t="b">
         <v>0</v>
@@ -15076,7 +15073,7 @@
         <v>1978</v>
       </c>
       <c r="AF88" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG88" t="b">
         <v>1</v>
@@ -15150,13 +15147,13 @@
         <v>2</v>
       </c>
       <c r="Z89" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE89" t="s">
         <v>1978</v>
       </c>
       <c r="AF89" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG89" t="b">
         <v>1</v>
@@ -15230,13 +15227,13 @@
         <v>2</v>
       </c>
       <c r="Z90" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE90" t="s">
         <v>1978</v>
       </c>
       <c r="AF90" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG90" t="b">
         <v>1</v>
@@ -15328,7 +15325,7 @@
         <v>1975</v>
       </c>
       <c r="AF91" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG91" t="b">
         <v>1</v>
@@ -15408,7 +15405,7 @@
         <v>2.5</v>
       </c>
       <c r="Z92" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA92">
         <v>1</v>
@@ -15423,10 +15420,10 @@
         <v>4</v>
       </c>
       <c r="AE92" t="s">
-        <v>1990</v>
+        <v>2011</v>
       </c>
       <c r="AF92" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -15521,7 +15518,7 @@
         <v>1975</v>
       </c>
       <c r="AF93" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG93" t="b">
         <v>1</v>
@@ -15610,7 +15607,7 @@
         <v>1975</v>
       </c>
       <c r="AF94" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG94" t="b">
         <v>1</v>
@@ -15705,7 +15702,7 @@
         <v>1975</v>
       </c>
       <c r="AF95" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG95" t="b">
         <v>1</v>
@@ -15764,7 +15761,7 @@
         <v>1841</v>
       </c>
       <c r="R96">
-        <v>2.96</v>
+        <v>1.93</v>
       </c>
       <c r="S96">
         <v>0.64</v>
@@ -15785,7 +15782,7 @@
         <v>6</v>
       </c>
       <c r="Z96" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA96">
         <v>2</v>
@@ -15794,25 +15791,25 @@
         <v>5</v>
       </c>
       <c r="AC96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE96" t="s">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="AF96" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AH96">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI96">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AJ96">
         <v>2</v>
@@ -15886,7 +15883,7 @@
         <v>5</v>
       </c>
       <c r="Z97" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA97">
         <v>2</v>
@@ -15904,7 +15901,7 @@
         <v>1975</v>
       </c>
       <c r="AF97" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG97" t="b">
         <v>1</v>
@@ -15963,7 +15960,7 @@
         <v>1758</v>
       </c>
       <c r="R98">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="S98">
         <v>0.64</v>
@@ -15987,7 +15984,7 @@
         <v>2</v>
       </c>
       <c r="Z98" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA98">
         <v>2</v>
@@ -16005,7 +16002,7 @@
         <v>2013</v>
       </c>
       <c r="AF98" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG98" t="b">
         <v>0</v>
@@ -16070,13 +16067,13 @@
         <v>1843</v>
       </c>
       <c r="R99">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="S99">
         <v>0.32</v>
       </c>
       <c r="T99">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="U99">
         <v>0.32</v>
@@ -16094,7 +16091,7 @@
         <v>1</v>
       </c>
       <c r="Z99" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA99">
         <v>2</v>
@@ -16109,10 +16106,10 @@
         <v>2</v>
       </c>
       <c r="AE99" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="AF99" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -16198,7 +16195,7 @@
         <v>5.67</v>
       </c>
       <c r="Z100" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA100">
         <v>2</v>
@@ -16213,10 +16210,10 @@
         <v>6</v>
       </c>
       <c r="AE100" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="AF100" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -16296,7 +16293,7 @@
         <v>6</v>
       </c>
       <c r="Z101" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA101">
         <v>2</v>
@@ -16314,7 +16311,7 @@
         <v>1975</v>
       </c>
       <c r="AF101" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG101" t="b">
         <v>1</v>
@@ -16373,13 +16370,13 @@
         <v>1846</v>
       </c>
       <c r="R102">
-        <v>0.78</v>
+        <v>0.32</v>
       </c>
       <c r="S102">
         <v>0.32</v>
       </c>
       <c r="T102">
-        <v>0.87</v>
+        <v>0.32</v>
       </c>
       <c r="U102">
         <v>0.32</v>
@@ -16394,7 +16391,7 @@
         <v>2</v>
       </c>
       <c r="Z102" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA102">
         <v>2</v>
@@ -16403,25 +16400,25 @@
         <v>5</v>
       </c>
       <c r="AC102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE102" t="s">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="AF102" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AH102">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI102">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AJ102">
         <v>0</v>
@@ -16513,7 +16510,7 @@
         <v>1975</v>
       </c>
       <c r="AF103" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG103" t="b">
         <v>1</v>
@@ -16608,7 +16605,7 @@
         <v>1975</v>
       </c>
       <c r="AF104" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG104" t="b">
         <v>1</v>
@@ -16703,7 +16700,7 @@
         <v>1975</v>
       </c>
       <c r="AF105" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG105" t="b">
         <v>1</v>
@@ -16762,13 +16759,13 @@
         <v>1847</v>
       </c>
       <c r="R106">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="S106">
         <v>0.48</v>
       </c>
       <c r="T106">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="U106">
         <v>0.48</v>
@@ -16804,7 +16801,7 @@
         <v>1977</v>
       </c>
       <c r="AF106" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG106" t="b">
         <v>0</v>
@@ -16869,13 +16866,13 @@
         <v>1848</v>
       </c>
       <c r="R107">
-        <v>3.24</v>
+        <v>0.48</v>
       </c>
       <c r="S107">
         <v>0.48</v>
       </c>
       <c r="T107">
-        <v>3.6</v>
+        <v>0.48</v>
       </c>
       <c r="U107">
         <v>0.48</v>
@@ -16890,7 +16887,7 @@
         <v>3</v>
       </c>
       <c r="Z107" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AA107">
         <v>2</v>
@@ -16899,25 +16896,25 @@
         <v>5</v>
       </c>
       <c r="AC107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE107" t="s">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="AF107" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AH107">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI107">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AJ107">
         <v>0</v>
@@ -16991,7 +16988,7 @@
         <v>1</v>
       </c>
       <c r="Z108" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA108">
         <v>0</v>
@@ -17009,7 +17006,7 @@
         <v>1975</v>
       </c>
       <c r="AF108" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG108" t="b">
         <v>1</v>
@@ -17065,13 +17062,13 @@
         <v>1849</v>
       </c>
       <c r="R109">
-        <v>23.46</v>
+        <v>0.32</v>
       </c>
       <c r="S109">
         <v>0.32</v>
       </c>
       <c r="T109">
-        <v>26.07</v>
+        <v>0.32</v>
       </c>
       <c r="U109">
         <v>0.32</v>
@@ -17086,7 +17083,7 @@
         <v>3</v>
       </c>
       <c r="Z109" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="AA109">
         <v>1</v>
@@ -17095,25 +17092,25 @@
         <v>5</v>
       </c>
       <c r="AC109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE109" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="AF109" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AH109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI109">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AJ109">
         <v>1</v>
@@ -17208,10 +17205,10 @@
         <v>4</v>
       </c>
       <c r="AE110" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="AF110" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -17315,10 +17312,10 @@
         <v>3</v>
       </c>
       <c r="AE111" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="AF111" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
@@ -17404,7 +17401,7 @@
         <v>2</v>
       </c>
       <c r="Z112" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA112">
         <v>1</v>
@@ -17422,7 +17419,7 @@
         <v>1975</v>
       </c>
       <c r="AF112" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG112" t="b">
         <v>1</v>
@@ -17517,7 +17514,7 @@
         <v>1975</v>
       </c>
       <c r="AF113" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG113" t="b">
         <v>1</v>
@@ -17612,7 +17609,7 @@
         <v>1975</v>
       </c>
       <c r="AF114" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG114" t="b">
         <v>1</v>
@@ -17686,7 +17683,7 @@
         <v>1</v>
       </c>
       <c r="Z115" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA115">
         <v>1</v>
@@ -17704,7 +17701,7 @@
         <v>1975</v>
       </c>
       <c r="AF115" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG115" t="b">
         <v>1</v>
@@ -17784,7 +17781,7 @@
         <v>1.89</v>
       </c>
       <c r="Z116" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA116">
         <v>1</v>
@@ -17799,10 +17796,10 @@
         <v>3</v>
       </c>
       <c r="AE116" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="AF116" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG116" t="b">
         <v>0</v>
@@ -17867,13 +17864,13 @@
         <v>1743</v>
       </c>
       <c r="R117">
-        <v>1.43</v>
+        <v>0.48</v>
       </c>
       <c r="S117">
         <v>0.48</v>
       </c>
       <c r="T117">
-        <v>1.59</v>
+        <v>0.48</v>
       </c>
       <c r="U117">
         <v>0.48</v>
@@ -17891,7 +17888,7 @@
         <v>2</v>
       </c>
       <c r="Z117" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AA117">
         <v>1</v>
@@ -17900,25 +17897,25 @@
         <v>3</v>
       </c>
       <c r="AC117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE117" t="s">
         <v>2017</v>
       </c>
       <c r="AF117" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AH117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI117">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ117">
         <v>1</v>
@@ -17992,7 +17989,7 @@
         <v>1</v>
       </c>
       <c r="Z118" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA118">
         <v>0</v>
@@ -18010,7 +18007,7 @@
         <v>1975</v>
       </c>
       <c r="AF118" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG118" t="b">
         <v>1</v>
@@ -18069,13 +18066,13 @@
         <v>1724</v>
       </c>
       <c r="R119">
-        <v>1.12</v>
+        <v>0.32</v>
       </c>
       <c r="S119">
         <v>0.32</v>
       </c>
       <c r="T119">
-        <v>1.25</v>
+        <v>0.32</v>
       </c>
       <c r="U119">
         <v>0.32</v>
@@ -18093,7 +18090,7 @@
         <v>2</v>
       </c>
       <c r="Z119" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA119">
         <v>1</v>
@@ -18102,25 +18099,25 @@
         <v>3</v>
       </c>
       <c r="AC119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE119" t="s">
         <v>2017</v>
       </c>
       <c r="AF119" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AH119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI119">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ119">
         <v>2</v>
@@ -18203,7 +18200,7 @@
         <v>1975</v>
       </c>
       <c r="AF120" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG120" t="b">
         <v>1</v>
@@ -18277,7 +18274,7 @@
         <v>1</v>
       </c>
       <c r="Z121" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA121">
         <v>0</v>
@@ -18295,7 +18292,7 @@
         <v>1975</v>
       </c>
       <c r="AF121" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG121" t="b">
         <v>1</v>
@@ -18375,7 +18372,7 @@
         <v>16.67</v>
       </c>
       <c r="Z122" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA122">
         <v>0</v>
@@ -18393,7 +18390,7 @@
         <v>2018</v>
       </c>
       <c r="AF122" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG122" t="b">
         <v>0</v>
@@ -18494,7 +18491,7 @@
         <v>2019</v>
       </c>
       <c r="AF123" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
@@ -18592,7 +18589,7 @@
         <v>1975</v>
       </c>
       <c r="AF124" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG124" t="b">
         <v>1</v>
@@ -18669,7 +18666,7 @@
         <v>2</v>
       </c>
       <c r="Z125" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA125">
         <v>1</v>
@@ -18687,7 +18684,7 @@
         <v>1975</v>
       </c>
       <c r="AF125" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG125" t="b">
         <v>1</v>
@@ -18773,7 +18770,7 @@
         <v>1975</v>
       </c>
       <c r="AF126" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG126" t="b">
         <v>1</v>
@@ -18865,7 +18862,7 @@
         <v>1975</v>
       </c>
       <c r="AF127" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG127" t="b">
         <v>1</v>
@@ -18927,7 +18924,7 @@
         <v>0.32</v>
       </c>
       <c r="T128">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="U128">
         <v>0.32</v>
@@ -18945,7 +18942,7 @@
         <v>1</v>
       </c>
       <c r="Z128" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA128">
         <v>1</v>
@@ -18963,7 +18960,7 @@
         <v>1977</v>
       </c>
       <c r="AF128" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -19067,10 +19064,10 @@
         <v>3</v>
       </c>
       <c r="AE129" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AF129" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
@@ -19162,7 +19159,7 @@
         <v>1975</v>
       </c>
       <c r="AF130" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG130" t="b">
         <v>1</v>
@@ -19254,7 +19251,7 @@
         <v>1975</v>
       </c>
       <c r="AF131" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG131" t="b">
         <v>1</v>
@@ -19334,7 +19331,7 @@
         <v>2.57</v>
       </c>
       <c r="Z132" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA132">
         <v>2</v>
@@ -19352,7 +19349,7 @@
         <v>1977</v>
       </c>
       <c r="AF132" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -19447,7 +19444,7 @@
         <v>1975</v>
       </c>
       <c r="AF133" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG133" t="b">
         <v>1</v>
@@ -19527,7 +19524,7 @@
         <v>15</v>
       </c>
       <c r="Z134" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC134">
         <v>5</v>
@@ -19539,7 +19536,7 @@
         <v>2020</v>
       </c>
       <c r="AF134" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
@@ -19610,7 +19607,7 @@
         <v>1978</v>
       </c>
       <c r="AF135" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG135" t="b">
         <v>1</v>
@@ -19696,10 +19693,10 @@
         <v>3</v>
       </c>
       <c r="AE136" t="s">
-        <v>2008</v>
+        <v>2021</v>
       </c>
       <c r="AF136" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG136" t="b">
         <v>0</v>
@@ -19770,7 +19767,7 @@
         <v>1978</v>
       </c>
       <c r="AF137" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG137" t="b">
         <v>1</v>
@@ -19826,13 +19823,13 @@
         <v>1861</v>
       </c>
       <c r="R138">
-        <v>4.11</v>
+        <v>1.59</v>
       </c>
       <c r="S138">
         <v>1.59</v>
       </c>
       <c r="T138">
-        <v>4.56</v>
+        <v>1.06</v>
       </c>
       <c r="U138">
         <v>1.06</v>
@@ -19850,19 +19847,19 @@
         <v>2</v>
       </c>
       <c r="Z138" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="AC138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE138" t="s">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="AF138" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG138" t="b">
         <v>0</v>
@@ -19957,7 +19954,7 @@
         <v>2022</v>
       </c>
       <c r="AF139" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG139" t="b">
         <v>0</v>
@@ -20052,10 +20049,10 @@
         <v>3</v>
       </c>
       <c r="AE140" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="AF140" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG140" t="b">
         <v>0</v>
@@ -20141,7 +20138,7 @@
         <v>2.25</v>
       </c>
       <c r="Z141" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA141">
         <v>1</v>
@@ -20156,10 +20153,10 @@
         <v>4</v>
       </c>
       <c r="AE141" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="AF141" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
@@ -20248,7 +20245,7 @@
         <v>3.86</v>
       </c>
       <c r="Z142" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC142">
         <v>6</v>
@@ -20260,7 +20257,7 @@
         <v>2022</v>
       </c>
       <c r="AF142" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
@@ -20349,10 +20346,10 @@
         <v>3</v>
       </c>
       <c r="AE143" t="s">
-        <v>2008</v>
+        <v>2021</v>
       </c>
       <c r="AF143" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -20408,7 +20405,7 @@
         <v>1724</v>
       </c>
       <c r="R144">
-        <v>9.69</v>
+        <v>4.16</v>
       </c>
       <c r="S144">
         <v>1.39</v>
@@ -20432,19 +20429,19 @@
         <v>3</v>
       </c>
       <c r="Z144" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC144">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AD144">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AE144" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="AF144" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -20533,10 +20530,10 @@
         <v>3</v>
       </c>
       <c r="AE145" t="s">
-        <v>2024</v>
+        <v>2006</v>
       </c>
       <c r="AF145" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -20628,7 +20625,7 @@
         <v>1975</v>
       </c>
       <c r="AF146" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG146" t="b">
         <v>1</v>
@@ -20708,7 +20705,7 @@
         <v>3</v>
       </c>
       <c r="Z147" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA147">
         <v>1</v>
@@ -20723,10 +20720,10 @@
         <v>4</v>
       </c>
       <c r="AE147" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="AF147" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -20827,10 +20824,10 @@
         <v>3</v>
       </c>
       <c r="AE148" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="AF148" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -20892,13 +20889,13 @@
         <v>1755</v>
       </c>
       <c r="R149">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="S149">
         <v>0.31</v>
       </c>
       <c r="T149">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="U149">
         <v>0.31</v>
@@ -20916,7 +20913,7 @@
         <v>1.33</v>
       </c>
       <c r="Z149" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA149">
         <v>0</v>
@@ -20931,10 +20928,10 @@
         <v>2</v>
       </c>
       <c r="AE149" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="AF149" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -20996,13 +20993,13 @@
         <v>1755</v>
       </c>
       <c r="R150">
-        <v>1.86</v>
+        <v>0.42</v>
       </c>
       <c r="S150">
         <v>0.42</v>
       </c>
       <c r="T150">
-        <v>2.06</v>
+        <v>0.42</v>
       </c>
       <c r="U150">
         <v>0.42</v>
@@ -21020,7 +21017,7 @@
         <v>2</v>
       </c>
       <c r="Z150" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AA150">
         <v>0</v>
@@ -21029,25 +21026,25 @@
         <v>1</v>
       </c>
       <c r="AC150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD150">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE150" t="s">
-        <v>1991</v>
+        <v>2023</v>
       </c>
       <c r="AF150" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AH150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ150">
         <v>2</v>
@@ -21121,7 +21118,7 @@
         <v>1</v>
       </c>
       <c r="Z151" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA151">
         <v>0</v>
@@ -21139,7 +21136,7 @@
         <v>1975</v>
       </c>
       <c r="AF151" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG151" t="b">
         <v>1</v>
@@ -21222,7 +21219,7 @@
         <v>1975</v>
       </c>
       <c r="AF152" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG152" t="b">
         <v>1</v>
@@ -21296,7 +21293,7 @@
         <v>10</v>
       </c>
       <c r="Z153" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA153">
         <v>2</v>
@@ -21314,7 +21311,7 @@
         <v>1975</v>
       </c>
       <c r="AF153" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG153" t="b">
         <v>1</v>
@@ -21388,7 +21385,7 @@
         <v>2</v>
       </c>
       <c r="Z154" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA154">
         <v>1</v>
@@ -21406,7 +21403,7 @@
         <v>1975</v>
       </c>
       <c r="AF154" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG154" t="b">
         <v>1</v>
@@ -21480,13 +21477,13 @@
         <v>1</v>
       </c>
       <c r="Z155" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE155" t="s">
         <v>1978</v>
       </c>
       <c r="AF155" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG155" t="b">
         <v>1</v>
@@ -21542,13 +21539,13 @@
         <v>1869</v>
       </c>
       <c r="R156">
-        <v>2.62</v>
+        <v>1.06</v>
       </c>
       <c r="S156">
         <v>1.06</v>
       </c>
       <c r="T156">
-        <v>1.12</v>
+        <v>0.64</v>
       </c>
       <c r="U156">
         <v>0.64</v>
@@ -21575,25 +21572,25 @@
         <v>2</v>
       </c>
       <c r="AC156">
+        <v>1</v>
+      </c>
+      <c r="AD156">
         <v>3</v>
       </c>
-      <c r="AD156">
-        <v>5</v>
-      </c>
       <c r="AE156" t="s">
-        <v>1989</v>
+        <v>2024</v>
       </c>
       <c r="AF156" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AH156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI156">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ156">
         <v>1</v>
@@ -21643,13 +21640,13 @@
         <v>1703</v>
       </c>
       <c r="R157">
-        <v>1.04</v>
+        <v>0.46</v>
       </c>
       <c r="S157">
         <v>0.46</v>
       </c>
       <c r="T157">
-        <v>1.16</v>
+        <v>0.46</v>
       </c>
       <c r="U157">
         <v>0.46</v>
@@ -21676,25 +21673,25 @@
         <v>3</v>
       </c>
       <c r="AC157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD157">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE157" t="s">
         <v>2017</v>
       </c>
       <c r="AF157" t="s">
-        <v>2078</v>
+        <v>2075</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AH157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI157">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ157">
         <v>5</v>
@@ -21783,7 +21780,7 @@
         <v>1975</v>
       </c>
       <c r="AF158" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG158" t="b">
         <v>1</v>
@@ -21875,7 +21872,7 @@
         <v>1975</v>
       </c>
       <c r="AF159" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG159" t="b">
         <v>1</v>
@@ -21949,7 +21946,7 @@
         <v>1</v>
       </c>
       <c r="Z160" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA160">
         <v>1</v>
@@ -21967,7 +21964,7 @@
         <v>1975</v>
       </c>
       <c r="AF160" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG160" t="b">
         <v>1</v>
@@ -22062,10 +22059,10 @@
         <v>3</v>
       </c>
       <c r="AE161" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AF161" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -22163,10 +22160,10 @@
         <v>3</v>
       </c>
       <c r="AE162" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AF162" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -22252,7 +22249,7 @@
         <v>2.2</v>
       </c>
       <c r="Z163" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA163">
         <v>1</v>
@@ -22267,10 +22264,10 @@
         <v>6</v>
       </c>
       <c r="AE163" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="AF163" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -22350,7 +22347,7 @@
         <v>1</v>
       </c>
       <c r="Z164" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA164">
         <v>1</v>
@@ -22368,7 +22365,7 @@
         <v>1975</v>
       </c>
       <c r="AF164" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG164" t="b">
         <v>1</v>
@@ -22460,7 +22457,7 @@
         <v>1975</v>
       </c>
       <c r="AF165" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG165" t="b">
         <v>1</v>
@@ -22513,13 +22510,13 @@
         <v>1874</v>
       </c>
       <c r="R166">
-        <v>5.13</v>
+        <v>0.98</v>
       </c>
       <c r="S166">
         <v>0.98</v>
       </c>
       <c r="T166">
-        <v>5.7</v>
+        <v>0.98</v>
       </c>
       <c r="U166">
         <v>0.98</v>
@@ -22534,7 +22531,7 @@
         <v>2</v>
       </c>
       <c r="Z166" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="AA166">
         <v>0</v>
@@ -22543,25 +22540,25 @@
         <v>2</v>
       </c>
       <c r="AC166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD166">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE166" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="AF166" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AH166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ166">
         <v>0</v>
@@ -22647,7 +22644,7 @@
         <v>1975</v>
       </c>
       <c r="AF167" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG167" t="b">
         <v>1</v>
@@ -22739,7 +22736,7 @@
         <v>1975</v>
       </c>
       <c r="AF168" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG168" t="b">
         <v>1</v>
@@ -22795,13 +22792,13 @@
         <v>1871</v>
       </c>
       <c r="R169">
-        <v>0.83</v>
+        <v>1.76</v>
       </c>
       <c r="S169">
         <v>1.76</v>
       </c>
       <c r="T169">
-        <v>0.93</v>
+        <v>1.76</v>
       </c>
       <c r="U169">
         <v>1.76</v>
@@ -22819,7 +22816,7 @@
         <v>1.25</v>
       </c>
       <c r="Z169" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="AA169">
         <v>0</v>
@@ -22828,25 +22825,25 @@
         <v>1</v>
       </c>
       <c r="AC169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE169" t="s">
-        <v>2025</v>
+        <v>1990</v>
       </c>
       <c r="AF169" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AH169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ169">
         <v>2</v>
@@ -22938,10 +22935,10 @@
         <v>4</v>
       </c>
       <c r="AE170" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="AF170" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
@@ -23030,7 +23027,7 @@
         <v>6.43</v>
       </c>
       <c r="Z171" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA171">
         <v>2</v>
@@ -23045,10 +23042,10 @@
         <v>9</v>
       </c>
       <c r="AE171" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="AF171" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -23137,7 +23134,7 @@
         <v>4</v>
       </c>
       <c r="Z172" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA172">
         <v>4</v>
@@ -23152,10 +23149,10 @@
         <v>6</v>
       </c>
       <c r="AE172" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="AF172" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -23259,10 +23256,10 @@
         <v>4</v>
       </c>
       <c r="AE173" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="AF173" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -23342,7 +23339,7 @@
         <v>2</v>
       </c>
       <c r="Z174" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA174">
         <v>1</v>
@@ -23360,7 +23357,7 @@
         <v>1975</v>
       </c>
       <c r="AF174" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG174" t="b">
         <v>1</v>
@@ -23458,7 +23455,7 @@
         <v>1982</v>
       </c>
       <c r="AF175" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG175" t="b">
         <v>0</v>
@@ -23541,7 +23538,7 @@
         <v>2</v>
       </c>
       <c r="Z176" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA176">
         <v>1</v>
@@ -23559,7 +23556,7 @@
         <v>1975</v>
       </c>
       <c r="AF176" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG176" t="b">
         <v>1</v>
@@ -23636,7 +23633,7 @@
         <v>4</v>
       </c>
       <c r="Z177" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA177">
         <v>2</v>
@@ -23654,7 +23651,7 @@
         <v>1975</v>
       </c>
       <c r="AF177" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG177" t="b">
         <v>1</v>
@@ -23737,7 +23734,7 @@
         <v>4.25</v>
       </c>
       <c r="Z178" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA178">
         <v>2</v>
@@ -23752,10 +23749,10 @@
         <v>8</v>
       </c>
       <c r="AE178" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="AF178" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG178" t="b">
         <v>0</v>
@@ -23859,10 +23856,10 @@
         <v>8</v>
       </c>
       <c r="AE179" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="AF179" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG179" t="b">
         <v>0</v>
@@ -23924,13 +23921,13 @@
         <v>1884</v>
       </c>
       <c r="R180">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="S180">
         <v>0.64</v>
       </c>
       <c r="T180">
-        <v>0.42</v>
+        <v>0.48</v>
       </c>
       <c r="U180">
         <v>0.48</v>
@@ -23963,10 +23960,10 @@
         <v>3</v>
       </c>
       <c r="AE180" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="AF180" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG180" t="b">
         <v>0</v>
@@ -24067,10 +24064,10 @@
         <v>5</v>
       </c>
       <c r="AE181" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="AF181" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -24159,7 +24156,7 @@
         <v>3.62</v>
       </c>
       <c r="Z182" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA182">
         <v>4</v>
@@ -24174,10 +24171,10 @@
         <v>8</v>
       </c>
       <c r="AE182" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="AF182" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -24281,7 +24278,7 @@
         <v>1977</v>
       </c>
       <c r="AF183" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -24370,7 +24367,7 @@
         <v>4.5</v>
       </c>
       <c r="Z184" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA184">
         <v>2</v>
@@ -24385,10 +24382,10 @@
         <v>9</v>
       </c>
       <c r="AE184" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="AF184" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG184" t="b">
         <v>0</v>
@@ -24477,7 +24474,7 @@
         <v>4.8</v>
       </c>
       <c r="Z185" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA185">
         <v>4</v>
@@ -24492,10 +24489,10 @@
         <v>7</v>
       </c>
       <c r="AE185" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="AF185" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -24581,7 +24578,7 @@
         <v>2</v>
       </c>
       <c r="Z186" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA186">
         <v>2</v>
@@ -24599,7 +24596,7 @@
         <v>1975</v>
       </c>
       <c r="AF186" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG186" t="b">
         <v>1</v>
@@ -24682,7 +24679,7 @@
         <v>4.5</v>
       </c>
       <c r="Z187" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA187">
         <v>2</v>
@@ -24697,10 +24694,10 @@
         <v>13</v>
       </c>
       <c r="AE187" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="AF187" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -24807,7 +24804,7 @@
         <v>1977</v>
       </c>
       <c r="AF188" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
@@ -24908,7 +24905,7 @@
         <v>1975</v>
       </c>
       <c r="AF189" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG189" t="b">
         <v>1</v>
@@ -24967,13 +24964,13 @@
         <v>1891</v>
       </c>
       <c r="R190">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="S190">
         <v>0.48</v>
       </c>
       <c r="T190">
-        <v>1.79</v>
+        <v>0.48</v>
       </c>
       <c r="U190">
         <v>0.48</v>
@@ -24991,7 +24988,7 @@
         <v>2</v>
       </c>
       <c r="Z190" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AA190">
         <v>4</v>
@@ -25000,25 +24997,25 @@
         <v>8</v>
       </c>
       <c r="AC190">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD190">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE190" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="AF190" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AH190">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AI190">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="AJ190">
         <v>1</v>
@@ -25098,7 +25095,7 @@
         <v>2.25</v>
       </c>
       <c r="Z191" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA191">
         <v>2</v>
@@ -25113,10 +25110,10 @@
         <v>5</v>
       </c>
       <c r="AE191" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="AF191" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
@@ -25199,7 +25196,7 @@
         <v>20</v>
       </c>
       <c r="Z192" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA192">
         <v>10</v>
@@ -25217,7 +25214,7 @@
         <v>1975</v>
       </c>
       <c r="AF192" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG192" t="b">
         <v>1</v>
@@ -25294,7 +25291,7 @@
         <v>4</v>
       </c>
       <c r="Z193" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA193">
         <v>2</v>
@@ -25312,7 +25309,7 @@
         <v>1975</v>
       </c>
       <c r="AF193" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG193" t="b">
         <v>1</v>
@@ -25407,7 +25404,7 @@
         <v>1975</v>
       </c>
       <c r="AF194" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG194" t="b">
         <v>1</v>
@@ -25466,13 +25463,13 @@
         <v>1774</v>
       </c>
       <c r="R195">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="S195">
         <v>0.64</v>
       </c>
       <c r="T195">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
       <c r="U195">
         <v>0.48</v>
@@ -25490,7 +25487,7 @@
         <v>2.33</v>
       </c>
       <c r="Z195" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA195">
         <v>2</v>
@@ -25505,10 +25502,10 @@
         <v>3</v>
       </c>
       <c r="AE195" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="AF195" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -25594,7 +25591,7 @@
         <v>2.44</v>
       </c>
       <c r="Z196" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA196">
         <v>2</v>
@@ -25609,10 +25606,10 @@
         <v>5</v>
       </c>
       <c r="AE196" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="AF196" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG196" t="b">
         <v>0</v>
@@ -25713,10 +25710,10 @@
         <v>5</v>
       </c>
       <c r="AE197" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AF197" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -25802,7 +25799,7 @@
         <v>3.2</v>
       </c>
       <c r="Z198" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA198">
         <v>0</v>
@@ -25817,10 +25814,10 @@
         <v>9</v>
       </c>
       <c r="AE198" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="AF198" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG198" t="b">
         <v>0</v>
@@ -25918,7 +25915,7 @@
         <v>1975</v>
       </c>
       <c r="AF199" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG199" t="b">
         <v>1</v>
@@ -25974,13 +25971,13 @@
         <v>1898</v>
       </c>
       <c r="R200">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="S200">
         <v>0.91</v>
       </c>
       <c r="T200">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="U200">
         <v>0.45</v>
@@ -26007,25 +26004,25 @@
         <v>4</v>
       </c>
       <c r="AC200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD200">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE200" t="s">
-        <v>1988</v>
+        <v>1977</v>
       </c>
       <c r="AF200" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AH200">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI200">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ200">
         <v>4</v>
@@ -26117,10 +26114,10 @@
         <v>4</v>
       </c>
       <c r="AE201" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="AF201" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -26218,7 +26215,7 @@
         <v>1975</v>
       </c>
       <c r="AF202" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG202" t="b">
         <v>1</v>
@@ -26304,7 +26301,7 @@
         <v>1975</v>
       </c>
       <c r="AF203" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG203" t="b">
         <v>1</v>
@@ -26396,7 +26393,7 @@
         <v>1975</v>
       </c>
       <c r="AF204" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG204" t="b">
         <v>1</v>
@@ -26491,7 +26488,7 @@
         <v>1975</v>
       </c>
       <c r="AF205" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG205" t="b">
         <v>1</v>
@@ -26547,13 +26544,13 @@
         <v>1900</v>
       </c>
       <c r="R206">
-        <v>0.43</v>
+        <v>0.8</v>
       </c>
       <c r="S206">
         <v>0.8</v>
       </c>
       <c r="T206">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="U206">
         <v>0.48</v>
@@ -26577,25 +26574,25 @@
         <v>4</v>
       </c>
       <c r="AC206">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD206">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE206" t="s">
-        <v>1988</v>
+        <v>1977</v>
       </c>
       <c r="AF206" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
       </c>
       <c r="AH206">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AI206">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AJ206">
         <v>0</v>
@@ -26651,7 +26648,7 @@
         <v>1901</v>
       </c>
       <c r="R207">
-        <v>25.56</v>
+        <v>20.76</v>
       </c>
       <c r="S207">
         <v>6.92</v>
@@ -26684,25 +26681,25 @@
         <v>8</v>
       </c>
       <c r="AC207">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AD207">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="AE207" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="AF207" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AH207">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AI207">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AJ207">
         <v>2</v>
@@ -26755,13 +26752,13 @@
         <v>1902</v>
       </c>
       <c r="R208">
-        <v>1.37</v>
+        <v>0.48</v>
       </c>
       <c r="S208">
         <v>0.48</v>
       </c>
       <c r="T208">
-        <v>1.52</v>
+        <v>0.48</v>
       </c>
       <c r="U208">
         <v>0.48</v>
@@ -26776,7 +26773,7 @@
         <v>5</v>
       </c>
       <c r="Z208" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AA208">
         <v>2</v>
@@ -26785,25 +26782,25 @@
         <v>5</v>
       </c>
       <c r="AC208">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD208">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE208" t="s">
-        <v>2001</v>
+        <v>2012</v>
       </c>
       <c r="AF208" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AH208">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI208">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AJ208">
         <v>2</v>
@@ -26892,7 +26889,7 @@
         <v>1975</v>
       </c>
       <c r="AF209" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG209" t="b">
         <v>1</v>
@@ -26966,7 +26963,7 @@
         <v>5</v>
       </c>
       <c r="Z210" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA210">
         <v>1</v>
@@ -26984,7 +26981,7 @@
         <v>1975</v>
       </c>
       <c r="AF210" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG210" t="b">
         <v>1</v>
@@ -27076,7 +27073,7 @@
         <v>1975</v>
       </c>
       <c r="AF211" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG211" t="b">
         <v>1</v>
@@ -27174,10 +27171,10 @@
         <v>4</v>
       </c>
       <c r="AE212" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="AF212" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -27263,7 +27260,7 @@
         <v>9.5</v>
       </c>
       <c r="Z213" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA213">
         <v>4</v>
@@ -27278,10 +27275,10 @@
         <v>5</v>
       </c>
       <c r="AE213" t="s">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="AF213" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG213" t="b">
         <v>0</v>
@@ -27367,7 +27364,7 @@
         <v>7.4</v>
       </c>
       <c r="Z214" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA214">
         <v>4</v>
@@ -27382,10 +27379,10 @@
         <v>11</v>
       </c>
       <c r="AE214" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="AF214" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -27471,7 +27468,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z215" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA215">
         <v>4</v>
@@ -27486,10 +27483,10 @@
         <v>9</v>
       </c>
       <c r="AE215" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="AF215" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -27575,7 +27572,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z216" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA216">
         <v>4</v>
@@ -27590,10 +27587,10 @@
         <v>11</v>
       </c>
       <c r="AE216" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="AF216" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -27679,7 +27676,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z217" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA217">
         <v>4</v>
@@ -27694,10 +27691,10 @@
         <v>9</v>
       </c>
       <c r="AE217" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="AF217" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -27762,13 +27759,13 @@
         <v>1905</v>
       </c>
       <c r="R218">
-        <v>10.11</v>
+        <v>0.46</v>
       </c>
       <c r="S218">
         <v>0.46</v>
       </c>
       <c r="T218">
-        <v>5.62</v>
+        <v>0.31</v>
       </c>
       <c r="U218">
         <v>0.31</v>
@@ -27786,7 +27783,7 @@
         <v>2.5</v>
       </c>
       <c r="Z218" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="AA218">
         <v>4</v>
@@ -27801,10 +27798,10 @@
         <v>3</v>
       </c>
       <c r="AE218" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="AF218" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -27890,7 +27887,7 @@
         <v>10.67</v>
       </c>
       <c r="Z219" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA219">
         <v>4</v>
@@ -27905,10 +27902,10 @@
         <v>6</v>
       </c>
       <c r="AE219" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="AF219" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -28006,7 +28003,7 @@
         <v>1975</v>
       </c>
       <c r="AF220" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG220" t="b">
         <v>1</v>
@@ -28098,7 +28095,7 @@
         <v>1975</v>
       </c>
       <c r="AF221" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG221" t="b">
         <v>1</v>
@@ -28190,7 +28187,7 @@
         <v>1975</v>
       </c>
       <c r="AF222" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG222" t="b">
         <v>1</v>
@@ -28264,7 +28261,7 @@
         <v>3</v>
       </c>
       <c r="Z223" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA223">
         <v>1</v>
@@ -28282,7 +28279,7 @@
         <v>1975</v>
       </c>
       <c r="AF223" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG223" t="b">
         <v>1</v>
@@ -28368,7 +28365,7 @@
         <v>1975</v>
       </c>
       <c r="AF224" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG224" t="b">
         <v>1</v>
@@ -28463,10 +28460,10 @@
         <v>16</v>
       </c>
       <c r="AE225" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="AF225" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG225" t="b">
         <v>0</v>
@@ -28546,7 +28543,7 @@
         <v>2</v>
       </c>
       <c r="Z226" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA226">
         <v>4</v>
@@ -28564,7 +28561,7 @@
         <v>1975</v>
       </c>
       <c r="AF226" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG226" t="b">
         <v>1</v>
@@ -28656,7 +28653,7 @@
         <v>1975</v>
       </c>
       <c r="AF227" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG227" t="b">
         <v>1</v>
@@ -28748,7 +28745,7 @@
         <v>1975</v>
       </c>
       <c r="AF228" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG228" t="b">
         <v>1</v>
@@ -28840,7 +28837,7 @@
         <v>1975</v>
       </c>
       <c r="AF229" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG229" t="b">
         <v>1</v>
@@ -28896,13 +28893,13 @@
         <v>1909</v>
       </c>
       <c r="R230">
-        <v>39.5</v>
+        <v>1.45</v>
       </c>
       <c r="S230">
         <v>1.45</v>
       </c>
       <c r="T230">
-        <v>11.55</v>
+        <v>0.48</v>
       </c>
       <c r="U230">
         <v>0.48</v>
@@ -28917,7 +28914,7 @@
         <v>9</v>
       </c>
       <c r="Z230" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="AA230">
         <v>2</v>
@@ -28926,25 +28923,25 @@
         <v>10</v>
       </c>
       <c r="AC230">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD230">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE230" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="AF230" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
       </c>
       <c r="AH230">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="AI230">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="AJ230">
         <v>0</v>
@@ -29015,7 +29012,7 @@
         <v>2</v>
       </c>
       <c r="Z231" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA231">
         <v>1</v>
@@ -29033,7 +29030,7 @@
         <v>1975</v>
       </c>
       <c r="AF231" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG231" t="b">
         <v>1</v>
@@ -29107,7 +29104,7 @@
         <v>4</v>
       </c>
       <c r="Z232" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA232">
         <v>2</v>
@@ -29125,7 +29122,7 @@
         <v>1975</v>
       </c>
       <c r="AF232" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG232" t="b">
         <v>1</v>
@@ -29181,13 +29178,13 @@
         <v>1783</v>
       </c>
       <c r="R233">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S233">
         <v>0.8</v>
       </c>
       <c r="T233">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="U233">
         <v>0.48</v>
@@ -29220,10 +29217,10 @@
         <v>4</v>
       </c>
       <c r="AE233" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="AF233" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -29285,13 +29282,13 @@
         <v>1912</v>
       </c>
       <c r="R234">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="S234">
         <v>0.8</v>
       </c>
       <c r="T234">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="U234">
         <v>0.48</v>
@@ -29321,10 +29318,10 @@
         <v>4</v>
       </c>
       <c r="AE234" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="AF234" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG234" t="b">
         <v>0</v>
@@ -29422,7 +29419,7 @@
         <v>1975</v>
       </c>
       <c r="AF235" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG235" t="b">
         <v>1</v>
@@ -29514,7 +29511,7 @@
         <v>1975</v>
       </c>
       <c r="AF236" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG236" t="b">
         <v>1</v>
@@ -29588,7 +29585,7 @@
         <v>2</v>
       </c>
       <c r="Z237" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA237">
         <v>4</v>
@@ -29606,7 +29603,7 @@
         <v>1975</v>
       </c>
       <c r="AF237" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG237" t="b">
         <v>1</v>
@@ -29698,7 +29695,7 @@
         <v>1975</v>
       </c>
       <c r="AF238" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG238" t="b">
         <v>1</v>
@@ -29790,7 +29787,7 @@
         <v>1975</v>
       </c>
       <c r="AF239" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG239" t="b">
         <v>1</v>
@@ -29882,7 +29879,7 @@
         <v>1975</v>
       </c>
       <c r="AF240" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG240" t="b">
         <v>1</v>
@@ -29962,7 +29959,7 @@
         <v>4</v>
       </c>
       <c r="Z241" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC241">
         <v>2</v>
@@ -29971,10 +29968,10 @@
         <v>4</v>
       </c>
       <c r="AE241" t="s">
-        <v>2021</v>
+        <v>2005</v>
       </c>
       <c r="AF241" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -30048,13 +30045,13 @@
         <v>25</v>
       </c>
       <c r="Z242" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE242" t="s">
         <v>1978</v>
       </c>
       <c r="AF242" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG242" t="b">
         <v>1</v>
@@ -30128,13 +30125,13 @@
         <v>15</v>
       </c>
       <c r="Z243" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE243" t="s">
         <v>1978</v>
       </c>
       <c r="AF243" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG243" t="b">
         <v>1</v>
@@ -30208,7 +30205,7 @@
         <v>15</v>
       </c>
       <c r="Z244" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA244">
         <v>5</v>
@@ -30226,7 +30223,7 @@
         <v>1975</v>
       </c>
       <c r="AF244" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG244" t="b">
         <v>1</v>
@@ -30300,7 +30297,7 @@
         <v>5</v>
       </c>
       <c r="Z245" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA245">
         <v>1</v>
@@ -30318,7 +30315,7 @@
         <v>1975</v>
       </c>
       <c r="AF245" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG245" t="b">
         <v>1</v>
@@ -30413,10 +30410,10 @@
         <v>6</v>
       </c>
       <c r="AE246" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="AF246" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -30478,13 +30475,13 @@
         <v>1918</v>
       </c>
       <c r="R247">
-        <v>2.08</v>
+        <v>0.49</v>
       </c>
       <c r="S247">
         <v>0.49</v>
       </c>
       <c r="T247">
-        <v>2.31</v>
+        <v>0.49</v>
       </c>
       <c r="U247">
         <v>0.49</v>
@@ -30499,7 +30496,7 @@
         <v>4</v>
       </c>
       <c r="Z247" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AA247">
         <v>1</v>
@@ -30508,25 +30505,25 @@
         <v>4</v>
       </c>
       <c r="AC247">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE247" t="s">
-        <v>1980</v>
+        <v>2052</v>
       </c>
       <c r="AF247" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
       </c>
       <c r="AH247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI247">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AJ247">
         <v>2</v>
@@ -30615,7 +30612,7 @@
         <v>1975</v>
       </c>
       <c r="AF248" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG248" t="b">
         <v>1</v>
@@ -30686,7 +30683,7 @@
         <v>50</v>
       </c>
       <c r="Z249" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA249">
         <v>5</v>
@@ -30704,7 +30701,7 @@
         <v>1975</v>
       </c>
       <c r="AF249" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG249" t="b">
         <v>1</v>
@@ -30793,7 +30790,7 @@
         <v>1975</v>
       </c>
       <c r="AF250" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG250" t="b">
         <v>1</v>
@@ -30882,7 +30879,7 @@
         <v>1975</v>
       </c>
       <c r="AF251" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG251" t="b">
         <v>1</v>
@@ -30980,7 +30977,7 @@
         <v>2053</v>
       </c>
       <c r="AF252" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -31042,7 +31039,7 @@
         <v>1783</v>
       </c>
       <c r="R253">
-        <v>10.32</v>
+        <v>6.73</v>
       </c>
       <c r="S253">
         <v>2.24</v>
@@ -31075,25 +31072,25 @@
         <v>1</v>
       </c>
       <c r="AC253">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD253">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE253" t="s">
         <v>2054</v>
       </c>
       <c r="AF253" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
       <c r="AH253">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI253">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ253">
         <v>4</v>
@@ -31143,13 +31140,13 @@
         <v>1920</v>
       </c>
       <c r="R254">
-        <v>3.17</v>
+        <v>2.25</v>
       </c>
       <c r="S254">
         <v>2.25</v>
       </c>
       <c r="T254">
-        <v>2.93</v>
+        <v>1.69</v>
       </c>
       <c r="U254">
         <v>1.69</v>
@@ -31167,7 +31164,7 @@
         <v>2</v>
       </c>
       <c r="Z254" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA254">
         <v>0</v>
@@ -31176,25 +31173,25 @@
         <v>1</v>
       </c>
       <c r="AC254">
+        <v>3</v>
+      </c>
+      <c r="AD254">
         <v>5</v>
-      </c>
-      <c r="AD254">
-        <v>7</v>
       </c>
       <c r="AE254" t="s">
         <v>2055</v>
       </c>
       <c r="AF254" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
       </c>
       <c r="AH254">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI254">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ254">
         <v>0</v>
@@ -31283,7 +31280,7 @@
         <v>1975</v>
       </c>
       <c r="AF255" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG255" t="b">
         <v>1</v>
@@ -31360,7 +31357,7 @@
         <v>2</v>
       </c>
       <c r="Z256" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA256">
         <v>1</v>
@@ -31378,7 +31375,7 @@
         <v>1975</v>
       </c>
       <c r="AF256" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG256" t="b">
         <v>1</v>
@@ -31470,7 +31467,7 @@
         <v>1975</v>
       </c>
       <c r="AF257" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG257" t="b">
         <v>1</v>
@@ -31562,7 +31559,7 @@
         <v>1975</v>
       </c>
       <c r="AF258" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG258" t="b">
         <v>1</v>
@@ -31654,7 +31651,7 @@
         <v>1975</v>
       </c>
       <c r="AF259" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG259" t="b">
         <v>1</v>
@@ -31746,7 +31743,7 @@
         <v>1975</v>
       </c>
       <c r="AF260" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG260" t="b">
         <v>1</v>
@@ -31838,7 +31835,7 @@
         <v>1975</v>
       </c>
       <c r="AF261" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG261" t="b">
         <v>1</v>
@@ -31930,7 +31927,7 @@
         <v>1975</v>
       </c>
       <c r="AF262" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG262" t="b">
         <v>1</v>
@@ -32025,7 +32022,7 @@
         <v>1975</v>
       </c>
       <c r="AF263" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG263" t="b">
         <v>1</v>
@@ -32084,13 +32081,13 @@
         <v>1921</v>
       </c>
       <c r="R264">
-        <v>0.62</v>
+        <v>0.32</v>
       </c>
       <c r="S264">
         <v>0.32</v>
       </c>
       <c r="T264">
-        <v>0.6899999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="U264">
         <v>0.32</v>
@@ -32105,7 +32102,7 @@
         <v>5</v>
       </c>
       <c r="Z264" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA264">
         <v>2</v>
@@ -32120,10 +32117,10 @@
         <v>2</v>
       </c>
       <c r="AE264" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="AF264" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -32221,7 +32218,7 @@
         <v>1975</v>
       </c>
       <c r="AF265" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG265" t="b">
         <v>1</v>
@@ -32313,7 +32310,7 @@
         <v>1975</v>
       </c>
       <c r="AF266" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG266" t="b">
         <v>1</v>
@@ -32405,7 +32402,7 @@
         <v>1975</v>
       </c>
       <c r="AF267" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG267" t="b">
         <v>1</v>
@@ -32497,7 +32494,7 @@
         <v>1975</v>
       </c>
       <c r="AF268" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG268" t="b">
         <v>1</v>
@@ -32571,7 +32568,7 @@
         <v>1</v>
       </c>
       <c r="Z269" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA269">
         <v>0</v>
@@ -32589,7 +32586,7 @@
         <v>1975</v>
       </c>
       <c r="AF269" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG269" t="b">
         <v>1</v>
@@ -32675,7 +32672,7 @@
         <v>1975</v>
       </c>
       <c r="AF270" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG270" t="b">
         <v>1</v>
@@ -32755,7 +32752,7 @@
         <v>1978</v>
       </c>
       <c r="AF271" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG271" t="b">
         <v>1</v>
@@ -32829,13 +32826,13 @@
         <v>7</v>
       </c>
       <c r="Z272" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE272" t="s">
         <v>1978</v>
       </c>
       <c r="AF272" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG272" t="b">
         <v>1</v>
@@ -32930,10 +32927,10 @@
         <v>3</v>
       </c>
       <c r="AE273" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="AF273" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -33013,7 +33010,7 @@
         <v>5</v>
       </c>
       <c r="Z274" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA274">
         <v>2</v>
@@ -33031,7 +33028,7 @@
         <v>1975</v>
       </c>
       <c r="AF274" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG274" t="b">
         <v>1</v>
@@ -33114,7 +33111,7 @@
         <v>4</v>
       </c>
       <c r="Z275" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA275">
         <v>2</v>
@@ -33132,7 +33129,7 @@
         <v>2056</v>
       </c>
       <c r="AF275" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -33212,7 +33209,7 @@
         <v>12</v>
       </c>
       <c r="Z276" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA276">
         <v>2</v>
@@ -33230,7 +33227,7 @@
         <v>1975</v>
       </c>
       <c r="AF276" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG276" t="b">
         <v>1</v>
@@ -33325,7 +33322,7 @@
         <v>1975</v>
       </c>
       <c r="AF277" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG277" t="b">
         <v>1</v>
@@ -33417,7 +33414,7 @@
         <v>1975</v>
       </c>
       <c r="AF278" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG278" t="b">
         <v>1</v>
@@ -33473,13 +33470,13 @@
         <v>1924</v>
       </c>
       <c r="R279">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
       <c r="S279">
         <v>0.48</v>
       </c>
       <c r="T279">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="U279">
         <v>0.32</v>
@@ -33497,7 +33494,7 @@
         <v>3</v>
       </c>
       <c r="Z279" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA279">
         <v>2</v>
@@ -33515,7 +33512,7 @@
         <v>2057</v>
       </c>
       <c r="AF279" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -33613,7 +33610,7 @@
         <v>1975</v>
       </c>
       <c r="AF280" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG280" t="b">
         <v>1</v>
@@ -33696,7 +33693,7 @@
         <v>7</v>
       </c>
       <c r="Z281" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA281">
         <v>2</v>
@@ -33714,7 +33711,7 @@
         <v>1976</v>
       </c>
       <c r="AF281" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -33776,7 +33773,7 @@
         <v>1926</v>
       </c>
       <c r="R282">
-        <v>7.82</v>
+        <v>2.9</v>
       </c>
       <c r="S282">
         <v>0.97</v>
@@ -33806,25 +33803,25 @@
         <v>10</v>
       </c>
       <c r="AC282">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD282">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE282" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
       <c r="AF282" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
       </c>
       <c r="AH282">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI282">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="AJ282">
         <v>27</v>
@@ -33877,7 +33874,7 @@
         <v>1927</v>
       </c>
       <c r="R283">
-        <v>4.03</v>
+        <v>3.86</v>
       </c>
       <c r="S283">
         <v>1.29</v>
@@ -33898,7 +33895,7 @@
         <v>17</v>
       </c>
       <c r="Z283" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA283">
         <v>2</v>
@@ -33913,10 +33910,10 @@
         <v>4</v>
       </c>
       <c r="AE283" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="AF283" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
@@ -34002,7 +33999,7 @@
         <v>12.5</v>
       </c>
       <c r="Z284" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA284">
         <v>2</v>
@@ -34020,7 +34017,7 @@
         <v>2058</v>
       </c>
       <c r="AF284" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -34118,7 +34115,7 @@
         <v>1975</v>
       </c>
       <c r="AF285" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG285" t="b">
         <v>1</v>
@@ -34198,7 +34195,7 @@
         <v>27.75</v>
       </c>
       <c r="Z286" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA286">
         <v>2</v>
@@ -34216,7 +34213,7 @@
         <v>1976</v>
       </c>
       <c r="AF286" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -34278,13 +34275,13 @@
         <v>1705</v>
       </c>
       <c r="R287">
-        <v>1.37</v>
+        <v>0.64</v>
       </c>
       <c r="S287">
         <v>0.64</v>
       </c>
       <c r="T287">
-        <v>0.76</v>
+        <v>0.32</v>
       </c>
       <c r="U287">
         <v>0.32</v>
@@ -34302,7 +34299,7 @@
         <v>2.5</v>
       </c>
       <c r="Z287" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA287">
         <v>2</v>
@@ -34311,25 +34308,25 @@
         <v>8</v>
       </c>
       <c r="AC287">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD287">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE287" t="s">
-        <v>2031</v>
+        <v>2059</v>
       </c>
       <c r="AF287" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
       </c>
       <c r="AH287">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI287">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="AJ287">
         <v>1</v>
@@ -34382,13 +34379,13 @@
         <v>1831</v>
       </c>
       <c r="R288">
-        <v>3.47</v>
+        <v>1.29</v>
       </c>
       <c r="S288">
         <v>1.29</v>
       </c>
       <c r="T288">
-        <v>1.61</v>
+        <v>0.48</v>
       </c>
       <c r="U288">
         <v>0.48</v>
@@ -34406,7 +34403,7 @@
         <v>5</v>
       </c>
       <c r="Z288" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="AA288">
         <v>2</v>
@@ -34415,25 +34412,25 @@
         <v>8</v>
       </c>
       <c r="AC288">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD288">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE288" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="AF288" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
       </c>
       <c r="AH288">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI288">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AJ288">
         <v>2</v>
@@ -34507,7 +34504,7 @@
         <v>2.5</v>
       </c>
       <c r="Z289" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA289">
         <v>2</v>
@@ -34525,7 +34522,7 @@
         <v>1975</v>
       </c>
       <c r="AF289" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG289" t="b">
         <v>1</v>
@@ -34605,7 +34602,7 @@
         <v>10</v>
       </c>
       <c r="Z290" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA290">
         <v>2</v>
@@ -34620,10 +34617,10 @@
         <v>4</v>
       </c>
       <c r="AE290" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="AF290" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -34709,7 +34706,7 @@
         <v>8</v>
       </c>
       <c r="Z291" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA291">
         <v>2</v>
@@ -34724,10 +34721,10 @@
         <v>9</v>
       </c>
       <c r="AE291" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="AF291" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -34831,10 +34828,10 @@
         <v>35</v>
       </c>
       <c r="AE292" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="AF292" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -34935,10 +34932,10 @@
         <v>3</v>
       </c>
       <c r="AE293" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="AF293" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -35036,7 +35033,7 @@
         <v>1975</v>
       </c>
       <c r="AF294" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG294" t="b">
         <v>1</v>
@@ -35113,7 +35110,7 @@
         <v>2</v>
       </c>
       <c r="Z295" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA295">
         <v>1</v>
@@ -35131,7 +35128,7 @@
         <v>1975</v>
       </c>
       <c r="AF295" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG295" t="b">
         <v>1</v>
@@ -35208,7 +35205,7 @@
         <v>1.5</v>
       </c>
       <c r="Z296" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA296">
         <v>0</v>
@@ -35226,7 +35223,7 @@
         <v>1975</v>
       </c>
       <c r="AF296" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG296" t="b">
         <v>1</v>
@@ -35282,13 +35279,13 @@
         <v>1932</v>
       </c>
       <c r="R297">
-        <v>1.12</v>
+        <v>0.64</v>
       </c>
       <c r="S297">
         <v>0.64</v>
       </c>
       <c r="T297">
-        <v>0.6899999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="U297">
         <v>0.48</v>
@@ -35315,25 +35312,25 @@
         <v>10</v>
       </c>
       <c r="AC297">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD297">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE297" t="s">
-        <v>2051</v>
+        <v>2057</v>
       </c>
       <c r="AF297" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
       </c>
       <c r="AH297">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI297">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="AJ297">
         <v>9</v>
@@ -35422,7 +35419,7 @@
         <v>1975</v>
       </c>
       <c r="AF298" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG298" t="b">
         <v>1</v>
@@ -35505,7 +35502,7 @@
         <v>8.67</v>
       </c>
       <c r="Z299" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA299">
         <v>2</v>
@@ -35520,10 +35517,10 @@
         <v>7</v>
       </c>
       <c r="AE299" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="AF299" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -35621,7 +35618,7 @@
         <v>1975</v>
       </c>
       <c r="AF300" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG300" t="b">
         <v>1</v>
@@ -35677,13 +35674,13 @@
         <v>1933</v>
       </c>
       <c r="R301">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="S301">
         <v>0.32</v>
       </c>
       <c r="T301">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="U301">
         <v>0.32</v>
@@ -35701,7 +35698,7 @@
         <v>1.5</v>
       </c>
       <c r="Z301" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA301">
         <v>2</v>
@@ -35719,7 +35716,7 @@
         <v>1973</v>
       </c>
       <c r="AF301" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -35817,7 +35814,7 @@
         <v>1975</v>
       </c>
       <c r="AF302" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG302" t="b">
         <v>1</v>
@@ -35891,7 +35888,7 @@
         <v>2</v>
       </c>
       <c r="Z303" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA303">
         <v>2</v>
@@ -35909,7 +35906,7 @@
         <v>1975</v>
       </c>
       <c r="AF303" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG303" t="b">
         <v>1</v>
@@ -36001,7 +35998,7 @@
         <v>1975</v>
       </c>
       <c r="AF304" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG304" t="b">
         <v>1</v>
@@ -36075,13 +36072,13 @@
         <v>8</v>
       </c>
       <c r="Z305" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE305" t="s">
         <v>1978</v>
       </c>
       <c r="AF305" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG305" t="b">
         <v>1</v>
@@ -36137,13 +36134,13 @@
         <v>1934</v>
       </c>
       <c r="R306">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="S306">
         <v>0.32</v>
       </c>
       <c r="T306">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="U306">
         <v>0.32</v>
@@ -36158,7 +36155,7 @@
         <v>8</v>
       </c>
       <c r="Z306" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AC306">
         <v>1</v>
@@ -36167,10 +36164,10 @@
         <v>2</v>
       </c>
       <c r="AE306" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="AF306" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG306" t="b">
         <v>0</v>
@@ -36250,7 +36247,7 @@
         <v>3.12</v>
       </c>
       <c r="Z307" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC307">
         <v>6</v>
@@ -36262,7 +36259,7 @@
         <v>2022</v>
       </c>
       <c r="AF307" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -36342,7 +36339,7 @@
         <v>1978</v>
       </c>
       <c r="AF308" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG308" t="b">
         <v>1</v>
@@ -36422,7 +36419,7 @@
         <v>1978</v>
       </c>
       <c r="AF309" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG309" t="b">
         <v>1</v>
@@ -36505,7 +36502,7 @@
         <v>1.88</v>
       </c>
       <c r="Z310" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC310">
         <v>3</v>
@@ -36514,10 +36511,10 @@
         <v>4</v>
       </c>
       <c r="AE310" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="AF310" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -36597,7 +36594,7 @@
         <v>1.82</v>
       </c>
       <c r="Z311" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA311">
         <v>2</v>
@@ -36615,7 +36612,7 @@
         <v>1974</v>
       </c>
       <c r="AF311" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -36695,13 +36692,13 @@
         <v>1</v>
       </c>
       <c r="Z312" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE312" t="s">
         <v>1978</v>
       </c>
       <c r="AF312" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG312" t="b">
         <v>1</v>
@@ -36778,13 +36775,13 @@
         <v>1</v>
       </c>
       <c r="Z313" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE313" t="s">
         <v>1978</v>
       </c>
       <c r="AF313" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG313" t="b">
         <v>1</v>
@@ -36858,13 +36855,13 @@
         <v>2</v>
       </c>
       <c r="Z314" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE314" t="s">
         <v>1978</v>
       </c>
       <c r="AF314" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG314" t="b">
         <v>1</v>
@@ -36944,7 +36941,7 @@
         <v>1978</v>
       </c>
       <c r="AF315" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG315" t="b">
         <v>1</v>
@@ -37018,13 +37015,13 @@
         <v>4</v>
       </c>
       <c r="Z316" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE316" t="s">
         <v>1978</v>
       </c>
       <c r="AF316" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG316" t="b">
         <v>1</v>
@@ -37098,13 +37095,13 @@
         <v>4</v>
       </c>
       <c r="Z317" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE317" t="s">
         <v>1978</v>
       </c>
       <c r="AF317" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG317" t="b">
         <v>1</v>
@@ -37184,7 +37181,7 @@
         <v>1978</v>
       </c>
       <c r="AF318" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG318" t="b">
         <v>1</v>
@@ -37264,7 +37261,7 @@
         <v>6.33</v>
       </c>
       <c r="Z319" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AC319">
         <v>6</v>
@@ -37273,10 +37270,10 @@
         <v>9</v>
       </c>
       <c r="AE319" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="AF319" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -37329,13 +37326,13 @@
         <v>1940</v>
       </c>
       <c r="R320">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="S320">
         <v>0.34</v>
       </c>
       <c r="T320">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="U320">
         <v>0.34</v>
@@ -37353,7 +37350,7 @@
         <v>1</v>
       </c>
       <c r="Z320" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AC320">
         <v>1</v>
@@ -37362,10 +37359,10 @@
         <v>2</v>
       </c>
       <c r="AE320" t="s">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="AF320" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -37418,13 +37415,13 @@
         <v>1864</v>
       </c>
       <c r="R321">
-        <v>29.86</v>
+        <v>0.36</v>
       </c>
       <c r="S321">
         <v>0.36</v>
       </c>
       <c r="T321">
-        <v>33.18</v>
+        <v>0.36</v>
       </c>
       <c r="U321">
         <v>0.36</v>
@@ -37442,7 +37439,7 @@
         <v>1.5</v>
       </c>
       <c r="Z321" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="AA321">
         <v>0</v>
@@ -37451,25 +37448,25 @@
         <v>2</v>
       </c>
       <c r="AC321">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="AD321">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="AE321" t="s">
-        <v>2067</v>
+        <v>2026</v>
       </c>
       <c r="AF321" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
       </c>
       <c r="AH321">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="AI321">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AJ321">
         <v>1</v>
@@ -37522,13 +37519,13 @@
         <v>1783</v>
       </c>
       <c r="R322">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="S322">
         <v>0.36</v>
       </c>
       <c r="T322">
-        <v>0.53</v>
+        <v>0.36</v>
       </c>
       <c r="U322">
         <v>0.36</v>
@@ -37546,7 +37543,7 @@
         <v>3.5</v>
       </c>
       <c r="Z322" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="AA322">
         <v>1</v>
@@ -37564,7 +37561,7 @@
         <v>1977</v>
       </c>
       <c r="AF322" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -37662,7 +37659,7 @@
         <v>1975</v>
       </c>
       <c r="AF323" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG323" t="b">
         <v>1</v>
@@ -37757,7 +37754,7 @@
         <v>1975</v>
       </c>
       <c r="AF324" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG324" t="b">
         <v>1</v>
@@ -37855,7 +37852,7 @@
         <v>1982</v>
       </c>
       <c r="AF325" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG325" t="b">
         <v>0</v>
@@ -37953,7 +37950,7 @@
         <v>1975</v>
       </c>
       <c r="AF326" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG326" t="b">
         <v>1</v>
@@ -38036,7 +38033,7 @@
         <v>2.2</v>
       </c>
       <c r="Z327" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA327">
         <v>0</v>
@@ -38054,7 +38051,7 @@
         <v>2068</v>
       </c>
       <c r="AF327" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -38140,7 +38137,7 @@
         <v>4</v>
       </c>
       <c r="Z328" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA328">
         <v>2</v>
@@ -38158,7 +38155,7 @@
         <v>2069</v>
       </c>
       <c r="AF328" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -38247,7 +38244,7 @@
         <v>1.83</v>
       </c>
       <c r="Z329" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA329">
         <v>1</v>
@@ -38262,10 +38259,10 @@
         <v>4</v>
       </c>
       <c r="AE329" t="s">
-        <v>1990</v>
+        <v>2011</v>
       </c>
       <c r="AF329" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -38351,7 +38348,7 @@
         <v>8.25</v>
       </c>
       <c r="Z330" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA330">
         <v>1</v>
@@ -38369,7 +38366,7 @@
         <v>2070</v>
       </c>
       <c r="AF330" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG330" t="b">
         <v>0</v>
@@ -38428,7 +38425,7 @@
         <v>1943</v>
       </c>
       <c r="R331">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="S331">
         <v>0.6</v>
@@ -38452,7 +38449,7 @@
         <v>2.33</v>
       </c>
       <c r="Z331" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA331">
         <v>0</v>
@@ -38467,10 +38464,10 @@
         <v>5</v>
       </c>
       <c r="AE331" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="AF331" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG331" t="b">
         <v>0</v>
@@ -38559,7 +38556,7 @@
         <v>1975</v>
       </c>
       <c r="AF332" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG332" t="b">
         <v>1</v>
@@ -38651,7 +38648,7 @@
         <v>1975</v>
       </c>
       <c r="AF333" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG333" t="b">
         <v>1</v>
@@ -38743,7 +38740,7 @@
         <v>1975</v>
       </c>
       <c r="AF334" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG334" t="b">
         <v>1</v>
@@ -38835,7 +38832,7 @@
         <v>1975</v>
       </c>
       <c r="AF335" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG335" t="b">
         <v>1</v>
@@ -38924,7 +38921,7 @@
         <v>1975</v>
       </c>
       <c r="AF336" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG336" t="b">
         <v>1</v>
@@ -38998,7 +38995,7 @@
         <v>2</v>
       </c>
       <c r="Z337" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA337">
         <v>1</v>
@@ -39016,7 +39013,7 @@
         <v>1975</v>
       </c>
       <c r="AF337" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG337" t="b">
         <v>1</v>
@@ -39090,7 +39087,7 @@
         <v>5</v>
       </c>
       <c r="Z338" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA338">
         <v>2</v>
@@ -39108,7 +39105,7 @@
         <v>1975</v>
       </c>
       <c r="AF338" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG338" t="b">
         <v>1</v>
@@ -39197,7 +39194,7 @@
         <v>1975</v>
       </c>
       <c r="AF339" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG339" t="b">
         <v>1</v>
@@ -39268,7 +39265,7 @@
         <v>1</v>
       </c>
       <c r="Z340" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA340">
         <v>0</v>
@@ -39286,7 +39283,7 @@
         <v>1975</v>
       </c>
       <c r="AF340" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG340" t="b">
         <v>1</v>
@@ -39357,7 +39354,7 @@
         <v>1</v>
       </c>
       <c r="Z341" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA341">
         <v>1</v>
@@ -39375,7 +39372,7 @@
         <v>1975</v>
       </c>
       <c r="AF341" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG341" t="b">
         <v>1</v>
@@ -39446,7 +39443,7 @@
         <v>1</v>
       </c>
       <c r="Z342" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA342">
         <v>1</v>
@@ -39464,7 +39461,7 @@
         <v>1975</v>
       </c>
       <c r="AF342" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG342" t="b">
         <v>1</v>
@@ -39544,7 +39541,7 @@
         <v>1.8</v>
       </c>
       <c r="Z343" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA343">
         <v>0</v>
@@ -39559,10 +39556,10 @@
         <v>3</v>
       </c>
       <c r="AE343" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="AF343" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -39657,7 +39654,7 @@
         <v>1975</v>
       </c>
       <c r="AF344" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG344" t="b">
         <v>1</v>
@@ -39746,7 +39743,7 @@
         <v>1975</v>
       </c>
       <c r="AF345" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG345" t="b">
         <v>1</v>
@@ -39835,7 +39832,7 @@
         <v>1975</v>
       </c>
       <c r="AF346" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG346" t="b">
         <v>1</v>
@@ -39924,7 +39921,7 @@
         <v>1975</v>
       </c>
       <c r="AF347" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG347" t="b">
         <v>1</v>
@@ -40013,7 +40010,7 @@
         <v>1975</v>
       </c>
       <c r="AF348" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG348" t="b">
         <v>1</v>
@@ -40102,7 +40099,7 @@
         <v>1975</v>
       </c>
       <c r="AF349" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG349" t="b">
         <v>1</v>
@@ -40191,7 +40188,7 @@
         <v>1975</v>
       </c>
       <c r="AF350" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG350" t="b">
         <v>1</v>
@@ -40283,7 +40280,7 @@
         <v>1975</v>
       </c>
       <c r="AF351" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG351" t="b">
         <v>1</v>
@@ -40375,7 +40372,7 @@
         <v>1975</v>
       </c>
       <c r="AF352" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG352" t="b">
         <v>1</v>
@@ -40464,7 +40461,7 @@
         <v>1975</v>
       </c>
       <c r="AF353" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG353" t="b">
         <v>1</v>
@@ -40556,7 +40553,7 @@
         <v>1975</v>
       </c>
       <c r="AF354" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG354" t="b">
         <v>1</v>
@@ -40651,7 +40648,7 @@
         <v>1975</v>
       </c>
       <c r="AF355" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG355" t="b">
         <v>1</v>
@@ -40746,7 +40743,7 @@
         <v>1975</v>
       </c>
       <c r="AF356" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG356" t="b">
         <v>1</v>
@@ -40835,7 +40832,7 @@
         <v>1975</v>
       </c>
       <c r="AF357" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG357" t="b">
         <v>1</v>
@@ -40924,7 +40921,7 @@
         <v>1975</v>
       </c>
       <c r="AF358" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG358" t="b">
         <v>1</v>
@@ -41019,7 +41016,7 @@
         <v>2071</v>
       </c>
       <c r="AF359" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG359" t="b">
         <v>0</v>
@@ -41114,7 +41111,7 @@
         <v>1975</v>
       </c>
       <c r="AF360" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG360" t="b">
         <v>1</v>
@@ -41209,7 +41206,7 @@
         <v>1975</v>
       </c>
       <c r="AF361" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG361" t="b">
         <v>1</v>
@@ -41301,7 +41298,7 @@
         <v>1975</v>
       </c>
       <c r="AF362" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG362" t="b">
         <v>1</v>
@@ -41393,7 +41390,7 @@
         <v>1975</v>
       </c>
       <c r="AF363" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG363" t="b">
         <v>1</v>
@@ -41485,7 +41482,7 @@
         <v>1975</v>
       </c>
       <c r="AF364" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG364" t="b">
         <v>1</v>
@@ -41541,13 +41538,13 @@
         <v>1783</v>
       </c>
       <c r="R365">
-        <v>29.86</v>
+        <v>1.59</v>
       </c>
       <c r="S365">
         <v>1.59</v>
       </c>
       <c r="T365">
-        <v>33.18</v>
+        <v>1.59</v>
       </c>
       <c r="U365">
         <v>1.59</v>
@@ -41565,7 +41562,7 @@
         <v>2</v>
       </c>
       <c r="Z365" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="AA365">
         <v>1</v>
@@ -41574,13 +41571,13 @@
         <v>2</v>
       </c>
       <c r="AC365">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AD365">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AE365" t="s">
-        <v>2072</v>
+        <v>1977</v>
       </c>
       <c r="AF365" t="s">
         <v>2078</v>
@@ -41589,10 +41586,10 @@
         <v>0</v>
       </c>
       <c r="AH365">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI365">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ365">
         <v>6</v>
@@ -41684,7 +41681,7 @@
         <v>1975</v>
       </c>
       <c r="AF366" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG366" t="b">
         <v>1</v>
@@ -41776,7 +41773,7 @@
         <v>1975</v>
       </c>
       <c r="AF367" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG367" t="b">
         <v>1</v>
@@ -41868,7 +41865,7 @@
         <v>1975</v>
       </c>
       <c r="AF368" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG368" t="b">
         <v>1</v>
@@ -41960,7 +41957,7 @@
         <v>1975</v>
       </c>
       <c r="AF369" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG369" t="b">
         <v>1</v>
@@ -42052,7 +42049,7 @@
         <v>1975</v>
       </c>
       <c r="AF370" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG370" t="b">
         <v>1</v>
@@ -42105,13 +42102,13 @@
         <v>1925</v>
       </c>
       <c r="R371">
-        <v>4.94</v>
+        <v>3.31</v>
       </c>
       <c r="S371">
         <v>3.31</v>
       </c>
       <c r="T371">
-        <v>2.74</v>
+        <v>1.66</v>
       </c>
       <c r="U371">
         <v>1.66</v>
@@ -42129,7 +42126,7 @@
         <v>4</v>
       </c>
       <c r="Z371" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA371">
         <v>1</v>
@@ -42138,25 +42135,25 @@
         <v>4</v>
       </c>
       <c r="AC371">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD371">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE371" t="s">
-        <v>2073</v>
+        <v>1982</v>
       </c>
       <c r="AF371" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
       </c>
       <c r="AH371">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI371">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ371">
         <v>4</v>
@@ -42245,7 +42242,7 @@
         <v>1975</v>
       </c>
       <c r="AF372" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG372" t="b">
         <v>1</v>
@@ -42337,7 +42334,7 @@
         <v>1975</v>
       </c>
       <c r="AF373" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG373" t="b">
         <v>1</v>
@@ -42420,7 +42417,7 @@
         <v>1975</v>
       </c>
       <c r="AF374" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG374" t="b">
         <v>1</v>
@@ -42503,7 +42500,7 @@
         <v>1975</v>
       </c>
       <c r="AF375" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG375" t="b">
         <v>1</v>
@@ -42595,7 +42592,7 @@
         <v>1975</v>
       </c>
       <c r="AF376" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG376" t="b">
         <v>1</v>
@@ -42687,7 +42684,7 @@
         <v>1975</v>
       </c>
       <c r="AF377" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG377" t="b">
         <v>1</v>
@@ -42782,7 +42779,7 @@
         <v>1975</v>
       </c>
       <c r="AF378" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG378" t="b">
         <v>1</v>
@@ -42874,7 +42871,7 @@
         <v>1975</v>
       </c>
       <c r="AF379" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG379" t="b">
         <v>1</v>
@@ -42966,7 +42963,7 @@
         <v>1975</v>
       </c>
       <c r="AF380" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG380" t="b">
         <v>1</v>
@@ -43022,13 +43019,13 @@
         <v>1953</v>
       </c>
       <c r="R381">
-        <v>156.43</v>
+        <v>8.69</v>
       </c>
       <c r="S381">
         <v>8.69</v>
       </c>
       <c r="T381">
-        <v>86.90000000000001</v>
+        <v>3.26</v>
       </c>
       <c r="U381">
         <v>3.26</v>
@@ -43046,7 +43043,7 @@
         <v>8</v>
       </c>
       <c r="Z381" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="AA381">
         <v>2</v>
@@ -43055,25 +43052,25 @@
         <v>12</v>
       </c>
       <c r="AC381">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AD381">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AE381" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="AF381" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
       </c>
       <c r="AH381">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="AI381">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="AJ381">
         <v>8</v>
@@ -43153,7 +43150,7 @@
         <v>1975</v>
       </c>
       <c r="AF382" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG382" t="b">
         <v>1</v>
@@ -43236,7 +43233,7 @@
         <v>1975</v>
       </c>
       <c r="AF383" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG383" t="b">
         <v>1</v>
@@ -43325,7 +43322,7 @@
         <v>1975</v>
       </c>
       <c r="AF384" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG384" t="b">
         <v>1</v>
@@ -43414,7 +43411,7 @@
         <v>1975</v>
       </c>
       <c r="AF385" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG385" t="b">
         <v>1</v>
@@ -43503,7 +43500,7 @@
         <v>1975</v>
       </c>
       <c r="AF386" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG386" t="b">
         <v>1</v>
@@ -43595,7 +43592,7 @@
         <v>1975</v>
       </c>
       <c r="AF387" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG387" t="b">
         <v>1</v>
@@ -43651,7 +43648,7 @@
         <v>1954</v>
       </c>
       <c r="R388">
-        <v>23.22</v>
+        <v>18.43</v>
       </c>
       <c r="S388">
         <v>6.14</v>
@@ -43684,25 +43681,25 @@
         <v>2</v>
       </c>
       <c r="AC388">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD388">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE388" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="AF388" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
       </c>
       <c r="AH388">
+        <v>3</v>
+      </c>
+      <c r="AI388">
         <v>4</v>
-      </c>
-      <c r="AI388">
-        <v>5</v>
       </c>
       <c r="AJ388">
         <v>3</v>
@@ -43794,7 +43791,7 @@
         <v>1975</v>
       </c>
       <c r="AF389" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG389" t="b">
         <v>1</v>
@@ -43871,7 +43868,7 @@
         <v>2</v>
       </c>
       <c r="Z390" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA390">
         <v>1</v>
@@ -43889,7 +43886,7 @@
         <v>1975</v>
       </c>
       <c r="AF390" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG390" t="b">
         <v>1</v>
@@ -43981,7 +43978,7 @@
         <v>1975</v>
       </c>
       <c r="AF391" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG391" t="b">
         <v>1</v>
@@ -44037,13 +44034,13 @@
         <v>1955</v>
       </c>
       <c r="R392">
-        <v>2.99</v>
+        <v>3.63</v>
       </c>
       <c r="S392">
         <v>3.63</v>
       </c>
       <c r="T392">
-        <v>3.32</v>
+        <v>3.63</v>
       </c>
       <c r="U392">
         <v>3.63</v>
@@ -44061,7 +44058,7 @@
         <v>1.5</v>
       </c>
       <c r="Z392" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA392">
         <v>1</v>
@@ -44076,10 +44073,10 @@
         <v>3</v>
       </c>
       <c r="AE392" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="AF392" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
@@ -44177,7 +44174,7 @@
         <v>1975</v>
       </c>
       <c r="AF393" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG393" t="b">
         <v>1</v>
@@ -44269,7 +44266,7 @@
         <v>1975</v>
       </c>
       <c r="AF394" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG394" t="b">
         <v>1</v>
@@ -44343,7 +44340,7 @@
         <v>2</v>
       </c>
       <c r="Z395" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA395">
         <v>1</v>
@@ -44361,7 +44358,7 @@
         <v>1975</v>
       </c>
       <c r="AF395" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG395" t="b">
         <v>1</v>
@@ -44435,7 +44432,7 @@
         <v>1</v>
       </c>
       <c r="Z396" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA396">
         <v>1</v>
@@ -44453,7 +44450,7 @@
         <v>1975</v>
       </c>
       <c r="AF396" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG396" t="b">
         <v>1</v>
@@ -44542,7 +44539,7 @@
         <v>1975</v>
       </c>
       <c r="AF397" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG397" t="b">
         <v>1</v>
@@ -44631,7 +44628,7 @@
         <v>1975</v>
       </c>
       <c r="AF398" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG398" t="b">
         <v>1</v>
@@ -44720,7 +44717,7 @@
         <v>1975</v>
       </c>
       <c r="AF399" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG399" t="b">
         <v>1</v>
@@ -44809,7 +44806,7 @@
         <v>1975</v>
       </c>
       <c r="AF400" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG400" t="b">
         <v>1</v>
@@ -44862,13 +44859,13 @@
         <v>1956</v>
       </c>
       <c r="R401">
-        <v>10.95</v>
+        <v>15.87</v>
       </c>
       <c r="S401">
         <v>15.87</v>
       </c>
       <c r="T401">
-        <v>12.17</v>
+        <v>15.87</v>
       </c>
       <c r="U401">
         <v>15.87</v>
@@ -44904,7 +44901,7 @@
         <v>1975</v>
       </c>
       <c r="AF401" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG401" t="b">
         <v>1</v>
@@ -44996,7 +44993,7 @@
         <v>1975</v>
       </c>
       <c r="AF402" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG402" t="b">
         <v>1</v>
@@ -45079,7 +45076,7 @@
         <v>1975</v>
       </c>
       <c r="AF403" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG403" t="b">
         <v>1</v>
@@ -45168,7 +45165,7 @@
         <v>1975</v>
       </c>
       <c r="AF404" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG404" t="b">
         <v>1</v>
@@ -45260,7 +45257,7 @@
         <v>1975</v>
       </c>
       <c r="AF405" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG405" t="b">
         <v>1</v>
@@ -45334,7 +45331,7 @@
         <v>13</v>
       </c>
       <c r="Z406" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA406">
         <v>2</v>
@@ -45352,7 +45349,7 @@
         <v>1975</v>
       </c>
       <c r="AF406" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG406" t="b">
         <v>1</v>
@@ -45444,7 +45441,7 @@
         <v>1975</v>
       </c>
       <c r="AF407" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG407" t="b">
         <v>1</v>
@@ -45536,7 +45533,7 @@
         <v>1975</v>
       </c>
       <c r="AF408" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG408" t="b">
         <v>1</v>
@@ -45628,7 +45625,7 @@
         <v>1975</v>
       </c>
       <c r="AF409" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG409" t="b">
         <v>1</v>
@@ -45702,7 +45699,7 @@
         <v>33</v>
       </c>
       <c r="Z410" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA410">
         <v>4</v>
@@ -45720,7 +45717,7 @@
         <v>1975</v>
       </c>
       <c r="AF410" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG410" t="b">
         <v>1</v>
@@ -45812,7 +45809,7 @@
         <v>1975</v>
       </c>
       <c r="AF411" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG411" t="b">
         <v>1</v>
@@ -45901,10 +45898,10 @@
         <v>3</v>
       </c>
       <c r="AE412" t="s">
-        <v>2008</v>
+        <v>2021</v>
       </c>
       <c r="AF412" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="AG412" t="b">
         <v>0</v>
@@ -45981,7 +45978,7 @@
         <v>2</v>
       </c>
       <c r="Z413" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA413">
         <v>1</v>
@@ -45999,7 +45996,7 @@
         <v>1975</v>
       </c>
       <c r="AF413" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG413" t="b">
         <v>1</v>
@@ -46091,7 +46088,7 @@
         <v>1975</v>
       </c>
       <c r="AF414" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG414" t="b">
         <v>1</v>
@@ -46186,7 +46183,7 @@
         <v>1975</v>
       </c>
       <c r="AF415" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG415" t="b">
         <v>1</v>
@@ -46266,7 +46263,7 @@
         <v>1.64</v>
       </c>
       <c r="Z416" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA416">
         <v>1</v>
@@ -46284,7 +46281,7 @@
         <v>1981</v>
       </c>
       <c r="AF416" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -46376,7 +46373,7 @@
         <v>1975</v>
       </c>
       <c r="AF417" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG417" t="b">
         <v>1</v>
@@ -46468,7 +46465,7 @@
         <v>1975</v>
       </c>
       <c r="AF418" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG418" t="b">
         <v>1</v>
@@ -46560,7 +46557,7 @@
         <v>1975</v>
       </c>
       <c r="AF419" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG419" t="b">
         <v>1</v>
@@ -46634,7 +46631,7 @@
         <v>2</v>
       </c>
       <c r="Z420" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AA420">
         <v>1</v>
@@ -46652,7 +46649,7 @@
         <v>1975</v>
       </c>
       <c r="AF420" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG420" t="b">
         <v>1</v>
@@ -46747,7 +46744,7 @@
         <v>1975</v>
       </c>
       <c r="AF421" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG421" t="b">
         <v>1</v>
@@ -46827,7 +46824,7 @@
         <v>1.25</v>
       </c>
       <c r="Z422" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="AA422">
         <v>1</v>
@@ -46845,7 +46842,7 @@
         <v>1977</v>
       </c>
       <c r="AF422" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="AG422" t="b">
         <v>0</v>
@@ -46925,13 +46922,13 @@
         <v>3</v>
       </c>
       <c r="Z423" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="AE423" t="s">
         <v>1978</v>
       </c>
       <c r="AF423" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG423" t="b">
         <v>1</v>
@@ -46984,13 +46981,13 @@
         <v>1899</v>
       </c>
       <c r="R424">
-        <v>328.5</v>
+        <v>0.84</v>
       </c>
       <c r="S424">
         <v>0.84</v>
       </c>
       <c r="T424">
-        <v>182.5</v>
+        <v>0.42</v>
       </c>
       <c r="U424">
         <v>0.42</v>
@@ -47005,7 +47002,7 @@
         <v>4</v>
       </c>
       <c r="Z424" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="AA424">
         <v>0</v>
@@ -47014,25 +47011,25 @@
         <v>1</v>
       </c>
       <c r="AC424">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AD424">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="AE424" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="AF424" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="AG424" t="b">
         <v>0</v>
       </c>
       <c r="AH424">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AI424">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AJ424">
         <v>0</v>
@@ -47118,7 +47115,7 @@
         <v>1975</v>
       </c>
       <c r="AF425" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG425" t="b">
         <v>1</v>
@@ -47213,7 +47210,7 @@
         <v>1975</v>
       </c>
       <c r="AF426" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG426" t="b">
         <v>1</v>
@@ -47308,7 +47305,7 @@
         <v>1975</v>
       </c>
       <c r="AF427" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="AG427" t="b">
         <v>1</v>

--- a/output/analysis_result.xlsx
+++ b/output/analysis_result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="2081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5544" uniqueCount="2075">
   <si>
     <t>code</t>
   </si>
@@ -5965,15 +5965,15 @@
     <t>建議提高：Min 1→3、Max 4→5</t>
   </si>
   <si>
+    <t>建議提高：Min 1→2、Max 2→4</t>
+  </si>
+  <si>
     <t>建議提高：Min 1→3、Max 3→4</t>
   </si>
   <si>
     <t>建議提高：Min 1→2、Max 2→3</t>
   </si>
   <si>
-    <t>建議提高：Min 1→2、Max 2→4</t>
-  </si>
-  <si>
     <t>建議提高：Max 2→3</t>
   </si>
   <si>
@@ -5989,7 +5989,7 @@
     <t>建議提高：Min 0→2、Max 1→3</t>
   </si>
   <si>
-    <t>建議調整範圍：Min 0→3、Max 10→4</t>
+    <t>建議調整範圍：Min 0→2、Max 10→3</t>
   </si>
   <si>
     <t>建議降低：Max 10→5</t>
@@ -6007,10 +6007,7 @@
     <t>尚未設定安全庫存，建議新增 Min 19 / Max 21</t>
   </si>
   <si>
-    <t>建議調整範圍：Min 1→2、Max 5→3</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 1→2、Max 5→4</t>
+    <t>建議降低：Max 5→2</t>
   </si>
   <si>
     <t>建議降低：Max 5→3</t>
@@ -6019,10 +6016,7 @@
     <t>建議提高：Min 1→3</t>
   </si>
   <si>
-    <t>建議降低：Max 5→2</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 1→3、Max 10→5</t>
+    <t>建議調整範圍：Min 1→2、Max 10→4</t>
   </si>
   <si>
     <t>建議降低：Min 3→1、Max 10→2</t>
@@ -6031,211 +6025,199 @@
     <t>建議調整範圍：Min 3→4、Max 10→6</t>
   </si>
   <si>
+    <t>尚未設定安全庫存，建議新增 Min 1 / Max 3</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 1 / Max 2</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 8 / Max 10</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→8、Max 10→17</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 4 / Max 5</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 5→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→4、Max 5→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→2、Max 3→4</t>
+  </si>
+  <si>
+    <t>建議降低：Max 3→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→2</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 0→7、Max 20→9</t>
+  </si>
+  <si>
+    <t>建議降低：Min 10→3、Max 20→6</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 5 / Max 8</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 2 / Max 3</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 6 / Max 8</t>
+  </si>
+  <si>
     <t>尚未設定安全庫存，建議新增 Min 2 / Max 4</t>
   </si>
   <si>
-    <t>尚未設定安全庫存，建議新增 Min 1 / Max 3</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 1 / Max 2</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 12 / Max 14</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→19、Max 10→28</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 4 / Max 5</t>
+    <t>建議提高：Min 0→1、Max 1→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→1、Max 2→3</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→4、Max 3→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→1</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→3、Max 2→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→5、Max 8→9</t>
+  </si>
+  <si>
+    <t>建議提高：Max 4→6</t>
+  </si>
+  <si>
+    <t>建議降低：Max 8→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→6、Max 4→8</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 0→1、Max 4→3</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→3、Max 8→5</t>
+  </si>
+  <si>
+    <t>建議提高：Min 4→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→6、Max 4→9</t>
+  </si>
+  <si>
+    <t>建議降低：Max 8→7</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→9、Max 4→13</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→3、Max 4→5</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→1、Max 8→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→6、Max 1→9</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→18、Max 8→21</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→2、Max 10→4</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→3、Max 10→5</t>
+  </si>
+  <si>
+    <t>建議提高：Min 4→8、Max 10→11</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 4→7、Max 10→9</t>
+  </si>
+  <si>
+    <t>建議降低：Min 4→1、Max 10→3</t>
+  </si>
+  <si>
+    <t>建議降低：Max 10→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→13、Max 6→16</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 10→4</t>
+  </si>
+  <si>
+    <t>建議降低：Max 10→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 1→4、Max 5→6</t>
+  </si>
+  <si>
+    <t>建議降低：Max 4→2</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→21、Max 4→26</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→3、Max 1→5</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→7、Max 10→9</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 10→3</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→4、Max 10→6</t>
+  </si>
+  <si>
+    <t>建議降低：Min 2→1、Max 8→3</t>
+  </si>
+  <si>
+    <t>建議降低：Max 8→5</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→3、Max 10→4</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→6、Max 8→9</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 10→32、Max 50→35</t>
+  </si>
+  <si>
+    <t>建議降低：Min 5→2、Max 10→3</t>
+  </si>
+  <si>
+    <t>建議調整範圍：Min 2→5、Max 10→7</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 3 / Max 4</t>
+  </si>
+  <si>
+    <t>尚未設定安全庫存，建議新增 Min 6 / Max 9</t>
+  </si>
+  <si>
+    <t>建議提高：Min 0→4、Max 3→6</t>
+  </si>
+  <si>
+    <t>建議提高：Min 2→4</t>
   </si>
   <si>
     <t>建議提高：Min 1→3、Max 2→4</t>
   </si>
   <si>
-    <t>建議降低：Min 2→1、Max 5→2</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→3、Max 5→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→4、Max 5→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→2、Max 3→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→2</t>
-  </si>
-  <si>
-    <t>建議降低：Max 3→2</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 0→7、Max 20→9</t>
-  </si>
-  <si>
-    <t>建議降低：Min 10→2、Max 20→5</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 5 / Max 8</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 2 / Max 3</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 6 / Max 8</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→1、Max 1→2</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→1、Max 2→3</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→4、Max 3→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→1</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→3、Max 2→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→5、Max 8→9</t>
-  </si>
-  <si>
-    <t>建議提高：Max 4→6</t>
-  </si>
-  <si>
-    <t>建議降低：Max 8→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→6、Max 4→8</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 0→1、Max 4→3</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→3、Max 8→5</t>
-  </si>
-  <si>
-    <t>建議提高：Min 4→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→6、Max 4→9</t>
-  </si>
-  <si>
-    <t>建議降低：Max 8→7</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→9、Max 4→13</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→1、Max 8→2</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→3、Max 4→5</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→6、Max 1→9</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→27、Max 8→30</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→2、Max 10→4</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→3、Max 10→5</t>
-  </si>
-  <si>
-    <t>建議提高：Min 4→8、Max 10→11</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 4→7、Max 10→9</t>
-  </si>
-  <si>
-    <t>建議降低：Min 4→1、Max 10→3</t>
-  </si>
-  <si>
-    <t>建議降低：Max 10→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→13、Max 6→16</t>
-  </si>
-  <si>
-    <t>建議降低：Min 2→1、Max 10→4</t>
-  </si>
-  <si>
-    <t>建議降低：Max 10→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→4、Max 5→6</t>
-  </si>
-  <si>
-    <t>建議降低：Max 4→2</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→21、Max 4→26</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→5、Max 1→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→3、Max 1→5</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→7、Max 10→9</t>
-  </si>
-  <si>
-    <t>建議降低：Min 2→1、Max 10→3</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→4、Max 10→6</t>
-  </si>
-  <si>
-    <t>建議降低：Min 2→1、Max 8→3</t>
-  </si>
-  <si>
-    <t>建議降低：Max 8→5</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→3、Max 10→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→6、Max 8→9</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 10→32、Max 50→35</t>
-  </si>
-  <si>
-    <t>建議降低：Min 5→2、Max 10→3</t>
-  </si>
-  <si>
-    <t>建議調整範圍：Min 2→5、Max 10→7</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 3 / Max 4</t>
-  </si>
-  <si>
-    <t>尚未設定安全庫存，建議新增 Min 6 / Max 9</t>
-  </si>
-  <si>
-    <t>建議提高：Min 0→4、Max 3→6</t>
-  </si>
-  <si>
-    <t>建議提高：Min 2→4</t>
-  </si>
-  <si>
     <t>建議提高：Min 1→5、Max 4→7</t>
   </si>
   <si>
-    <t>建議提高：Min 1→5、Max 2→7</t>
-  </si>
-  <si>
     <t>建議降低：Min 2→1、Max 12→4</t>
-  </si>
-  <si>
-    <t>建議提高：Min 1→4、Max 2→6</t>
   </si>
   <si>
     <t>建議提高：Min 0→1、Max 1→3</t>
@@ -6819,7 +6801,7 @@
         <v>1973</v>
       </c>
       <c r="AF2" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -6884,13 +6866,13 @@
         <v>1793</v>
       </c>
       <c r="R3">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S3">
         <v>0.8100000000000001</v>
       </c>
       <c r="T3">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U3">
         <v>0.8100000000000001</v>
@@ -6926,7 +6908,7 @@
         <v>1974</v>
       </c>
       <c r="AF3" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -7030,7 +7012,7 @@
         <v>1975</v>
       </c>
       <c r="AF4" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG4" t="b">
         <v>1</v>
@@ -7089,7 +7071,7 @@
         <v>1795</v>
       </c>
       <c r="R5">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="S5">
         <v>0.97</v>
@@ -7131,7 +7113,7 @@
         <v>1976</v>
       </c>
       <c r="AF5" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -7235,7 +7217,7 @@
         <v>1977</v>
       </c>
       <c r="AF6" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -7336,7 +7318,7 @@
         <v>1975</v>
       </c>
       <c r="AF7" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG7" t="b">
         <v>1</v>
@@ -7419,7 +7401,7 @@
         <v>1978</v>
       </c>
       <c r="AF8" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG8" t="b">
         <v>1</v>
@@ -7502,7 +7484,7 @@
         <v>1978</v>
       </c>
       <c r="AF9" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG9" t="b">
         <v>1</v>
@@ -7603,7 +7585,7 @@
         <v>1979</v>
       </c>
       <c r="AF10" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -7710,7 +7692,7 @@
         <v>1974</v>
       </c>
       <c r="AF11" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -7802,7 +7784,7 @@
         <v>1978</v>
       </c>
       <c r="AF12" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG12" t="b">
         <v>1</v>
@@ -7891,7 +7873,7 @@
         <v>1975</v>
       </c>
       <c r="AF13" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG13" t="b">
         <v>1</v>
@@ -7971,7 +7953,7 @@
         <v>1978</v>
       </c>
       <c r="AF14" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG14" t="b">
         <v>1</v>
@@ -8066,7 +8048,7 @@
         <v>1975</v>
       </c>
       <c r="AF15" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG15" t="b">
         <v>1</v>
@@ -8167,7 +8149,7 @@
         <v>1980</v>
       </c>
       <c r="AF16" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG16" t="b">
         <v>0</v>
@@ -8253,7 +8235,7 @@
         <v>1978</v>
       </c>
       <c r="AF17" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG17" t="b">
         <v>1</v>
@@ -8336,7 +8318,7 @@
         <v>1978</v>
       </c>
       <c r="AF18" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG18" t="b">
         <v>1</v>
@@ -8437,7 +8419,7 @@
         <v>1981</v>
       </c>
       <c r="AF19" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG19" t="b">
         <v>0</v>
@@ -8541,7 +8523,7 @@
         <v>1982</v>
       </c>
       <c r="AF20" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -8603,7 +8585,7 @@
         <v>1803</v>
       </c>
       <c r="R21">
-        <v>3.38</v>
+        <v>2.25</v>
       </c>
       <c r="S21">
         <v>1.13</v>
@@ -8636,25 +8618,25 @@
         <v>2</v>
       </c>
       <c r="AC21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE21" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="AF21" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ21">
         <v>1</v>
@@ -8722,7 +8704,7 @@
         <v>1978</v>
       </c>
       <c r="AF22" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG22" t="b">
         <v>1</v>
@@ -8817,10 +8799,10 @@
         <v>4</v>
       </c>
       <c r="AE23" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="AF23" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG23" t="b">
         <v>0</v>
@@ -8882,13 +8864,13 @@
         <v>1805</v>
       </c>
       <c r="R24">
-        <v>1.34</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S24">
         <v>0.8100000000000001</v>
       </c>
       <c r="T24">
-        <v>1.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U24">
         <v>0.8100000000000001</v>
@@ -8921,10 +8903,10 @@
         <v>3</v>
       </c>
       <c r="AE24" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="AF24" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG24" t="b">
         <v>0</v>
@@ -9025,10 +9007,10 @@
         <v>4</v>
       </c>
       <c r="AE25" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="AF25" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG25" t="b">
         <v>0</v>
@@ -9132,7 +9114,7 @@
         <v>1986</v>
       </c>
       <c r="AF26" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG26" t="b">
         <v>0</v>
@@ -9236,7 +9218,7 @@
         <v>1987</v>
       </c>
       <c r="AF27" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG27" t="b">
         <v>0</v>
@@ -9340,7 +9322,7 @@
         <v>1988</v>
       </c>
       <c r="AF28" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG28" t="b">
         <v>0</v>
@@ -9444,7 +9426,7 @@
         <v>1977</v>
       </c>
       <c r="AF29" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG29" t="b">
         <v>0</v>
@@ -9548,7 +9530,7 @@
         <v>1989</v>
       </c>
       <c r="AF30" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -9643,7 +9625,7 @@
         <v>1975</v>
       </c>
       <c r="AF31" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG31" t="b">
         <v>1</v>
@@ -9732,7 +9714,7 @@
         <v>1975</v>
       </c>
       <c r="AF32" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG32" t="b">
         <v>1</v>
@@ -9830,7 +9812,7 @@
         <v>1990</v>
       </c>
       <c r="AF33" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG33" t="b">
         <v>0</v>
@@ -9931,7 +9913,7 @@
         <v>1977</v>
       </c>
       <c r="AF34" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -10029,7 +10011,7 @@
         <v>1975</v>
       </c>
       <c r="AF35" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG35" t="b">
         <v>1</v>
@@ -10124,7 +10106,7 @@
         <v>1975</v>
       </c>
       <c r="AF36" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG36" t="b">
         <v>1</v>
@@ -10180,13 +10162,13 @@
         <v>1775</v>
       </c>
       <c r="R37">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="S37">
         <v>1.55</v>
       </c>
       <c r="T37">
-        <v>2.86</v>
+        <v>2.07</v>
       </c>
       <c r="U37">
         <v>2.07</v>
@@ -10219,10 +10201,10 @@
         <v>3</v>
       </c>
       <c r="AE37" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="AF37" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG37" t="b">
         <v>0</v>
@@ -10320,7 +10302,7 @@
         <v>1975</v>
       </c>
       <c r="AF38" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG38" t="b">
         <v>1</v>
@@ -10376,13 +10358,13 @@
         <v>1813</v>
       </c>
       <c r="R39">
-        <v>2.27</v>
+        <v>0.85</v>
       </c>
       <c r="S39">
         <v>0.85</v>
       </c>
       <c r="T39">
-        <v>2.53</v>
+        <v>0.85</v>
       </c>
       <c r="U39">
         <v>0.85</v>
@@ -10400,7 +10382,7 @@
         <v>4</v>
       </c>
       <c r="Z39" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA39">
         <v>0</v>
@@ -10409,25 +10391,25 @@
         <v>10</v>
       </c>
       <c r="AC39">
+        <v>2</v>
+      </c>
+      <c r="AD39">
         <v>3</v>
-      </c>
-      <c r="AD39">
-        <v>4</v>
       </c>
       <c r="AE39" t="s">
         <v>1991</v>
       </c>
       <c r="AF39" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI39">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="AJ39">
         <v>1</v>
@@ -10522,7 +10504,7 @@
         <v>1992</v>
       </c>
       <c r="AF40" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -10626,7 +10608,7 @@
         <v>1993</v>
       </c>
       <c r="AF41" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG41" t="b">
         <v>0</v>
@@ -10730,7 +10712,7 @@
         <v>1992</v>
       </c>
       <c r="AF42" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -10834,7 +10816,7 @@
         <v>1994</v>
       </c>
       <c r="AF43" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG43" t="b">
         <v>0</v>
@@ -10938,7 +10920,7 @@
         <v>1995</v>
       </c>
       <c r="AF44" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>
@@ -11039,7 +11021,7 @@
         <v>1975</v>
       </c>
       <c r="AF45" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG45" t="b">
         <v>1</v>
@@ -11134,7 +11116,7 @@
         <v>1975</v>
       </c>
       <c r="AF46" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG46" t="b">
         <v>1</v>
@@ -11226,7 +11208,7 @@
         <v>1975</v>
       </c>
       <c r="AF47" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG47" t="b">
         <v>1</v>
@@ -11318,7 +11300,7 @@
         <v>1975</v>
       </c>
       <c r="AF48" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG48" t="b">
         <v>1</v>
@@ -11413,7 +11395,7 @@
         <v>1975</v>
       </c>
       <c r="AF49" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG49" t="b">
         <v>1</v>
@@ -11505,7 +11487,7 @@
         <v>1996</v>
       </c>
       <c r="AF50" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG50" t="b">
         <v>0</v>
@@ -11597,7 +11579,7 @@
         <v>1975</v>
       </c>
       <c r="AF51" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG51" t="b">
         <v>1</v>
@@ -11653,13 +11635,13 @@
         <v>1821</v>
       </c>
       <c r="R52">
-        <v>1.47</v>
+        <v>0.79</v>
       </c>
       <c r="S52">
         <v>0.79</v>
       </c>
       <c r="T52">
-        <v>1.64</v>
+        <v>0.79</v>
       </c>
       <c r="U52">
         <v>0.79</v>
@@ -11674,7 +11656,7 @@
         <v>5</v>
       </c>
       <c r="Z52" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA52">
         <v>1</v>
@@ -11683,25 +11665,25 @@
         <v>5</v>
       </c>
       <c r="AC52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE52" t="s">
         <v>1997</v>
       </c>
       <c r="AF52" t="s">
-        <v>2079</v>
+        <v>2069</v>
       </c>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI52">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="AJ52">
         <v>1</v>
@@ -11754,13 +11736,13 @@
         <v>1822</v>
       </c>
       <c r="R53">
-        <v>1.88</v>
+        <v>0.99</v>
       </c>
       <c r="S53">
         <v>0.99</v>
       </c>
       <c r="T53">
-        <v>1.8</v>
+        <v>0.79</v>
       </c>
       <c r="U53">
         <v>0.79</v>
@@ -11775,7 +11757,7 @@
         <v>5</v>
       </c>
       <c r="Z53" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA53">
         <v>1</v>
@@ -11784,25 +11766,25 @@
         <v>5</v>
       </c>
       <c r="AC53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE53" t="s">
         <v>1998</v>
       </c>
       <c r="AF53" t="s">
-        <v>2079</v>
+        <v>2069</v>
       </c>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI53">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AJ53">
         <v>0</v>
@@ -11855,13 +11837,13 @@
         <v>1823</v>
       </c>
       <c r="R54">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="S54">
         <v>1.38</v>
       </c>
       <c r="T54">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="U54">
         <v>0.99</v>
@@ -11894,10 +11876,10 @@
         <v>3</v>
       </c>
       <c r="AE54" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="AF54" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -11998,10 +11980,10 @@
         <v>5</v>
       </c>
       <c r="AE55" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="AF55" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG55" t="b">
         <v>0</v>
@@ -12063,13 +12045,13 @@
         <v>1825</v>
       </c>
       <c r="R56">
-        <v>2.47</v>
+        <v>1.01</v>
       </c>
       <c r="S56">
         <v>1.01</v>
       </c>
       <c r="T56">
-        <v>2.28</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="U56">
         <v>0.8100000000000001</v>
@@ -12084,7 +12066,7 @@
         <v>5</v>
       </c>
       <c r="Z56" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA56">
         <v>1</v>
@@ -12093,25 +12075,25 @@
         <v>5</v>
       </c>
       <c r="AC56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE56" t="s">
         <v>1998</v>
       </c>
       <c r="AF56" t="s">
-        <v>2079</v>
+        <v>2069</v>
       </c>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI56">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AJ56">
         <v>0</v>
@@ -12200,7 +12182,7 @@
         <v>1975</v>
       </c>
       <c r="AF57" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG57" t="b">
         <v>1</v>
@@ -12292,7 +12274,7 @@
         <v>1975</v>
       </c>
       <c r="AF58" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG58" t="b">
         <v>1</v>
@@ -12387,10 +12369,10 @@
         <v>2</v>
       </c>
       <c r="AE59" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="AF59" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG59" t="b">
         <v>0</v>
@@ -12488,7 +12470,7 @@
         <v>1975</v>
       </c>
       <c r="AF60" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG60" t="b">
         <v>1</v>
@@ -12544,7 +12526,7 @@
         <v>1828</v>
       </c>
       <c r="R61">
-        <v>5.79</v>
+        <v>3.86</v>
       </c>
       <c r="S61">
         <v>1.93</v>
@@ -12577,25 +12559,25 @@
         <v>10</v>
       </c>
       <c r="AC61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE61" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="AF61" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AH61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI61">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="AJ61">
         <v>0</v>
@@ -12687,10 +12669,10 @@
         <v>2</v>
       </c>
       <c r="AE62" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="AF62" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG62" t="b">
         <v>0</v>
@@ -12791,10 +12773,10 @@
         <v>6</v>
       </c>
       <c r="AE63" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="AF63" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG63" t="b">
         <v>0</v>
@@ -12892,7 +12874,7 @@
         <v>1975</v>
       </c>
       <c r="AF64" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG64" t="b">
         <v>1</v>
@@ -12984,7 +12966,7 @@
         <v>1975</v>
       </c>
       <c r="AF65" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG65" t="b">
         <v>1</v>
@@ -13040,7 +13022,7 @@
         <v>1831</v>
       </c>
       <c r="R66">
-        <v>6.92</v>
+        <v>4.61</v>
       </c>
       <c r="S66">
         <v>2.31</v>
@@ -13067,16 +13049,16 @@
         <v>1972</v>
       </c>
       <c r="AC66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE66" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="AF66" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG66" t="b">
         <v>0</v>
@@ -13132,13 +13114,13 @@
         <v>1832</v>
       </c>
       <c r="R67">
-        <v>4.94</v>
+        <v>1.65</v>
       </c>
       <c r="S67">
         <v>1.65</v>
       </c>
       <c r="T67">
-        <v>16.75</v>
+        <v>0.82</v>
       </c>
       <c r="U67">
         <v>0.82</v>
@@ -13153,7 +13135,7 @@
         <v>10</v>
       </c>
       <c r="Z67" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="AC67">
         <v>1</v>
@@ -13162,10 +13144,10 @@
         <v>3</v>
       </c>
       <c r="AE67" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="AF67" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG67" t="b">
         <v>0</v>
@@ -13236,7 +13218,7 @@
         <v>1978</v>
       </c>
       <c r="AF68" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG68" t="b">
         <v>1</v>
@@ -13322,10 +13304,10 @@
         <v>2</v>
       </c>
       <c r="AE69" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="AF69" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG69" t="b">
         <v>0</v>
@@ -13381,7 +13363,7 @@
         <v>1833</v>
       </c>
       <c r="R70">
-        <v>9.640000000000001</v>
+        <v>6.42</v>
       </c>
       <c r="S70">
         <v>3.21</v>
@@ -13408,16 +13390,16 @@
         <v>1972</v>
       </c>
       <c r="AC70">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AD70">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE70" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="AF70" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG70" t="b">
         <v>0</v>
@@ -13503,10 +13485,10 @@
         <v>2</v>
       </c>
       <c r="AE71" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="AF71" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG71" t="b">
         <v>0</v>
@@ -13601,7 +13583,7 @@
         <v>1987</v>
       </c>
       <c r="AF72" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG72" t="b">
         <v>0</v>
@@ -13699,7 +13681,7 @@
         <v>1975</v>
       </c>
       <c r="AF73" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG73" t="b">
         <v>1</v>
@@ -13791,7 +13773,7 @@
         <v>1975</v>
       </c>
       <c r="AF74" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG74" t="b">
         <v>1</v>
@@ -13883,7 +13865,7 @@
         <v>1975</v>
       </c>
       <c r="AF75" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG75" t="b">
         <v>1</v>
@@ -13975,7 +13957,7 @@
         <v>1975</v>
       </c>
       <c r="AF76" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG76" t="b">
         <v>1</v>
@@ -14070,10 +14052,10 @@
         <v>2</v>
       </c>
       <c r="AE77" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="AF77" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -14135,13 +14117,13 @@
         <v>1837</v>
       </c>
       <c r="R78">
-        <v>14.21</v>
+        <v>5.79</v>
       </c>
       <c r="S78">
         <v>5.79</v>
       </c>
       <c r="T78">
-        <v>0.92</v>
+        <v>0.64</v>
       </c>
       <c r="U78">
         <v>0.64</v>
@@ -14168,25 +14150,25 @@
         <v>10</v>
       </c>
       <c r="AC78">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AD78">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AE78" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="AF78" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AH78">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AI78">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="AJ78">
         <v>11</v>
@@ -14275,7 +14257,7 @@
         <v>1975</v>
       </c>
       <c r="AF79" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG79" t="b">
         <v>1</v>
@@ -14367,7 +14349,7 @@
         <v>1975</v>
       </c>
       <c r="AF80" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG80" t="b">
         <v>1</v>
@@ -14459,7 +14441,7 @@
         <v>1975</v>
       </c>
       <c r="AF81" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG81" t="b">
         <v>1</v>
@@ -14551,7 +14533,7 @@
         <v>1975</v>
       </c>
       <c r="AF82" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG82" t="b">
         <v>1</v>
@@ -14640,10 +14622,10 @@
         <v>5</v>
       </c>
       <c r="AE83" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="AF83" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG83" t="b">
         <v>0</v>
@@ -14726,7 +14708,7 @@
         <v>1978</v>
       </c>
       <c r="AF84" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG84" t="b">
         <v>1</v>
@@ -14812,7 +14794,7 @@
         <v>1978</v>
       </c>
       <c r="AF85" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG85" t="b">
         <v>1</v>
@@ -14898,7 +14880,7 @@
         <v>1978</v>
       </c>
       <c r="AF86" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG86" t="b">
         <v>1</v>
@@ -14987,10 +14969,10 @@
         <v>2</v>
       </c>
       <c r="AE87" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="AF87" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG87" t="b">
         <v>0</v>
@@ -15073,7 +15055,7 @@
         <v>1978</v>
       </c>
       <c r="AF88" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG88" t="b">
         <v>1</v>
@@ -15153,7 +15135,7 @@
         <v>1978</v>
       </c>
       <c r="AF89" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG89" t="b">
         <v>1</v>
@@ -15233,7 +15215,7 @@
         <v>1978</v>
       </c>
       <c r="AF90" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG90" t="b">
         <v>1</v>
@@ -15325,7 +15307,7 @@
         <v>1975</v>
       </c>
       <c r="AF91" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG91" t="b">
         <v>1</v>
@@ -15381,13 +15363,13 @@
         <v>1840</v>
       </c>
       <c r="R92">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="S92">
         <v>1.3</v>
       </c>
       <c r="T92">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="U92">
         <v>1.3</v>
@@ -15405,7 +15387,7 @@
         <v>2.5</v>
       </c>
       <c r="Z92" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA92">
         <v>1</v>
@@ -15414,25 +15396,25 @@
         <v>2</v>
       </c>
       <c r="AC92">
+        <v>2</v>
+      </c>
+      <c r="AD92">
         <v>3</v>
       </c>
-      <c r="AD92">
-        <v>4</v>
-      </c>
       <c r="AE92" t="s">
-        <v>2011</v>
+        <v>1985</v>
       </c>
       <c r="AF92" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
       <c r="AH92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ92">
         <v>1</v>
@@ -15518,7 +15500,7 @@
         <v>1975</v>
       </c>
       <c r="AF93" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG93" t="b">
         <v>1</v>
@@ -15607,7 +15589,7 @@
         <v>1975</v>
       </c>
       <c r="AF94" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG94" t="b">
         <v>1</v>
@@ -15702,7 +15684,7 @@
         <v>1975</v>
       </c>
       <c r="AF95" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG95" t="b">
         <v>1</v>
@@ -15761,13 +15743,13 @@
         <v>1841</v>
       </c>
       <c r="R96">
-        <v>1.93</v>
+        <v>0.64</v>
       </c>
       <c r="S96">
         <v>0.64</v>
       </c>
       <c r="T96">
-        <v>3.29</v>
+        <v>0.64</v>
       </c>
       <c r="U96">
         <v>0.64</v>
@@ -15782,7 +15764,7 @@
         <v>6</v>
       </c>
       <c r="Z96" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA96">
         <v>2</v>
@@ -15797,10 +15779,10 @@
         <v>2</v>
       </c>
       <c r="AE96" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="AF96" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG96" t="b">
         <v>0</v>
@@ -15901,7 +15883,7 @@
         <v>1975</v>
       </c>
       <c r="AF97" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG97" t="b">
         <v>1</v>
@@ -15960,13 +15942,13 @@
         <v>1758</v>
       </c>
       <c r="R98">
-        <v>1.93</v>
+        <v>0.64</v>
       </c>
       <c r="S98">
         <v>0.64</v>
       </c>
       <c r="T98">
-        <v>2.21</v>
+        <v>0.64</v>
       </c>
       <c r="U98">
         <v>0.64</v>
@@ -15984,7 +15966,7 @@
         <v>2</v>
       </c>
       <c r="Z98" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA98">
         <v>2</v>
@@ -15993,25 +15975,25 @@
         <v>5</v>
       </c>
       <c r="AC98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD98">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE98" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="AF98" t="s">
-        <v>2079</v>
+        <v>2069</v>
       </c>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AH98">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="AI98">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AJ98">
         <v>2</v>
@@ -16106,10 +16088,10 @@
         <v>2</v>
       </c>
       <c r="AE99" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="AF99" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -16210,10 +16192,10 @@
         <v>6</v>
       </c>
       <c r="AE100" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="AF100" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -16311,7 +16293,7 @@
         <v>1975</v>
       </c>
       <c r="AF101" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG101" t="b">
         <v>1</v>
@@ -16406,10 +16388,10 @@
         <v>2</v>
       </c>
       <c r="AE102" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="AF102" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG102" t="b">
         <v>0</v>
@@ -16510,7 +16492,7 @@
         <v>1975</v>
       </c>
       <c r="AF103" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG103" t="b">
         <v>1</v>
@@ -16605,7 +16587,7 @@
         <v>1975</v>
       </c>
       <c r="AF104" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG104" t="b">
         <v>1</v>
@@ -16700,7 +16682,7 @@
         <v>1975</v>
       </c>
       <c r="AF105" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG105" t="b">
         <v>1</v>
@@ -16801,7 +16783,7 @@
         <v>1977</v>
       </c>
       <c r="AF106" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG106" t="b">
         <v>0</v>
@@ -16902,10 +16884,10 @@
         <v>2</v>
       </c>
       <c r="AE107" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="AF107" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG107" t="b">
         <v>0</v>
@@ -17006,7 +16988,7 @@
         <v>1975</v>
       </c>
       <c r="AF108" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG108" t="b">
         <v>1</v>
@@ -17098,10 +17080,10 @@
         <v>2</v>
       </c>
       <c r="AE109" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
       <c r="AF109" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG109" t="b">
         <v>0</v>
@@ -17166,13 +17148,13 @@
         <v>1850</v>
       </c>
       <c r="R110">
-        <v>0.79</v>
+        <v>1.13</v>
       </c>
       <c r="S110">
         <v>1.13</v>
       </c>
       <c r="T110">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="U110">
         <v>0.8</v>
@@ -17205,10 +17187,10 @@
         <v>4</v>
       </c>
       <c r="AE110" t="s">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="AF110" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -17273,13 +17255,13 @@
         <v>1851</v>
       </c>
       <c r="R111">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="S111">
         <v>0.64</v>
       </c>
       <c r="T111">
-        <v>0.87</v>
+        <v>0.64</v>
       </c>
       <c r="U111">
         <v>0.64</v>
@@ -17306,25 +17288,25 @@
         <v>3</v>
       </c>
       <c r="AC111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE111" t="s">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="AF111" t="s">
-        <v>2077</v>
+        <v>2069</v>
       </c>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AH111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI111">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ111">
         <v>1</v>
@@ -17419,7 +17401,7 @@
         <v>1975</v>
       </c>
       <c r="AF112" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG112" t="b">
         <v>1</v>
@@ -17514,7 +17496,7 @@
         <v>1975</v>
       </c>
       <c r="AF113" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG113" t="b">
         <v>1</v>
@@ -17609,7 +17591,7 @@
         <v>1975</v>
       </c>
       <c r="AF114" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG114" t="b">
         <v>1</v>
@@ -17701,7 +17683,7 @@
         <v>1975</v>
       </c>
       <c r="AF115" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG115" t="b">
         <v>1</v>
@@ -17796,10 +17778,10 @@
         <v>3</v>
       </c>
       <c r="AE116" t="s">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="AF116" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG116" t="b">
         <v>0</v>
@@ -17903,10 +17885,10 @@
         <v>2</v>
       </c>
       <c r="AE117" t="s">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="AF117" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG117" t="b">
         <v>0</v>
@@ -18007,7 +17989,7 @@
         <v>1975</v>
       </c>
       <c r="AF118" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG118" t="b">
         <v>1</v>
@@ -18105,10 +18087,10 @@
         <v>2</v>
       </c>
       <c r="AE119" t="s">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="AF119" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG119" t="b">
         <v>0</v>
@@ -18200,7 +18182,7 @@
         <v>1975</v>
       </c>
       <c r="AF120" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG120" t="b">
         <v>1</v>
@@ -18292,7 +18274,7 @@
         <v>1975</v>
       </c>
       <c r="AF121" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG121" t="b">
         <v>1</v>
@@ -18387,10 +18369,10 @@
         <v>9</v>
       </c>
       <c r="AE122" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="AF122" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG122" t="b">
         <v>0</v>
@@ -18452,13 +18434,13 @@
         <v>1855</v>
       </c>
       <c r="R123">
-        <v>1.31</v>
+        <v>1.77</v>
       </c>
       <c r="S123">
         <v>1.77</v>
       </c>
       <c r="T123">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="U123">
         <v>0.8</v>
@@ -18482,25 +18464,25 @@
         <v>20</v>
       </c>
       <c r="AC123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE123" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="AF123" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AH123">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="AI123">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="AJ123">
         <v>7</v>
@@ -18589,7 +18571,7 @@
         <v>1975</v>
       </c>
       <c r="AF124" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG124" t="b">
         <v>1</v>
@@ -18684,7 +18666,7 @@
         <v>1975</v>
       </c>
       <c r="AF125" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG125" t="b">
         <v>1</v>
@@ -18770,7 +18752,7 @@
         <v>1975</v>
       </c>
       <c r="AF126" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG126" t="b">
         <v>1</v>
@@ -18862,7 +18844,7 @@
         <v>1975</v>
       </c>
       <c r="AF127" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG127" t="b">
         <v>1</v>
@@ -18960,7 +18942,7 @@
         <v>1977</v>
       </c>
       <c r="AF128" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG128" t="b">
         <v>0</v>
@@ -19025,13 +19007,13 @@
         <v>1858</v>
       </c>
       <c r="R129">
-        <v>1.07</v>
+        <v>0.64</v>
       </c>
       <c r="S129">
         <v>0.64</v>
       </c>
       <c r="T129">
-        <v>1.19</v>
+        <v>0.64</v>
       </c>
       <c r="U129">
         <v>0.64</v>
@@ -19058,25 +19040,25 @@
         <v>2</v>
       </c>
       <c r="AC129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD129">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE129" t="s">
-        <v>1984</v>
+        <v>1977</v>
       </c>
       <c r="AF129" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AH129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ129">
         <v>1</v>
@@ -19159,7 +19141,7 @@
         <v>1975</v>
       </c>
       <c r="AF130" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG130" t="b">
         <v>1</v>
@@ -19251,7 +19233,7 @@
         <v>1975</v>
       </c>
       <c r="AF131" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG131" t="b">
         <v>1</v>
@@ -19349,7 +19331,7 @@
         <v>1977</v>
       </c>
       <c r="AF132" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG132" t="b">
         <v>0</v>
@@ -19444,7 +19426,7 @@
         <v>1975</v>
       </c>
       <c r="AF133" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG133" t="b">
         <v>1</v>
@@ -19533,10 +19515,10 @@
         <v>8</v>
       </c>
       <c r="AE134" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="AF134" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG134" t="b">
         <v>0</v>
@@ -19607,7 +19589,7 @@
         <v>1978</v>
       </c>
       <c r="AF135" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG135" t="b">
         <v>1</v>
@@ -19693,10 +19675,10 @@
         <v>3</v>
       </c>
       <c r="AE136" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="AF136" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG136" t="b">
         <v>0</v>
@@ -19767,7 +19749,7 @@
         <v>1978</v>
       </c>
       <c r="AF137" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG137" t="b">
         <v>1</v>
@@ -19856,10 +19838,10 @@
         <v>3</v>
       </c>
       <c r="AE138" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="AF138" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG138" t="b">
         <v>0</v>
@@ -19951,10 +19933,10 @@
         <v>8</v>
       </c>
       <c r="AE139" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="AF139" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG139" t="b">
         <v>0</v>
@@ -20010,13 +19992,13 @@
         <v>1863</v>
       </c>
       <c r="R140">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="S140">
         <v>0.65</v>
       </c>
       <c r="T140">
-        <v>0.9399999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="U140">
         <v>0.65</v>
@@ -20043,25 +20025,25 @@
         <v>3</v>
       </c>
       <c r="AC140">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD140">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE140" t="s">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="AF140" t="s">
-        <v>2077</v>
+        <v>2069</v>
       </c>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AH140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI140">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AJ140">
         <v>0</v>
@@ -20153,10 +20135,10 @@
         <v>4</v>
       </c>
       <c r="AE141" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="AF141" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG141" t="b">
         <v>0</v>
@@ -20254,10 +20236,10 @@
         <v>8</v>
       </c>
       <c r="AE142" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="AF142" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG142" t="b">
         <v>0</v>
@@ -20346,10 +20328,10 @@
         <v>3</v>
       </c>
       <c r="AE143" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="AF143" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG143" t="b">
         <v>0</v>
@@ -20405,13 +20387,13 @@
         <v>1724</v>
       </c>
       <c r="R144">
-        <v>4.16</v>
+        <v>1.39</v>
       </c>
       <c r="S144">
         <v>1.39</v>
       </c>
       <c r="T144">
-        <v>3.69</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="U144">
         <v>0.6899999999999999</v>
@@ -20429,19 +20411,19 @@
         <v>3</v>
       </c>
       <c r="Z144" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AC144">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD144">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE144" t="s">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="AF144" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG144" t="b">
         <v>0</v>
@@ -20497,13 +20479,13 @@
         <v>1865</v>
       </c>
       <c r="R145">
-        <v>2.35</v>
+        <v>1.56</v>
       </c>
       <c r="S145">
         <v>1.56</v>
       </c>
       <c r="T145">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="U145">
         <v>0.87</v>
@@ -20530,10 +20512,10 @@
         <v>3</v>
       </c>
       <c r="AE145" t="s">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="AF145" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG145" t="b">
         <v>0</v>
@@ -20625,7 +20607,7 @@
         <v>1975</v>
       </c>
       <c r="AF146" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG146" t="b">
         <v>1</v>
@@ -20720,10 +20702,10 @@
         <v>4</v>
       </c>
       <c r="AE147" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="AF147" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG147" t="b">
         <v>0</v>
@@ -20827,7 +20809,7 @@
         <v>1990</v>
       </c>
       <c r="AF148" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG148" t="b">
         <v>0</v>
@@ -20928,10 +20910,10 @@
         <v>2</v>
       </c>
       <c r="AE149" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="AF149" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG149" t="b">
         <v>0</v>
@@ -21032,10 +21014,10 @@
         <v>2</v>
       </c>
       <c r="AE150" t="s">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="AF150" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG150" t="b">
         <v>0</v>
@@ -21136,7 +21118,7 @@
         <v>1975</v>
       </c>
       <c r="AF151" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG151" t="b">
         <v>1</v>
@@ -21219,7 +21201,7 @@
         <v>1975</v>
       </c>
       <c r="AF152" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG152" t="b">
         <v>1</v>
@@ -21311,7 +21293,7 @@
         <v>1975</v>
       </c>
       <c r="AF153" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG153" t="b">
         <v>1</v>
@@ -21403,7 +21385,7 @@
         <v>1975</v>
       </c>
       <c r="AF154" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG154" t="b">
         <v>1</v>
@@ -21483,7 +21465,7 @@
         <v>1978</v>
       </c>
       <c r="AF155" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG155" t="b">
         <v>1</v>
@@ -21578,10 +21560,10 @@
         <v>3</v>
       </c>
       <c r="AE156" t="s">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="AF156" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG156" t="b">
         <v>0</v>
@@ -21679,10 +21661,10 @@
         <v>2</v>
       </c>
       <c r="AE157" t="s">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="AF157" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG157" t="b">
         <v>0</v>
@@ -21780,7 +21762,7 @@
         <v>1975</v>
       </c>
       <c r="AF158" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG158" t="b">
         <v>1</v>
@@ -21872,7 +21854,7 @@
         <v>1975</v>
       </c>
       <c r="AF159" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG159" t="b">
         <v>1</v>
@@ -21964,7 +21946,7 @@
         <v>1975</v>
       </c>
       <c r="AF160" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG160" t="b">
         <v>1</v>
@@ -22020,13 +22002,13 @@
         <v>1871</v>
       </c>
       <c r="R161">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="S161">
         <v>0.87</v>
       </c>
       <c r="T161">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="U161">
         <v>1.09</v>
@@ -22059,10 +22041,10 @@
         <v>3</v>
       </c>
       <c r="AE161" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="AF161" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG161" t="b">
         <v>0</v>
@@ -22121,13 +22103,13 @@
         <v>1872</v>
       </c>
       <c r="R162">
-        <v>1.29</v>
+        <v>0.92</v>
       </c>
       <c r="S162">
         <v>0.92</v>
       </c>
       <c r="T162">
-        <v>1.43</v>
+        <v>0.92</v>
       </c>
       <c r="U162">
         <v>0.92</v>
@@ -22160,10 +22142,10 @@
         <v>3</v>
       </c>
       <c r="AE162" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="AF162" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG162" t="b">
         <v>0</v>
@@ -22264,10 +22246,10 @@
         <v>6</v>
       </c>
       <c r="AE163" t="s">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="AF163" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG163" t="b">
         <v>0</v>
@@ -22365,7 +22347,7 @@
         <v>1975</v>
       </c>
       <c r="AF164" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG164" t="b">
         <v>1</v>
@@ -22457,7 +22439,7 @@
         <v>1975</v>
       </c>
       <c r="AF165" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG165" t="b">
         <v>1</v>
@@ -22546,10 +22528,10 @@
         <v>2</v>
       </c>
       <c r="AE166" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="AF166" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG166" t="b">
         <v>0</v>
@@ -22644,7 +22626,7 @@
         <v>1975</v>
       </c>
       <c r="AF167" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG167" t="b">
         <v>1</v>
@@ -22736,7 +22718,7 @@
         <v>1975</v>
       </c>
       <c r="AF168" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG168" t="b">
         <v>1</v>
@@ -22834,7 +22816,7 @@
         <v>1990</v>
       </c>
       <c r="AF169" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG169" t="b">
         <v>0</v>
@@ -22935,10 +22917,10 @@
         <v>4</v>
       </c>
       <c r="AE170" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="AF170" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG170" t="b">
         <v>0</v>
@@ -23042,10 +23024,10 @@
         <v>9</v>
       </c>
       <c r="AE171" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="AF171" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG171" t="b">
         <v>0</v>
@@ -23149,10 +23131,10 @@
         <v>6</v>
       </c>
       <c r="AE172" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="AF172" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG172" t="b">
         <v>0</v>
@@ -23256,10 +23238,10 @@
         <v>4</v>
       </c>
       <c r="AE173" t="s">
-        <v>2030</v>
+        <v>2026</v>
       </c>
       <c r="AF173" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG173" t="b">
         <v>0</v>
@@ -23357,7 +23339,7 @@
         <v>1975</v>
       </c>
       <c r="AF174" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG174" t="b">
         <v>1</v>
@@ -23413,13 +23395,13 @@
         <v>1879</v>
       </c>
       <c r="R175">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="S175">
         <v>1.61</v>
       </c>
       <c r="T175">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="U175">
         <v>0.8</v>
@@ -23455,7 +23437,7 @@
         <v>1982</v>
       </c>
       <c r="AF175" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG175" t="b">
         <v>0</v>
@@ -23556,7 +23538,7 @@
         <v>1975</v>
       </c>
       <c r="AF176" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG176" t="b">
         <v>1</v>
@@ -23651,7 +23633,7 @@
         <v>1975</v>
       </c>
       <c r="AF177" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG177" t="b">
         <v>1</v>
@@ -23749,10 +23731,10 @@
         <v>8</v>
       </c>
       <c r="AE178" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="AF178" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG178" t="b">
         <v>0</v>
@@ -23856,10 +23838,10 @@
         <v>8</v>
       </c>
       <c r="AE179" t="s">
-        <v>2031</v>
+        <v>2027</v>
       </c>
       <c r="AF179" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG179" t="b">
         <v>0</v>
@@ -23960,10 +23942,10 @@
         <v>3</v>
       </c>
       <c r="AE180" t="s">
-        <v>2032</v>
+        <v>2028</v>
       </c>
       <c r="AF180" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG180" t="b">
         <v>0</v>
@@ -24064,10 +24046,10 @@
         <v>5</v>
       </c>
       <c r="AE181" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="AF181" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -24171,10 +24153,10 @@
         <v>8</v>
       </c>
       <c r="AE182" t="s">
-        <v>2034</v>
+        <v>2030</v>
       </c>
       <c r="AF182" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG182" t="b">
         <v>0</v>
@@ -24236,13 +24218,13 @@
         <v>1886</v>
       </c>
       <c r="R183">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="S183">
         <v>1.29</v>
       </c>
       <c r="T183">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="U183">
         <v>0.64</v>
@@ -24278,7 +24260,7 @@
         <v>1977</v>
       </c>
       <c r="AF183" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -24382,10 +24364,10 @@
         <v>9</v>
       </c>
       <c r="AE184" t="s">
-        <v>2035</v>
+        <v>2031</v>
       </c>
       <c r="AF184" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG184" t="b">
         <v>0</v>
@@ -24489,10 +24471,10 @@
         <v>7</v>
       </c>
       <c r="AE185" t="s">
-        <v>2036</v>
+        <v>2032</v>
       </c>
       <c r="AF185" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG185" t="b">
         <v>0</v>
@@ -24596,7 +24578,7 @@
         <v>1975</v>
       </c>
       <c r="AF186" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG186" t="b">
         <v>1</v>
@@ -24694,10 +24676,10 @@
         <v>13</v>
       </c>
       <c r="AE187" t="s">
-        <v>2037</v>
+        <v>2033</v>
       </c>
       <c r="AF187" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG187" t="b">
         <v>0</v>
@@ -24762,13 +24744,13 @@
         <v>1890</v>
       </c>
       <c r="R188">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="S188">
         <v>1.61</v>
       </c>
       <c r="T188">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="U188">
         <v>0.8</v>
@@ -24795,25 +24777,25 @@
         <v>4</v>
       </c>
       <c r="AC188">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD188">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE188" t="s">
-        <v>1977</v>
+        <v>2034</v>
       </c>
       <c r="AF188" t="s">
-        <v>2078</v>
+        <v>2071</v>
       </c>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AH188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ188">
         <v>2</v>
@@ -24905,7 +24887,7 @@
         <v>1975</v>
       </c>
       <c r="AF189" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG189" t="b">
         <v>1</v>
@@ -25003,10 +24985,10 @@
         <v>2</v>
       </c>
       <c r="AE190" t="s">
-        <v>2038</v>
+        <v>2035</v>
       </c>
       <c r="AF190" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG190" t="b">
         <v>0</v>
@@ -25071,13 +25053,13 @@
         <v>1892</v>
       </c>
       <c r="R191">
-        <v>1.87</v>
+        <v>1.13</v>
       </c>
       <c r="S191">
         <v>1.13</v>
       </c>
       <c r="T191">
-        <v>1.56</v>
+        <v>0.8</v>
       </c>
       <c r="U191">
         <v>0.8</v>
@@ -25095,7 +25077,7 @@
         <v>2.25</v>
       </c>
       <c r="Z191" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA191">
         <v>2</v>
@@ -25104,25 +25086,25 @@
         <v>4</v>
       </c>
       <c r="AC191">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE191" t="s">
-        <v>2039</v>
+        <v>1977</v>
       </c>
       <c r="AF191" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AH191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ191">
         <v>2</v>
@@ -25214,7 +25196,7 @@
         <v>1975</v>
       </c>
       <c r="AF192" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG192" t="b">
         <v>1</v>
@@ -25309,7 +25291,7 @@
         <v>1975</v>
       </c>
       <c r="AF193" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG193" t="b">
         <v>1</v>
@@ -25404,7 +25386,7 @@
         <v>1975</v>
       </c>
       <c r="AF194" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG194" t="b">
         <v>1</v>
@@ -25505,7 +25487,7 @@
         <v>1987</v>
       </c>
       <c r="AF195" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG195" t="b">
         <v>0</v>
@@ -25606,10 +25588,10 @@
         <v>5</v>
       </c>
       <c r="AE196" t="s">
-        <v>2039</v>
+        <v>2034</v>
       </c>
       <c r="AF196" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG196" t="b">
         <v>0</v>
@@ -25713,7 +25695,7 @@
         <v>1988</v>
       </c>
       <c r="AF197" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG197" t="b">
         <v>0</v>
@@ -25814,10 +25796,10 @@
         <v>9</v>
       </c>
       <c r="AE198" t="s">
-        <v>2040</v>
+        <v>2036</v>
       </c>
       <c r="AF198" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG198" t="b">
         <v>0</v>
@@ -25915,7 +25897,7 @@
         <v>1975</v>
       </c>
       <c r="AF199" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG199" t="b">
         <v>1</v>
@@ -26013,7 +25995,7 @@
         <v>1977</v>
       </c>
       <c r="AF200" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG200" t="b">
         <v>0</v>
@@ -26075,13 +26057,13 @@
         <v>1734</v>
       </c>
       <c r="R201">
-        <v>0.97</v>
+        <v>1.45</v>
       </c>
       <c r="S201">
         <v>1.45</v>
       </c>
       <c r="T201">
-        <v>0.66</v>
+        <v>1.16</v>
       </c>
       <c r="U201">
         <v>1.16</v>
@@ -26114,10 +26096,10 @@
         <v>4</v>
       </c>
       <c r="AE201" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="AF201" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG201" t="b">
         <v>0</v>
@@ -26215,7 +26197,7 @@
         <v>1975</v>
       </c>
       <c r="AF202" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG202" t="b">
         <v>1</v>
@@ -26301,7 +26283,7 @@
         <v>1975</v>
       </c>
       <c r="AF203" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG203" t="b">
         <v>1</v>
@@ -26393,7 +26375,7 @@
         <v>1975</v>
       </c>
       <c r="AF204" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG204" t="b">
         <v>1</v>
@@ -26488,7 +26470,7 @@
         <v>1975</v>
       </c>
       <c r="AF205" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG205" t="b">
         <v>1</v>
@@ -26583,7 +26565,7 @@
         <v>1977</v>
       </c>
       <c r="AF206" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG206" t="b">
         <v>0</v>
@@ -26648,7 +26630,7 @@
         <v>1901</v>
       </c>
       <c r="R207">
-        <v>20.76</v>
+        <v>13.84</v>
       </c>
       <c r="S207">
         <v>6.92</v>
@@ -26681,25 +26663,25 @@
         <v>8</v>
       </c>
       <c r="AC207">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AD207">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AE207" t="s">
-        <v>2041</v>
+        <v>2037</v>
       </c>
       <c r="AF207" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG207" t="b">
         <v>0</v>
       </c>
       <c r="AH207">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AI207">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AJ207">
         <v>2</v>
@@ -26788,10 +26770,10 @@
         <v>2</v>
       </c>
       <c r="AE208" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="AF208" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG208" t="b">
         <v>0</v>
@@ -26889,7 +26871,7 @@
         <v>1975</v>
       </c>
       <c r="AF209" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG209" t="b">
         <v>1</v>
@@ -26981,7 +26963,7 @@
         <v>1975</v>
       </c>
       <c r="AF210" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG210" t="b">
         <v>1</v>
@@ -27073,7 +27055,7 @@
         <v>1975</v>
       </c>
       <c r="AF211" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG211" t="b">
         <v>1</v>
@@ -27171,10 +27153,10 @@
         <v>4</v>
       </c>
       <c r="AE212" t="s">
-        <v>2042</v>
+        <v>2038</v>
       </c>
       <c r="AF212" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG212" t="b">
         <v>0</v>
@@ -27275,10 +27257,10 @@
         <v>5</v>
       </c>
       <c r="AE213" t="s">
-        <v>2043</v>
+        <v>2039</v>
       </c>
       <c r="AF213" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG213" t="b">
         <v>0</v>
@@ -27340,7 +27322,7 @@
         <v>1756</v>
       </c>
       <c r="R214">
-        <v>5.95</v>
+        <v>5.79</v>
       </c>
       <c r="S214">
         <v>2.9</v>
@@ -27379,10 +27361,10 @@
         <v>11</v>
       </c>
       <c r="AE214" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="AF214" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG214" t="b">
         <v>0</v>
@@ -27483,10 +27465,10 @@
         <v>9</v>
       </c>
       <c r="AE215" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="AF215" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG215" t="b">
         <v>0</v>
@@ -27548,7 +27530,7 @@
         <v>1756</v>
       </c>
       <c r="R216">
-        <v>5.95</v>
+        <v>5.79</v>
       </c>
       <c r="S216">
         <v>2.9</v>
@@ -27587,10 +27569,10 @@
         <v>11</v>
       </c>
       <c r="AE216" t="s">
-        <v>2044</v>
+        <v>2040</v>
       </c>
       <c r="AF216" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG216" t="b">
         <v>0</v>
@@ -27691,10 +27673,10 @@
         <v>9</v>
       </c>
       <c r="AE217" t="s">
-        <v>2045</v>
+        <v>2041</v>
       </c>
       <c r="AF217" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG217" t="b">
         <v>0</v>
@@ -27798,10 +27780,10 @@
         <v>3</v>
       </c>
       <c r="AE218" t="s">
-        <v>2046</v>
+        <v>2042</v>
       </c>
       <c r="AF218" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG218" t="b">
         <v>0</v>
@@ -27902,10 +27884,10 @@
         <v>6</v>
       </c>
       <c r="AE219" t="s">
-        <v>2047</v>
+        <v>2043</v>
       </c>
       <c r="AF219" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG219" t="b">
         <v>0</v>
@@ -28003,7 +27985,7 @@
         <v>1975</v>
       </c>
       <c r="AF220" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG220" t="b">
         <v>1</v>
@@ -28095,7 +28077,7 @@
         <v>1975</v>
       </c>
       <c r="AF221" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG221" t="b">
         <v>1</v>
@@ -28187,7 +28169,7 @@
         <v>1975</v>
       </c>
       <c r="AF222" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG222" t="b">
         <v>1</v>
@@ -28279,7 +28261,7 @@
         <v>1975</v>
       </c>
       <c r="AF223" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG223" t="b">
         <v>1</v>
@@ -28365,7 +28347,7 @@
         <v>1975</v>
       </c>
       <c r="AF224" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG224" t="b">
         <v>1</v>
@@ -28460,10 +28442,10 @@
         <v>16</v>
       </c>
       <c r="AE225" t="s">
-        <v>2048</v>
+        <v>2044</v>
       </c>
       <c r="AF225" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG225" t="b">
         <v>0</v>
@@ -28561,7 +28543,7 @@
         <v>1975</v>
       </c>
       <c r="AF226" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG226" t="b">
         <v>1</v>
@@ -28653,7 +28635,7 @@
         <v>1975</v>
       </c>
       <c r="AF227" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG227" t="b">
         <v>1</v>
@@ -28745,7 +28727,7 @@
         <v>1975</v>
       </c>
       <c r="AF228" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG228" t="b">
         <v>1</v>
@@ -28837,7 +28819,7 @@
         <v>1975</v>
       </c>
       <c r="AF229" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG229" t="b">
         <v>1</v>
@@ -28929,10 +28911,10 @@
         <v>4</v>
       </c>
       <c r="AE230" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="AF230" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG230" t="b">
         <v>0</v>
@@ -29030,7 +29012,7 @@
         <v>1975</v>
       </c>
       <c r="AF231" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG231" t="b">
         <v>1</v>
@@ -29122,7 +29104,7 @@
         <v>1975</v>
       </c>
       <c r="AF232" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG232" t="b">
         <v>1</v>
@@ -29217,10 +29199,10 @@
         <v>4</v>
       </c>
       <c r="AE233" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="AF233" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG233" t="b">
         <v>0</v>
@@ -29318,10 +29300,10 @@
         <v>4</v>
       </c>
       <c r="AE234" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="AF234" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG234" t="b">
         <v>0</v>
@@ -29419,7 +29401,7 @@
         <v>1975</v>
       </c>
       <c r="AF235" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG235" t="b">
         <v>1</v>
@@ -29511,7 +29493,7 @@
         <v>1975</v>
       </c>
       <c r="AF236" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG236" t="b">
         <v>1</v>
@@ -29603,7 +29585,7 @@
         <v>1975</v>
       </c>
       <c r="AF237" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG237" t="b">
         <v>1</v>
@@ -29695,7 +29677,7 @@
         <v>1975</v>
       </c>
       <c r="AF238" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG238" t="b">
         <v>1</v>
@@ -29787,7 +29769,7 @@
         <v>1975</v>
       </c>
       <c r="AF239" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG239" t="b">
         <v>1</v>
@@ -29879,7 +29861,7 @@
         <v>1975</v>
       </c>
       <c r="AF240" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG240" t="b">
         <v>1</v>
@@ -29968,10 +29950,10 @@
         <v>4</v>
       </c>
       <c r="AE241" t="s">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="AF241" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG241" t="b">
         <v>0</v>
@@ -30051,7 +30033,7 @@
         <v>1978</v>
       </c>
       <c r="AF242" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG242" t="b">
         <v>1</v>
@@ -30131,7 +30113,7 @@
         <v>1978</v>
       </c>
       <c r="AF243" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG243" t="b">
         <v>1</v>
@@ -30223,7 +30205,7 @@
         <v>1975</v>
       </c>
       <c r="AF244" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG244" t="b">
         <v>1</v>
@@ -30315,7 +30297,7 @@
         <v>1975</v>
       </c>
       <c r="AF245" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG245" t="b">
         <v>1</v>
@@ -30410,10 +30392,10 @@
         <v>6</v>
       </c>
       <c r="AE246" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="AF246" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG246" t="b">
         <v>0</v>
@@ -30511,10 +30493,10 @@
         <v>2</v>
       </c>
       <c r="AE247" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="AF247" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG247" t="b">
         <v>0</v>
@@ -30612,7 +30594,7 @@
         <v>1975</v>
       </c>
       <c r="AF248" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG248" t="b">
         <v>1</v>
@@ -30701,7 +30683,7 @@
         <v>1975</v>
       </c>
       <c r="AF249" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG249" t="b">
         <v>1</v>
@@ -30790,7 +30772,7 @@
         <v>1975</v>
       </c>
       <c r="AF250" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG250" t="b">
         <v>1</v>
@@ -30879,7 +30861,7 @@
         <v>1975</v>
       </c>
       <c r="AF251" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG251" t="b">
         <v>1</v>
@@ -30974,10 +30956,10 @@
         <v>26</v>
       </c>
       <c r="AE252" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="AF252" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG252" t="b">
         <v>0</v>
@@ -31039,13 +31021,13 @@
         <v>1783</v>
       </c>
       <c r="R253">
-        <v>6.73</v>
+        <v>2.24</v>
       </c>
       <c r="S253">
         <v>2.24</v>
       </c>
       <c r="T253">
-        <v>11.46</v>
+        <v>2.24</v>
       </c>
       <c r="U253">
         <v>2.24</v>
@@ -31063,7 +31045,7 @@
         <v>2</v>
       </c>
       <c r="Z253" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="AA253">
         <v>0</v>
@@ -31072,25 +31054,25 @@
         <v>1</v>
       </c>
       <c r="AC253">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD253">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AE253" t="s">
-        <v>2054</v>
+        <v>1990</v>
       </c>
       <c r="AF253" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
       <c r="AH253">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI253">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ253">
         <v>4</v>
@@ -31179,10 +31161,10 @@
         <v>5</v>
       </c>
       <c r="AE254" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="AF254" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG254" t="b">
         <v>0</v>
@@ -31280,7 +31262,7 @@
         <v>1975</v>
       </c>
       <c r="AF255" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG255" t="b">
         <v>1</v>
@@ -31375,7 +31357,7 @@
         <v>1975</v>
       </c>
       <c r="AF256" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG256" t="b">
         <v>1</v>
@@ -31467,7 +31449,7 @@
         <v>1975</v>
       </c>
       <c r="AF257" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG257" t="b">
         <v>1</v>
@@ -31559,7 +31541,7 @@
         <v>1975</v>
       </c>
       <c r="AF258" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG258" t="b">
         <v>1</v>
@@ -31651,7 +31633,7 @@
         <v>1975</v>
       </c>
       <c r="AF259" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG259" t="b">
         <v>1</v>
@@ -31743,7 +31725,7 @@
         <v>1975</v>
       </c>
       <c r="AF260" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG260" t="b">
         <v>1</v>
@@ -31835,7 +31817,7 @@
         <v>1975</v>
       </c>
       <c r="AF261" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG261" t="b">
         <v>1</v>
@@ -31927,7 +31909,7 @@
         <v>1975</v>
       </c>
       <c r="AF262" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG262" t="b">
         <v>1</v>
@@ -32022,7 +32004,7 @@
         <v>1975</v>
       </c>
       <c r="AF263" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG263" t="b">
         <v>1</v>
@@ -32117,10 +32099,10 @@
         <v>2</v>
       </c>
       <c r="AE264" t="s">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="AF264" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG264" t="b">
         <v>0</v>
@@ -32218,7 +32200,7 @@
         <v>1975</v>
       </c>
       <c r="AF265" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG265" t="b">
         <v>1</v>
@@ -32310,7 +32292,7 @@
         <v>1975</v>
       </c>
       <c r="AF266" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG266" t="b">
         <v>1</v>
@@ -32402,7 +32384,7 @@
         <v>1975</v>
       </c>
       <c r="AF267" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG267" t="b">
         <v>1</v>
@@ -32494,7 +32476,7 @@
         <v>1975</v>
       </c>
       <c r="AF268" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG268" t="b">
         <v>1</v>
@@ -32586,7 +32568,7 @@
         <v>1975</v>
       </c>
       <c r="AF269" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG269" t="b">
         <v>1</v>
@@ -32672,7 +32654,7 @@
         <v>1975</v>
       </c>
       <c r="AF270" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG270" t="b">
         <v>1</v>
@@ -32752,7 +32734,7 @@
         <v>1978</v>
       </c>
       <c r="AF271" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG271" t="b">
         <v>1</v>
@@ -32832,7 +32814,7 @@
         <v>1978</v>
       </c>
       <c r="AF272" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG272" t="b">
         <v>1</v>
@@ -32930,7 +32912,7 @@
         <v>1993</v>
       </c>
       <c r="AF273" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG273" t="b">
         <v>0</v>
@@ -33028,7 +33010,7 @@
         <v>1975</v>
       </c>
       <c r="AF274" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG274" t="b">
         <v>1</v>
@@ -33126,10 +33108,10 @@
         <v>9</v>
       </c>
       <c r="AE275" t="s">
-        <v>2056</v>
+        <v>2051</v>
       </c>
       <c r="AF275" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG275" t="b">
         <v>0</v>
@@ -33227,7 +33209,7 @@
         <v>1975</v>
       </c>
       <c r="AF276" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG276" t="b">
         <v>1</v>
@@ -33322,7 +33304,7 @@
         <v>1975</v>
       </c>
       <c r="AF277" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG277" t="b">
         <v>1</v>
@@ -33414,7 +33396,7 @@
         <v>1975</v>
       </c>
       <c r="AF278" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG278" t="b">
         <v>1</v>
@@ -33509,10 +33491,10 @@
         <v>3</v>
       </c>
       <c r="AE279" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="AF279" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG279" t="b">
         <v>0</v>
@@ -33610,7 +33592,7 @@
         <v>1975</v>
       </c>
       <c r="AF280" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG280" t="b">
         <v>1</v>
@@ -33711,7 +33693,7 @@
         <v>1976</v>
       </c>
       <c r="AF281" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG281" t="b">
         <v>0</v>
@@ -33773,13 +33755,13 @@
         <v>1926</v>
       </c>
       <c r="R282">
-        <v>2.9</v>
+        <v>0.97</v>
       </c>
       <c r="S282">
         <v>0.97</v>
       </c>
       <c r="T282">
-        <v>7.24</v>
+        <v>0.8</v>
       </c>
       <c r="U282">
         <v>0.8</v>
@@ -33794,7 +33776,7 @@
         <v>33</v>
       </c>
       <c r="Z282" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="AA282">
         <v>2</v>
@@ -33809,10 +33791,10 @@
         <v>3</v>
       </c>
       <c r="AE282" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="AF282" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG282" t="b">
         <v>0</v>
@@ -33874,13 +33856,13 @@
         <v>1927</v>
       </c>
       <c r="R283">
-        <v>3.86</v>
+        <v>1.29</v>
       </c>
       <c r="S283">
         <v>1.29</v>
       </c>
       <c r="T283">
-        <v>2.73</v>
+        <v>0.8</v>
       </c>
       <c r="U283">
         <v>0.8</v>
@@ -33895,7 +33877,7 @@
         <v>17</v>
       </c>
       <c r="Z283" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA283">
         <v>2</v>
@@ -33904,25 +33886,25 @@
         <v>10</v>
       </c>
       <c r="AC283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD283">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE283" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="AF283" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG283" t="b">
         <v>0</v>
       </c>
       <c r="AH283">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AI283">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="AJ283">
         <v>9</v>
@@ -34014,10 +33996,10 @@
         <v>6</v>
       </c>
       <c r="AE284" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="AF284" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG284" t="b">
         <v>0</v>
@@ -34115,7 +34097,7 @@
         <v>1975</v>
       </c>
       <c r="AF285" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG285" t="b">
         <v>1</v>
@@ -34213,7 +34195,7 @@
         <v>1976</v>
       </c>
       <c r="AF286" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG286" t="b">
         <v>0</v>
@@ -34314,10 +34296,10 @@
         <v>3</v>
       </c>
       <c r="AE287" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="AF287" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG287" t="b">
         <v>0</v>
@@ -34418,10 +34400,10 @@
         <v>5</v>
       </c>
       <c r="AE288" t="s">
-        <v>2060</v>
+        <v>2055</v>
       </c>
       <c r="AF288" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG288" t="b">
         <v>0</v>
@@ -34522,7 +34504,7 @@
         <v>1975</v>
       </c>
       <c r="AF289" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG289" t="b">
         <v>1</v>
@@ -34617,10 +34599,10 @@
         <v>4</v>
       </c>
       <c r="AE290" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="AF290" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG290" t="b">
         <v>0</v>
@@ -34721,10 +34703,10 @@
         <v>9</v>
       </c>
       <c r="AE291" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="AF291" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG291" t="b">
         <v>0</v>
@@ -34828,10 +34810,10 @@
         <v>35</v>
       </c>
       <c r="AE292" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="AF292" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG292" t="b">
         <v>0</v>
@@ -34932,10 +34914,10 @@
         <v>3</v>
       </c>
       <c r="AE293" t="s">
-        <v>2064</v>
+        <v>2059</v>
       </c>
       <c r="AF293" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG293" t="b">
         <v>0</v>
@@ -35033,7 +35015,7 @@
         <v>1975</v>
       </c>
       <c r="AF294" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG294" t="b">
         <v>1</v>
@@ -35128,7 +35110,7 @@
         <v>1975</v>
       </c>
       <c r="AF295" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG295" t="b">
         <v>1</v>
@@ -35223,7 +35205,7 @@
         <v>1975</v>
       </c>
       <c r="AF296" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG296" t="b">
         <v>1</v>
@@ -35318,10 +35300,10 @@
         <v>3</v>
       </c>
       <c r="AE297" t="s">
-        <v>2057</v>
+        <v>2052</v>
       </c>
       <c r="AF297" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG297" t="b">
         <v>0</v>
@@ -35419,7 +35401,7 @@
         <v>1975</v>
       </c>
       <c r="AF298" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG298" t="b">
         <v>1</v>
@@ -35517,10 +35499,10 @@
         <v>7</v>
       </c>
       <c r="AE299" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="AF299" t="s">
-        <v>2079</v>
+        <v>2073</v>
       </c>
       <c r="AG299" t="b">
         <v>0</v>
@@ -35618,7 +35600,7 @@
         <v>1975</v>
       </c>
       <c r="AF300" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG300" t="b">
         <v>1</v>
@@ -35716,7 +35698,7 @@
         <v>1973</v>
       </c>
       <c r="AF301" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG301" t="b">
         <v>0</v>
@@ -35814,7 +35796,7 @@
         <v>1975</v>
       </c>
       <c r="AF302" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG302" t="b">
         <v>1</v>
@@ -35906,7 +35888,7 @@
         <v>1975</v>
       </c>
       <c r="AF303" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG303" t="b">
         <v>1</v>
@@ -35998,7 +35980,7 @@
         <v>1975</v>
       </c>
       <c r="AF304" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG304" t="b">
         <v>1</v>
@@ -36078,7 +36060,7 @@
         <v>1978</v>
       </c>
       <c r="AF305" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG305" t="b">
         <v>1</v>
@@ -36164,10 +36146,10 @@
         <v>2</v>
       </c>
       <c r="AE306" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="AF306" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG306" t="b">
         <v>0</v>
@@ -36256,10 +36238,10 @@
         <v>8</v>
       </c>
       <c r="AE307" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="AF307" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG307" t="b">
         <v>0</v>
@@ -36339,7 +36321,7 @@
         <v>1978</v>
       </c>
       <c r="AF308" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG308" t="b">
         <v>1</v>
@@ -36419,7 +36401,7 @@
         <v>1978</v>
       </c>
       <c r="AF309" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG309" t="b">
         <v>1</v>
@@ -36511,10 +36493,10 @@
         <v>4</v>
       </c>
       <c r="AE310" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="AF310" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG310" t="b">
         <v>0</v>
@@ -36612,7 +36594,7 @@
         <v>1974</v>
       </c>
       <c r="AF311" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG311" t="b">
         <v>0</v>
@@ -36698,7 +36680,7 @@
         <v>1978</v>
       </c>
       <c r="AF312" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG312" t="b">
         <v>1</v>
@@ -36781,7 +36763,7 @@
         <v>1978</v>
       </c>
       <c r="AF313" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG313" t="b">
         <v>1</v>
@@ -36861,7 +36843,7 @@
         <v>1978</v>
       </c>
       <c r="AF314" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG314" t="b">
         <v>1</v>
@@ -36941,7 +36923,7 @@
         <v>1978</v>
       </c>
       <c r="AF315" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG315" t="b">
         <v>1</v>
@@ -37021,7 +37003,7 @@
         <v>1978</v>
       </c>
       <c r="AF316" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG316" t="b">
         <v>1</v>
@@ -37101,7 +37083,7 @@
         <v>1978</v>
       </c>
       <c r="AF317" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG317" t="b">
         <v>1</v>
@@ -37181,7 +37163,7 @@
         <v>1978</v>
       </c>
       <c r="AF318" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG318" t="b">
         <v>1</v>
@@ -37270,10 +37252,10 @@
         <v>9</v>
       </c>
       <c r="AE319" t="s">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="AF319" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG319" t="b">
         <v>0</v>
@@ -37359,10 +37341,10 @@
         <v>2</v>
       </c>
       <c r="AE320" t="s">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="AF320" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG320" t="b">
         <v>0</v>
@@ -37454,10 +37436,10 @@
         <v>2</v>
       </c>
       <c r="AE321" t="s">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="AF321" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG321" t="b">
         <v>0</v>
@@ -37561,7 +37543,7 @@
         <v>1977</v>
       </c>
       <c r="AF322" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG322" t="b">
         <v>0</v>
@@ -37659,7 +37641,7 @@
         <v>1975</v>
       </c>
       <c r="AF323" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG323" t="b">
         <v>1</v>
@@ -37754,7 +37736,7 @@
         <v>1975</v>
       </c>
       <c r="AF324" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG324" t="b">
         <v>1</v>
@@ -37810,13 +37792,13 @@
         <v>1796</v>
       </c>
       <c r="R325">
-        <v>2.26</v>
+        <v>1.28</v>
       </c>
       <c r="S325">
         <v>1.28</v>
       </c>
       <c r="T325">
-        <v>1.25</v>
+        <v>0.64</v>
       </c>
       <c r="U325">
         <v>0.64</v>
@@ -37843,25 +37825,25 @@
         <v>4</v>
       </c>
       <c r="AC325">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD325">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE325" t="s">
-        <v>1982</v>
+        <v>2012</v>
       </c>
       <c r="AF325" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG325" t="b">
         <v>0</v>
       </c>
       <c r="AH325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI325">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ325">
         <v>3</v>
@@ -37950,7 +37932,7 @@
         <v>1975</v>
       </c>
       <c r="AF326" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG326" t="b">
         <v>1</v>
@@ -38048,10 +38030,10 @@
         <v>6</v>
       </c>
       <c r="AE327" t="s">
-        <v>2068</v>
+        <v>2063</v>
       </c>
       <c r="AF327" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG327" t="b">
         <v>0</v>
@@ -38152,10 +38134,10 @@
         <v>6</v>
       </c>
       <c r="AE328" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="AF328" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -38259,10 +38241,10 @@
         <v>4</v>
       </c>
       <c r="AE329" t="s">
-        <v>2011</v>
+        <v>2065</v>
       </c>
       <c r="AF329" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG329" t="b">
         <v>0</v>
@@ -38363,10 +38345,10 @@
         <v>7</v>
       </c>
       <c r="AE330" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
       <c r="AF330" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG330" t="b">
         <v>0</v>
@@ -38425,13 +38407,13 @@
         <v>1943</v>
       </c>
       <c r="R331">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="S331">
         <v>0.6</v>
       </c>
       <c r="T331">
-        <v>1.69</v>
+        <v>0.48</v>
       </c>
       <c r="U331">
         <v>0.48</v>
@@ -38449,7 +38431,7 @@
         <v>2.33</v>
       </c>
       <c r="Z331" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA331">
         <v>0</v>
@@ -38458,25 +38440,25 @@
         <v>2</v>
       </c>
       <c r="AC331">
+        <v>1</v>
+      </c>
+      <c r="AD331">
         <v>3</v>
       </c>
-      <c r="AD331">
-        <v>5</v>
-      </c>
       <c r="AE331" t="s">
-        <v>1988</v>
+        <v>2020</v>
       </c>
       <c r="AF331" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG331" t="b">
         <v>0</v>
       </c>
       <c r="AH331">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI331">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ331">
         <v>0</v>
@@ -38556,7 +38538,7 @@
         <v>1975</v>
       </c>
       <c r="AF332" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG332" t="b">
         <v>1</v>
@@ -38648,7 +38630,7 @@
         <v>1975</v>
       </c>
       <c r="AF333" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG333" t="b">
         <v>1</v>
@@ -38740,7 +38722,7 @@
         <v>1975</v>
       </c>
       <c r="AF334" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG334" t="b">
         <v>1</v>
@@ -38832,7 +38814,7 @@
         <v>1975</v>
       </c>
       <c r="AF335" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG335" t="b">
         <v>1</v>
@@ -38921,7 +38903,7 @@
         <v>1975</v>
       </c>
       <c r="AF336" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG336" t="b">
         <v>1</v>
@@ -39013,7 +38995,7 @@
         <v>1975</v>
       </c>
       <c r="AF337" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG337" t="b">
         <v>1</v>
@@ -39105,7 +39087,7 @@
         <v>1975</v>
       </c>
       <c r="AF338" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG338" t="b">
         <v>1</v>
@@ -39194,7 +39176,7 @@
         <v>1975</v>
       </c>
       <c r="AF339" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG339" t="b">
         <v>1</v>
@@ -39283,7 +39265,7 @@
         <v>1975</v>
       </c>
       <c r="AF340" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG340" t="b">
         <v>1</v>
@@ -39372,7 +39354,7 @@
         <v>1975</v>
       </c>
       <c r="AF341" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG341" t="b">
         <v>1</v>
@@ -39461,7 +39443,7 @@
         <v>1975</v>
       </c>
       <c r="AF342" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG342" t="b">
         <v>1</v>
@@ -39559,7 +39541,7 @@
         <v>1990</v>
       </c>
       <c r="AF343" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG343" t="b">
         <v>0</v>
@@ -39654,7 +39636,7 @@
         <v>1975</v>
       </c>
       <c r="AF344" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG344" t="b">
         <v>1</v>
@@ -39743,7 +39725,7 @@
         <v>1975</v>
       </c>
       <c r="AF345" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG345" t="b">
         <v>1</v>
@@ -39832,7 +39814,7 @@
         <v>1975</v>
       </c>
       <c r="AF346" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG346" t="b">
         <v>1</v>
@@ -39921,7 +39903,7 @@
         <v>1975</v>
       </c>
       <c r="AF347" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG347" t="b">
         <v>1</v>
@@ -40010,7 +39992,7 @@
         <v>1975</v>
       </c>
       <c r="AF348" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG348" t="b">
         <v>1</v>
@@ -40099,7 +40081,7 @@
         <v>1975</v>
       </c>
       <c r="AF349" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG349" t="b">
         <v>1</v>
@@ -40188,7 +40170,7 @@
         <v>1975</v>
       </c>
       <c r="AF350" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG350" t="b">
         <v>1</v>
@@ -40280,7 +40262,7 @@
         <v>1975</v>
       </c>
       <c r="AF351" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG351" t="b">
         <v>1</v>
@@ -40372,7 +40354,7 @@
         <v>1975</v>
       </c>
       <c r="AF352" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG352" t="b">
         <v>1</v>
@@ -40461,7 +40443,7 @@
         <v>1975</v>
       </c>
       <c r="AF353" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG353" t="b">
         <v>1</v>
@@ -40553,7 +40535,7 @@
         <v>1975</v>
       </c>
       <c r="AF354" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG354" t="b">
         <v>1</v>
@@ -40648,7 +40630,7 @@
         <v>1975</v>
       </c>
       <c r="AF355" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG355" t="b">
         <v>1</v>
@@ -40743,7 +40725,7 @@
         <v>1975</v>
       </c>
       <c r="AF356" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG356" t="b">
         <v>1</v>
@@ -40832,7 +40814,7 @@
         <v>1975</v>
       </c>
       <c r="AF357" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG357" t="b">
         <v>1</v>
@@ -40921,7 +40903,7 @@
         <v>1975</v>
       </c>
       <c r="AF358" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG358" t="b">
         <v>1</v>
@@ -40974,13 +40956,13 @@
         <v>1783</v>
       </c>
       <c r="R359">
-        <v>7.09</v>
+        <v>4.62</v>
       </c>
       <c r="S359">
         <v>4.62</v>
       </c>
       <c r="T359">
-        <v>5.63</v>
+        <v>3.08</v>
       </c>
       <c r="U359">
         <v>3.08</v>
@@ -40998,7 +40980,7 @@
         <v>3</v>
       </c>
       <c r="Z359" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="AA359">
         <v>1</v>
@@ -41007,25 +40989,25 @@
         <v>2</v>
       </c>
       <c r="AC359">
+        <v>3</v>
+      </c>
+      <c r="AD359">
         <v>5</v>
       </c>
-      <c r="AD359">
-        <v>7</v>
-      </c>
       <c r="AE359" t="s">
+        <v>1981</v>
+      </c>
+      <c r="AF359" t="s">
         <v>2071</v>
       </c>
-      <c r="AF359" t="s">
-        <v>2077</v>
-      </c>
       <c r="AG359" t="b">
         <v>0</v>
       </c>
       <c r="AH359">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI359">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ359">
         <v>3</v>
@@ -41111,7 +41093,7 @@
         <v>1975</v>
       </c>
       <c r="AF360" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG360" t="b">
         <v>1</v>
@@ -41206,7 +41188,7 @@
         <v>1975</v>
       </c>
       <c r="AF361" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG361" t="b">
         <v>1</v>
@@ -41298,7 +41280,7 @@
         <v>1975</v>
       </c>
       <c r="AF362" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG362" t="b">
         <v>1</v>
@@ -41390,7 +41372,7 @@
         <v>1975</v>
       </c>
       <c r="AF363" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG363" t="b">
         <v>1</v>
@@ -41482,7 +41464,7 @@
         <v>1975</v>
       </c>
       <c r="AF364" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG364" t="b">
         <v>1</v>
@@ -41580,7 +41562,7 @@
         <v>1977</v>
       </c>
       <c r="AF365" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG365" t="b">
         <v>0</v>
@@ -41681,7 +41663,7 @@
         <v>1975</v>
       </c>
       <c r="AF366" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG366" t="b">
         <v>1</v>
@@ -41773,7 +41755,7 @@
         <v>1975</v>
       </c>
       <c r="AF367" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG367" t="b">
         <v>1</v>
@@ -41865,7 +41847,7 @@
         <v>1975</v>
       </c>
       <c r="AF368" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG368" t="b">
         <v>1</v>
@@ -41957,7 +41939,7 @@
         <v>1975</v>
       </c>
       <c r="AF369" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG369" t="b">
         <v>1</v>
@@ -42049,7 +42031,7 @@
         <v>1975</v>
       </c>
       <c r="AF370" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG370" t="b">
         <v>1</v>
@@ -42144,7 +42126,7 @@
         <v>1982</v>
       </c>
       <c r="AF371" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG371" t="b">
         <v>0</v>
@@ -42242,7 +42224,7 @@
         <v>1975</v>
       </c>
       <c r="AF372" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG372" t="b">
         <v>1</v>
@@ -42334,7 +42316,7 @@
         <v>1975</v>
       </c>
       <c r="AF373" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG373" t="b">
         <v>1</v>
@@ -42417,7 +42399,7 @@
         <v>1975</v>
       </c>
       <c r="AF374" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG374" t="b">
         <v>1</v>
@@ -42500,7 +42482,7 @@
         <v>1975</v>
       </c>
       <c r="AF375" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG375" t="b">
         <v>1</v>
@@ -42592,7 +42574,7 @@
         <v>1975</v>
       </c>
       <c r="AF376" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG376" t="b">
         <v>1</v>
@@ -42684,7 +42666,7 @@
         <v>1975</v>
       </c>
       <c r="AF377" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG377" t="b">
         <v>1</v>
@@ -42779,7 +42761,7 @@
         <v>1975</v>
       </c>
       <c r="AF378" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG378" t="b">
         <v>1</v>
@@ -42871,7 +42853,7 @@
         <v>1975</v>
       </c>
       <c r="AF379" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG379" t="b">
         <v>1</v>
@@ -42963,7 +42945,7 @@
         <v>1975</v>
       </c>
       <c r="AF380" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG380" t="b">
         <v>1</v>
@@ -43058,10 +43040,10 @@
         <v>4</v>
       </c>
       <c r="AE381" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="AF381" t="s">
-        <v>2075</v>
+        <v>2069</v>
       </c>
       <c r="AG381" t="b">
         <v>0</v>
@@ -43150,7 +43132,7 @@
         <v>1975</v>
       </c>
       <c r="AF382" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG382" t="b">
         <v>1</v>
@@ -43233,7 +43215,7 @@
         <v>1975</v>
       </c>
       <c r="AF383" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG383" t="b">
         <v>1</v>
@@ -43322,7 +43304,7 @@
         <v>1975</v>
       </c>
       <c r="AF384" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG384" t="b">
         <v>1</v>
@@ -43411,7 +43393,7 @@
         <v>1975</v>
       </c>
       <c r="AF385" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG385" t="b">
         <v>1</v>
@@ -43500,7 +43482,7 @@
         <v>1975</v>
       </c>
       <c r="AF386" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG386" t="b">
         <v>1</v>
@@ -43592,7 +43574,7 @@
         <v>1975</v>
       </c>
       <c r="AF387" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG387" t="b">
         <v>1</v>
@@ -43648,13 +43630,13 @@
         <v>1954</v>
       </c>
       <c r="R388">
-        <v>18.43</v>
+        <v>6.14</v>
       </c>
       <c r="S388">
         <v>6.14</v>
       </c>
       <c r="T388">
-        <v>15.73</v>
+        <v>4.92</v>
       </c>
       <c r="U388">
         <v>4.92</v>
@@ -43681,25 +43663,25 @@
         <v>2</v>
       </c>
       <c r="AC388">
+        <v>2</v>
+      </c>
+      <c r="AD388">
         <v>4</v>
       </c>
-      <c r="AD388">
-        <v>6</v>
-      </c>
       <c r="AE388" t="s">
-        <v>2073</v>
+        <v>1983</v>
       </c>
       <c r="AF388" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG388" t="b">
         <v>0</v>
       </c>
       <c r="AH388">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI388">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AJ388">
         <v>3</v>
@@ -43791,7 +43773,7 @@
         <v>1975</v>
       </c>
       <c r="AF389" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG389" t="b">
         <v>1</v>
@@ -43886,7 +43868,7 @@
         <v>1975</v>
       </c>
       <c r="AF390" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG390" t="b">
         <v>1</v>
@@ -43978,7 +43960,7 @@
         <v>1975</v>
       </c>
       <c r="AF391" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG391" t="b">
         <v>1</v>
@@ -44073,10 +44055,10 @@
         <v>3</v>
       </c>
       <c r="AE392" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="AF392" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG392" t="b">
         <v>0</v>
@@ -44174,7 +44156,7 @@
         <v>1975</v>
       </c>
       <c r="AF393" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG393" t="b">
         <v>1</v>
@@ -44266,7 +44248,7 @@
         <v>1975</v>
       </c>
       <c r="AF394" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG394" t="b">
         <v>1</v>
@@ -44358,7 +44340,7 @@
         <v>1975</v>
       </c>
       <c r="AF395" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG395" t="b">
         <v>1</v>
@@ -44450,7 +44432,7 @@
         <v>1975</v>
       </c>
       <c r="AF396" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG396" t="b">
         <v>1</v>
@@ -44539,7 +44521,7 @@
         <v>1975</v>
       </c>
       <c r="AF397" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG397" t="b">
         <v>1</v>
@@ -44628,7 +44610,7 @@
         <v>1975</v>
       </c>
       <c r="AF398" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG398" t="b">
         <v>1</v>
@@ -44717,7 +44699,7 @@
         <v>1975</v>
       </c>
       <c r="AF399" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG399" t="b">
         <v>1</v>
@@ -44806,7 +44788,7 @@
         <v>1975</v>
       </c>
       <c r="AF400" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG400" t="b">
         <v>1</v>
@@ -44901,7 +44883,7 @@
         <v>1975</v>
       </c>
       <c r="AF401" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG401" t="b">
         <v>1</v>
@@ -44993,7 +44975,7 @@
         <v>1975</v>
       </c>
       <c r="AF402" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG402" t="b">
         <v>1</v>
@@ -45076,7 +45058,7 @@
         <v>1975</v>
       </c>
       <c r="AF403" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG403" t="b">
         <v>1</v>
@@ -45165,7 +45147,7 @@
         <v>1975</v>
       </c>
       <c r="AF404" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG404" t="b">
         <v>1</v>
@@ -45257,7 +45239,7 @@
         <v>1975</v>
       </c>
       <c r="AF405" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG405" t="b">
         <v>1</v>
@@ -45349,7 +45331,7 @@
         <v>1975</v>
       </c>
       <c r="AF406" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG406" t="b">
         <v>1</v>
@@ -45441,7 +45423,7 @@
         <v>1975</v>
       </c>
       <c r="AF407" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG407" t="b">
         <v>1</v>
@@ -45533,7 +45515,7 @@
         <v>1975</v>
       </c>
       <c r="AF408" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG408" t="b">
         <v>1</v>
@@ -45625,7 +45607,7 @@
         <v>1975</v>
       </c>
       <c r="AF409" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG409" t="b">
         <v>1</v>
@@ -45717,7 +45699,7 @@
         <v>1975</v>
       </c>
       <c r="AF410" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG410" t="b">
         <v>1</v>
@@ -45809,7 +45791,7 @@
         <v>1975</v>
       </c>
       <c r="AF411" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG411" t="b">
         <v>1</v>
@@ -45865,13 +45847,13 @@
         <v>1958</v>
       </c>
       <c r="R412">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="S412">
         <v>0.87</v>
       </c>
       <c r="T412">
-        <v>1.14</v>
+        <v>0.87</v>
       </c>
       <c r="U412">
         <v>0.87</v>
@@ -45898,10 +45880,10 @@
         <v>3</v>
       </c>
       <c r="AE412" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="AF412" t="s">
-        <v>2080</v>
+        <v>2074</v>
       </c>
       <c r="AG412" t="b">
         <v>0</v>
@@ -45996,7 +45978,7 @@
         <v>1975</v>
       </c>
       <c r="AF413" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG413" t="b">
         <v>1</v>
@@ -46088,7 +46070,7 @@
         <v>1975</v>
       </c>
       <c r="AF414" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG414" t="b">
         <v>1</v>
@@ -46183,7 +46165,7 @@
         <v>1975</v>
       </c>
       <c r="AF415" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG415" t="b">
         <v>1</v>
@@ -46281,7 +46263,7 @@
         <v>1981</v>
       </c>
       <c r="AF416" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG416" t="b">
         <v>0</v>
@@ -46373,7 +46355,7 @@
         <v>1975</v>
       </c>
       <c r="AF417" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG417" t="b">
         <v>1</v>
@@ -46465,7 +46447,7 @@
         <v>1975</v>
       </c>
       <c r="AF418" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG418" t="b">
         <v>1</v>
@@ -46557,7 +46539,7 @@
         <v>1975</v>
       </c>
       <c r="AF419" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG419" t="b">
         <v>1</v>
@@ -46649,7 +46631,7 @@
         <v>1975</v>
       </c>
       <c r="AF420" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG420" t="b">
         <v>1</v>
@@ -46744,7 +46726,7 @@
         <v>1975</v>
       </c>
       <c r="AF421" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG421" t="b">
         <v>1</v>
@@ -46800,13 +46782,13 @@
         <v>1963</v>
       </c>
       <c r="R422">
-        <v>1.36</v>
+        <v>0.65</v>
       </c>
       <c r="S422">
         <v>0.65</v>
       </c>
       <c r="T422">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
       <c r="U422">
         <v>0.65</v>
@@ -46824,7 +46806,7 @@
         <v>1.25</v>
       </c>
       <c r="Z422" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="AA422">
         <v>1</v>
@@ -46842,7 +46824,7 @@
         <v>1977</v>
       </c>
       <c r="AF422" t="s">
-        <v>2078</v>
+        <v>2072</v>
       </c>
       <c r="AG422" t="b">
         <v>0</v>
@@ -46928,7 +46910,7 @@
         <v>1978</v>
       </c>
       <c r="AF423" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG423" t="b">
         <v>1</v>
@@ -47017,10 +46999,10 @@
         <v>3</v>
       </c>
       <c r="AE424" t="s">
-        <v>2074</v>
+        <v>2068</v>
       </c>
       <c r="AF424" t="s">
-        <v>2077</v>
+        <v>2071</v>
       </c>
       <c r="AG424" t="b">
         <v>0</v>
@@ -47115,7 +47097,7 @@
         <v>1975</v>
       </c>
       <c r="AF425" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG425" t="b">
         <v>1</v>
@@ -47210,7 +47192,7 @@
         <v>1975</v>
       </c>
       <c r="AF426" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG426" t="b">
         <v>1</v>
@@ -47305,7 +47287,7 @@
         <v>1975</v>
       </c>
       <c r="AF427" t="s">
-        <v>2076</v>
+        <v>2070</v>
       </c>
       <c r="AG427" t="b">
         <v>1</v>
